--- a/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
+++ b/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Ke hoach bai viet" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Doi chieu cum" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Tu khoa chi tiet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Ngoai pham vi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Tu khoa chinh theo cum" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Ngoai pham vi" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,6 +103,10 @@
       <b val="1"/>
       <color rgb="00A85C10"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -186,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -241,13 +246,34 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -338,6 +364,23 @@
     <tableColumn id="6" name="Cum"/>
     <tableColumn id="7" name="Trang thai"/>
     <tableColumn id="8" name="Trang / ghi chu"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TuKhoaChinhTheoCum" displayName="TuKhoaChinhTheoCum" ref="A1:H15" headerRowCount="1">
+  <autoFilter ref="A1:H15"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Cum tu khoa"/>
+    <tableColumn id="2" name="Tu khoa chinh (dai dien)"/>
+    <tableColumn id="3" name="Volume tu khoa chinh"/>
+    <tableColumn id="4" name="So tu khoa trong cum"/>
+    <tableColumn id="5" name="Tong volume cum"/>
+    <tableColumn id="6" name="Trang thai"/>
+    <tableColumn id="7" name="Trang / ghi chu"/>
+    <tableColumn id="8" name="Danh sach tu khoa con lai trong cum"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -632,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -836,7 +879,14 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Sheet 5 - Ngoai pham vi: 2 nhom tu khoa khong lien quan dich vu Digicom.</t>
+          <t>Sheet 5 - Tu khoa chinh theo cum: moi cum 1 dong - tu khoa chinh dai dien + toan bo tu khoa con lai trong cum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Sheet 6 - Ngoai pham vi: 2 nhom tu khoa khong lien quan dich vu Digicom.</t>
         </is>
       </c>
     </row>
@@ -23905,6 +23955,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Cum tu khoa</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Tu khoa chinh (dai dien)</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Volume tu khoa chinh</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>So tu khoa trong cum</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Tong volume cum</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Trang thai</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Trang / ghi chu</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Danh sach tu khoa con lai trong cum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Cách viết / công thức / cấu trúc</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>cấu trúc bài pr</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>290</v>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>/cach-viet-bai-pr-chuan-bao-chi/</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>cách viết bài pr; cách viết bài pr cho sản phẩm; cách viết bài pr sản phẩm; công thức viết bài pr; kỹ năng viết bài pr; bài pr theo công thức pas; các dạng bài pr; cách viết bài pr cho doanh nghiệp; cách viết bài pr trên facebook; viết bài pr theo công thức 3s; cách viết bài pr sự kiện; 12 cách viết tiêu đề cho bài pr; 3 công thức viết bài pr; bài pr bất động sản theo công thức; bài viết pr theo công thức 3s; bố cục bài pr; bố cục bài viết pr; bố cục một bài pr; các cách viết bài pr; các công thức viết bài pr; các dạng bài viết pr; các loại bài viết pr; cách viết 1 bài báo pr; cách viết 1 bài pr; cách viết 1 bài pr hiệu quả; cách viết 1 bài pr sản phẩm; cách viết bài báo pr; cách viết bài chia sẻ pr brand; cách viết bài pr cho công ty; cách viết bài pr cho mỹ phẩm; cách viết bài pr cho page; cách viết bài pr cho sản phẩm công nghệ; cách viết bài pr cho sự kiện; cách viết bài pr cho trung tâm ngoại ngữ; cách viết bài pr cho trường mầm non; cách viết bài pr chuyên đề; cách viết bài pr chương trình khuyến mãi; cách viết bài pr công ty; cách viết bài pr du lịch; cách viết bài pr dịch vụ; cách viết bài pr dự án bất động sản; cách viết bài pr giới thiệu sản phẩm; cách viết bài pr giới thiệu về workshop; cách viết bài pr hấp dẫn; cách viết bài pr khách sạn; cách viết bài pr lên báo; cách viết bài pr mỹ phẩm hiệu quả; cách viết bài pr ngược trong bds; cách viết bài pr nhân vật; cách viết bài pr pha t biê u; cách viết bài pr sách; cách viết bài pr theo công thức 3s; cách viết bài pr thuê; cách viết bài pr trên facebook group; cách viết bài pr trên fanpage hấp dẫn; cách viết bài pr về bệnh sỏi thận; cách viết bài pr về sản phẩm; cách viết bài pr đèn led; cách viết bài quản cáo pr trên facebook; cách viết bài quảng cáo pr trên facebook; cách viết bài truyền thông pr; cách viết một bài adaption trong pr; cấu trúc của một bài pr; học cách viết bài pr; kỹ năng viết bài pr bán hàng; kỹ năng viết bài pr fb; kỹ năng viết bài pr tăng doanh số bán hàng; phân loại bài pr; phân loại bài viết pr</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>Đuôi dài chung (bài PR / viết bài PR...)</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>bài pr</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="D3" s="24" t="n">
+        <v>260</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>210</v>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ gián tiếp (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>/bai-pr-la-gi/ + /cach-viet-bai-pr-chuan-bao-chi/ trả lời ở mức tổng quát</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>bài báo pr; bài viết pr; bài viết pr spa; viết bài pr; viết bài pr báo chí; 1 pr 2 4-9 bài đọc; 1 số bài viết pr son; 3 dang bài viết pr; 64 từ khóa trong viết bài pr; adverter bài pr; balo bài pr; bao gia bài pr báo saigon time; box thông tin bài pr; by-liner bài pr có qc chân trang; bài biết pr cho nội thất; bài báo pr chuyên; bài báo pr chuyên mục tài trợ tư vấn; bài báo pr thuộc công cụ quảng cáo nào; bài báo pr về sàn văn phòng; bài demographic trong pr; bài dịch về nhân viên pr; bài giảng pr truyền thông; bài học pr từ sunlight; bài pr 400 chữ; bài pr aroma resort trên dântrí bị xóa; bài pr bao nhiêu tiền; bài pr bia budweiser trên báo; bài pr budweiser trên báo; bài pr báo; bài pr báo chíu; bài pr báo lecourrier; bài pr báo saigon times online; bài pr cao sao vàng; bài pr cho công ty thiết kế nội thất; bài pr cho gà texas; bài pr cho page; bài pr cho texas; bài pr cho trang sức kim cương; bài pr có chèn tvc quảng cáo; bài pr của acnes; bài pr của kols viết như thế nào; bài pr demographic; bài pr gồm những phần nào; bài pr infographic; bài pr inforgraphic; bài pr kem chống nắng; bài pr kem đánh răng p s; bài pr khu đô thị; bài pr len; bài pr ly cafe; bài pr lửa trại; bài pr máy lọc khí sharp; bài pr nhà sách; bài pr nhân vật; bài pr nước hoa; bài pr nội bộ; bài pr saigon times; bài pr sách nguyễn nhật ánh; bài pr theo string; bài pr theo strings; bài pr tiếng anh là j; bài pr trên báo giúp tăng uy tín trên google; bài pr trên kênh14; bài pr trên thời báo kinh tế sài gòn; bài pr trưởng ban đối nội; bài pr tăng cơ bắp; bài pr tổng kết cuối nam; bài pr và bài quảng cáo; bài pr về bộ phận chăm sóc khách hàng; bài pr về ca sỹ; bài pr về công ty; bài pr về dasani; bài pr về digital marketing; bài pr về món nga; bài pr về nhân vật; bài pr về nutiboost; bài pr về nước dasani; bài pr về nước tẩy; bài pr về nước uống; bài pr về nội y; bài pr về phân bón; bài pr về sữa nutiboost; bài pr về trị mụn; bài pr về tập đoàn; bài pr xe tải; bài pr đơn vị tài trợ; bài pr đại lý; bài pr đại lý ô tô; bài viết cho báo chí và bài viết cho pr; bài viết chuẩn pr; bài viết pr branding cho bán lẻ; bài viết pr cho muối tôm tây ninh; bài viết pr cho shop; bài viết pr của now; bài viết pr của now.vn; bài viết pr do nhà báo viết; bài viết pr dạy bơi; bài viết pr fb; bài viết pr homestay; bài viết pr hài; bài viết pr layout; bài viết pr luxgarden; bài viết pr marketingai; bài viết pr nhân viên; bài viết pr nước hoa; bài viết pr quyên góp áo trắng cho em; bài viết pr sàn văn phòng; bài viết pr trà sữa; bài viết pr tôm hùm; bài viết pr vietnambiz; bài viết pr và quảng cáo khác nhau; bài viết pr về công ty; bài viết pr về durex; bài viết pr về nha trang; bài viết pr về đồ nội thất cao cấp; bài viết pr đồ ăn; bài viết quảng cáo pr; bài viết testimonal trong pr; bài đăng pr; bài đọc 2 1 pr 3 18-22; báo bài pr trên saigon tourist; báo bài pr trên saigontourist; bí quyết viết bài pr; cach viet một bài pr; caác bài phát biểu trong chiến dịch pr; caác bài pr cho dầu gội trị gàu; caác bài viết pr cho các dầu gội trị gàu; caácc bài pr cho dầu gội trị gàu; caách viết 1 bài pr; caách viết bài pr về công ty; caấu trúc một bài pr; chapeau bài pr; chiến lược đi bài pr; chèn clip vào bài pr; chủ đề viết bài pr; coông thức strings trong viết bài pr; các bài báo pr sacombank; các bài pr; các bài pr game; các bài pr nước hoa; các bài pr theo kiểu editorial; các bài pr về seo; các bài viết pr strings; các bài viết pr về bác sĩ hàn quốc; các bài viết pr về rong nho; các hình thức bài pr; các phần của bài viết pr; các thể loại bài viết pr; các viết bài pr; cách chuẩn bị bài phát biểu pr; cách lập dàn ý bài pr; cách thức viết 1 bài pr; cách thức viết bài pr; cách trình bày campaign trong báo cáo pr; cách xác định giai đoạn của môt bài pr; công cụ số liệu bài pr; cơ sở lý thuyết về bài pr của kols; cần người viết bài pr; cần tìm người viết bài pr; demo bài pr báo vne; diễn văn bài phát biểu trong pr; dàn ý một bài pr; dđặt bài viết pr; dđể viết tốt 1 bài pr; dđịnh nghĩa bài pr; dộ dài một bài pr; format bài pr gửi báo chí; format bài pr mớ; format bài pr mới; freelancer viết bài pr; gói bài pr cho seo; hoọc anh văn để viết bài pr; học viết bài pr; học viết bài pr marketing ở đâu; hợp đồng viết bài pr; khung viết một bài pr; khóa học viết bài pr; kinh nghiệm viết bài pr; kế hoạch tin bài pr; kế hoạch viết cho bài pr; kỹ thuật viết bài pr; kỹ thuật viết bài pr pdf; kỹ thuật viết bài pr quảng cáo pdf; làm sao để viết bài pr; lượt view trung bình cho bài pr hieeu; mua sách kỹ thuật viết bài pr; mô hình kim tự tháp ngược trong viết bài pr; nestle bài pr; neên đi bài pr như thế nào; nghiên cứu về bài pr; nghề viết bài pr; nghệ thuật viết bài pr; nguyên tắc viết bài pr; nguyên tắc viết bài pr trên báo chí; nhung bài viết pr bán nhà đất; nhân viên viết bài pr; nhận viết bài pr; những bài pr nổi tiếng; những bài pr nổi tiếng fb; những bài pr đăng cuối năm; những bài viết pr cho ngày hội sách; những bài viết pr cho trung tâm tiếng anh; phân biệt 1 bài báo và 1 bài pr; phân biệt bài viết pr; phân cấp bài pr; phân tích một bài pr trên báo; phần mở đầu của một bài pr; pr là hãng bày nào; quy cách đi bài pr trên báo; sabo bài pr; sách kỹ thuật viết bài pr quảng cáo; sườn bài pr; thế nào là bài báo pr; tiêu chí của một bài pr; tiêu đề bài pr; toplist.vn là trang web viết các bài pr lừa đảo; trình bày các công cụ của pr; trình bày khái niệm pr; tìm người viết bài pr; tìm người viết bài pr fb; tìm từ khóa trên bài viết pr onliine; tìm từ khóa trên bài viết pr online; tìm việc làm viết bài pr; từ khóa seo cho bài pr; unica kĩ thuật viết bài pr quảng cáo; vieế bài pr theo cong thức strings; vieết bài pr sao cho thu hút; vieết bài pr tại nhà; viết bài pr bao nhiêu tiền 1 bài; viết bài pr chia sẻ lên các diễn đàn; viết bài pr cho cảng biển; viết bài pr cho phụ gia ngành giấy; viết bài pr cho studio cưới; viết bài pr công ty; viết bài pr công ty honda; viết bài pr công ty với 200 từ; viết bài pr first sight; viết bài pr hiệu quả; viết bài pr la gì; viết bài pr món ăn cho người mới bắt đầu; viết bài pr toeic; viết bài pr và seo; viết bài pr về món nga; viết bài pr về địa điểm tổ chức; viết bài pr zalo; viết bài pr đăng báo; viết bài quảng pr cho phân bón; viết kết bài pr; văn phong bài pr; vị trí pr bài viết trên báo điện tử; xem báo giaá bài pr các báo ở đâu; xem số liệu bài pr; xu hướng viết bài pr; xác định công chúng của bài viết pr; xây dựng thông điệp của bài viết pr; yêu cầu của một bài pr; yý tưởng viết bài pr; đặt tít bài pr sao cho hấp dẫn; đọc &amp; phân tích các bài pr sau</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Mẫu / ví dụ bài PR</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>bài pr mẫu</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" s="24" t="n">
+        <v>67</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>/bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>bài pr hay; các bài pr mẫu; mẫu bài viết pr sự kiện; những bài pr hay; những bài viết pr sản phẩm hay; những mẫu bài pr hay; bài viết pr mẫu; các bài pr hay; mẫu bài pr sản phẩm; bài mẫu pr; bài mẫu pr sự kiện; bài mẫu pr về món nga; bài pr mẫu của tổ chức giáo dục; bài pr mẫu theo công thức pas; bài pr mẫu về công ty; bài pr mẫu về nhân vật; bài pr nhà hangfd hay; bài pr nhân vật hay; bài pr sản phẩm hay; bài pr sản phẩm mẫu; bài viết pr hay; bài viết pr mẫu xe hơi; bài viết pr sản phẩm mẫu; bài viết pr về sản phẩm hay; caách giật tít hay cho bài pr; các bài phỏng pr vấn mẫu; các bài pr hay về dược phẩm; các bài pr pas mẫu; các bài pr sự kiện mẫu; các bài viết pr sản phẩm hay; các facebooer viết pr bài viết hay; các facebooker viết pr bài viết hay; các facebooker viết pr bài viết hay nổi tiếng; các nhân vật viết pr bài viết hay; cách giật tít hay cho bài pr; cách nhận biết baì pr hay bài marketing; cách tạo một bài pr hay; cách viết bài pr hay; cách viết bài pr sản phẩm hay; mẫu 1 bài pr; mẫu bài pr cho sự kiện; mẫu bài pr hay; mẫu bài pr theo aida; mẫu bài pr theo công thức aida; mẫu bài pr xe tải; mẫu bài viết pr sản phẩm; một bài pr mẫu cho ra mắt sản phẩm mới; một bài pr ấn tượng; một số bài pr hay; một số bài pr mẫu; một số bài pr mẫu sự kiện; nhung bài viết pr bán nhà đất hay; những bài pr game hay; những bài pr hay nhất; những bài pr hầm rượu vang hay; những bài pr pas mẫu; những bài viết pr hay; những bài viết pr hay nhất; những bài viết pr về shop hay; tham khảo các mẫu bài pr đỉnh cao; tập hợp các bài viết hay về pr; ví dụ bài pr; ví dụ các bài pr về món nga; ví dụ các công thức viết bài pr; ví dụ các công thức viết bài pr facebook; đặt tít hay cho bài pr sản phẩm sơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Báo giá theo đầu báo cụ thể</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>báo giá bài pr vnexpress</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>152</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>180</v>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm Booking báo)</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>15 trang /book-bao-*/ + /booking-bao-pr/</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>báo giá đăng bài pr trên kenh14; báo giá bài pr 24h; báo giá bài pr cafef; báo giá bài pr kenh14; báo giá bài pr trên vnexpress; báo giá bài pr vietnamnet; báo giá đăng bài pr trên kênh 14; báo giá đăng bài pr trên vnexpress; agency book bài pr trên báo cnn; agency book bài pr trên times new; bao gia bài pr giaoduc.net.vn; bao giaá viết bài pr cafef; bao giá bài pr báo xa luan điện tử; bao giá bài pr theleader; bao giá bài pr thế giới tiếp thị online; bao giá bài pr xa luan online; bao giá bài pr xaluan online; baáo giá bài pr an ninh thủ đô online; baáo giá bài pr baodautu.vn; baáo giá bài pr báo thanh niên online; baáo giá bài pr báo đầu tư; baáo giá bài pr báo đầu tư 2019; baáo giá bài pr eva; baáo giá bài pr người lao động; baáo giá bài pr thiếu niên tiền phong online; baáo giá bài pr tiếp thị gia đình báo giấy; baáo giá bài pr trên báo baodautu.vn; baáo giá bài pr vietnam economic times online; baáo giá bài pr vietnamnet; baáo giá bài pr vir online; baáo giá bài pr vnexpress; baáo giá bài pr zing news; baáo giá lên bài pr 24h.com.vn; baáo giá lên bài pr afamily.vn; baáo giá lên bài pr baodautu.vn; baáo giá lên bài pr batdongsan.com.vn; baáo giá lên bài pr cafebiz; baáo giá lên bài pr cafef; baáo giá lên bài pr dân trí; baáo giá lên bài pr eva.vn; baáo giá lên bài pr giadinh.net; baáo giá lên bài pr ictnew; baáo giá lên bài pr otofun; baáo giá lên bài pr soha; baáo giá lên bài pr thanh niên; baáo giá lên bài pr vietnamnet; baáo giá lên bài pr vnexpress; baáo giá lên bài pr zing; baáo giá đăng bài pr trên soha; book bài pr trên báo nước ngoài cnn; book bài pr trên tạp chí bác sĩ gia đình; booking bài pr báo batdongsan.com.vn; booking bài pr trên tiếp thị và gia đình; bài pr aroma resort trên dân trí bị xóa; bài pr báo msn online; bài pr báo pháp luật online; bài pr báo sggp hoa van online; bài pr báo sggp online; bài pr báo vtc news online; bài pr cafef; bài pr dân trí; bài pr kenh14; bài pr ngoisao; bài pr ngoisao.net; bài pr thanh niên; bài pr trên vnexpress; bài pr zing; báo giá book bài pr trên vnexpress; báo giá bài pr 24h.com.vn; báo giá bài pr afamily; báo giá bài pr báo công an giấy; báo giá bài pr báo công an nhân dân online; báo giá bài pr báo giấy sggp hoa văn; báo giá bài pr báo giấy tiếp thị gia đình; báo giá bài pr báo giấy tuổi trẻ; báo giá bài pr báo lao động online; báo giá bài pr báo pháp luật việt nam online; báo giá bài pr báo theleader; báo giá bài pr báo tiếp thị gia đình online; báo giá bài pr báo vnexpress; báo giá bài pr báo vtc điện tử; báo giá bài pr báo xaluan; báo giá bài pr báo đầu tư 2019; báo giá bài pr doanh nhân sài gòn; báo giá bài pr eva.vn; báo giá bài pr kenh14 2017; báo giá bài pr lao động online; báo giá bài pr ngoisao.net; báo giá bài pr người lao động; báo giá bài pr người lao động 2019; báo giá bài pr người lao động online; báo giá bài pr sài gòn giải phóng online; báo giá bài pr theleader; báo giá bài pr tiền phong online; báo giá bài pr trên 24h; báo giá bài pr trên afamily; báo giá bài pr trên baodautu.vn; báo giá bài pr trên báo baodautu.vn; báo giá bài pr trên dân trí; báo giá bài pr trên eva; báo giá bài pr trên eva.vn; báo giá bài pr trên lao động online; báo giá bài pr trên ngoisao net; báo giá bài pr trên vietnamnet; báo giá bài pr trên vnexpress 2017; báo giá bài pr trên vnexpress 2018; báo giá bài pr trên webtretho; báo giá bài pr trên zing; báo giá bài pr tạp chí elle; báo giá bài pr vietnam investment review online; báo giá bài pr vnexpress 2019; báo giá bài pr vnreview; báo giá bài pr vov; báo giá đăng bài pr batdongsan.com.vn; báo giá đăng bài pr trên 24h; báo giá đăng bài pr trên 24h.com.vn; báo giá đăng bài pr trên cafef; báo giá đăng bài pr trên soha; báo giá đăng bài pr trên zing; bảng giá đăng bài pr trên báo 24h; bảng giá đăng bài pr trên báo tuổi trẻ; cafef bài pr; cafef bài pr giá; chi phí bài pr của kenh14; chi phí thuê viết bài pr trên tạp chí elle; chi phí viết bài pr trên new zing; chi phí viết bài pr trên vnexpress; chi phí đăng bài pr trên cafebiz; chi phí đăng bài pr trên ictnews; cách thuê dân trí pr bài viết; demo các vị trí bài pr trên vnexpress; format bài pr gửi báo chí times new roman; giá book bài pr kenh14; giá bài pr trên dân trí; giá bài pr trên sggp hoa van dien tử; giá bài pr trên thời sự vtv1; giá bài pr trên vnexpress; giá bài pr tạp chí tài chính; giá bài quảng cáo pr baomoi.com; giá bài quảng cáo pr new.zing.vn; giá bài viết pr trên zing; giá đăng bài pr vnexpress 2017; liên hệ bài pr trên vnexpress; lên bài pr baomoi; viết bài pr trên báo cafef; đăng bài pr trên báo dân trí; đăng bài pr trên cafef; đăng bài pr trên eva.vn; đăng bài pr trên giadinh.net; đăng bài pr trên vietnamnet; đăng bài pr trên vnexpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Dịch vụ viết bài PR (chưa có trang)</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>dịch vụ viết bài pr</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>160</v>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Gap - BÀI MỚI (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Đề xuất bài mới, CTA về /booking-bao-pr/</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>báo giá viết bài pr; chi phí viết bài pr; thuê viết bài pr; giá viết bài pr; báo giá bài viết pr trên website cho phu nư; báo giá dịch vụ viết bài pr; báo giá viết bài pr cho sản phẩm; báo giá viết bài pr trên http genk.vn; bảng báo giá viết bài pr trên baogiaothong.vn; bảng giá viết bài pr; cách đánh giá bài viết pr hiệu quả; dịch vụ viết bài pr chuyên nghiệp; gía dịch vụ viết bài pr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Giá / đăng / booking chung (không kèm tên báo)</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>đăng bài pr</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>126</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm Booking báo)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>/booking-bao-pr/ (hub giá)</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>book bài pr; báo giá bài pr; giá bài pr; giá đăng bài pr; booking bài pr; đăng bài pr trên báo; agency book bài pr; agency book bài pr trên các báo nước ngoài; agency book bài pr được các báo online nước ngoài; agency đăng bài pr; bao giá bài pr dmtin; baáo giá bài pr; baáo giá bài pr báo vsao; baáo giá bài pr báo vsao điện tử; baáo giá bài pr báo xã luận điện tử; baáo giá bài pr dantri; baáo giá gói đăng bài pr trên ngôi sao.net; baáo giá lên bài pr phunuonline; baáo giá lên bài pr thethaovanhoa; baáo giá lên bài pr tuoitre; baáo giá lên bài pr vietnamexpress; baáo giá lên bài pr vneconomy; biểu giá bài pr báo công thương online; biểu giá bài pr báo công thương điện tử; book bài pr admicro; book bài pr trên báo nước ngoài time; booking bài pr báo online; booking viết bài pr; báo giá booking bài pr admicro; báo giá bài pr báo công thương online; báo giá bài pr báo hoa học trò điện tử; báo giá bài pr báo ione; báo giá bài pr báo mtv; báo giá bài pr báo mtv we điện tử; báo giá bài pr báo mtvwe điện tử; báo giá bài pr báo thitkho; báo giá bài pr báo thê thao văn hóa online; báo giá bài pr báo vsao.com; báo giá bài pr báo xone điện tử; báo giá bài pr bạch mỹ liên; báo giá bài pr chính phủ online; báo giá bài pr dan ong magazine; báo giá bài pr dantri.com.vn; báo giá bài pr dantri.com.vn 2017; báo giá bài pr ict news; báo giá bài pr ione 2017; báo giá bài pr kenh 14; báo giá bài pr marrybaby; báo giá bài pr online; báo giá bài pr thanhnien; báo giá bài pr the leader; báo giá bài pr thế giới văn hóa online; báo giá bài pr trên báo giấy lao độn; báo giá bài pr trên báo mới; báo giá bài pr trên doanh nhan cuoi tuan online; báo giá bài pr trên doanh nhan plus; báo giá bài pr trên foody; báo giá bài pr trên kienthuc; báo giá bài pr trên kienthucdoisong; báo giá bài pr trên marrybaby; báo giá bài pr trên thanhnien.vn; báo giá bài pr trên thế giới văn hóa; báo giá bài pr trên thế giới văn hóa online; báo giá bài pr trên trang thegioivanhoa.net; báo giá bài pr trên trang thế giới văn hóa.net; báo giá bài pr trên trang voh; báo giá bài pr tư vấn tiêu dùng; báo giá bài pr tư vấn tiêu dùng online; báo giá bài pr v economic times online; báo giá bài pr vneconomy online; báo giá bài pr vo; báo giá bài pr voh; báo giá bài pr đàn ông magazine; báo giá đăng bài pr trên baoquocte.vn; báo giá đăng bài pr trên báo quốc tế; bảng giá book bài pr trên ivivu; bảng giá bài pr có chèn tvc quảng cáo; bảng giá đăng bài pr trên báo điện tử; bảng giá đăng bài pr vneconomy; cah đăng bài pr trên các trang báo điện tử; chi phi đăng bài pr trên các báo; chi phí book bài pr; chuỗi bài pr giá rẻ; các bài pr mảng giáo dục; cách book bài pr trên báo chí; cách viêt bài pr facebook cho sản phẩm; cách đăng bài pr trên báo chí; công ty booking bài pr; giá 1 bài pr thông thường; giá 1 bài pr trên elle.vn; giá 1 bài pr trên kenh 14; giá bài pr báo công thương online; giá bài pr báo lecourrier; giá bài pr báo lecourrier online; giá bài pr forbes; giá bài pr trên báo bưu điện; giá bài pr trên báo đẹp plus điện tử; giá bài pr trên depplus online; giá bài pr trên docbao online; giá bài pr trên thời báo kinh tế; giá bài pr trên trang infonet online; giá bài quảng cáo pr basomoi.com; giá bài quảng cáo pr trên autobikes.vn; giá bài quảng cáo pr trên tinxe.vn; giá bài viêt pr trên diadiemanuong; giá chạy bài pr trên vneconomy là bao nhiêu; giá của một bài pr trung bình hiện nay; giá dang bài pr báo mới; giá đăng bài pr trên báo điện tử; giá đăng bài pr trên các báo; gói mua bài pr giá rẻ; hệ thống book bài pr trên các báo; hỗ trợ đăng bài pr trên nhịp sống sendo; kênh đăng bài pr; neên đăng bài pr lên báo nào; những bài pr dịch vụ educate consumers; viết bài pr facebook; viết bài pr sản phẩm trên facebook; viết bài pr thuê; xem báo giá bài pr các báo ở đâu; đăng bài pr báo điện tử; đăng bài pr trên báo điện tử; đăng bài pr trên các báo lớn; đăng bài pr trên phụ nữ today; đăng bài pr ở đâu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>PR theo sản phẩm</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>bài pr sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Mục con trong /cach-viet-bai-pr-chuan-bao-chi/ + /bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>bài viết pr sản phẩm; bài viết pr về sản phẩm; viết bài pr cho sản phẩm; viết bài pr sản phẩm; bài biết pr cho sản phẩm nước giải khát; bài pr cho sản phẩm; bài pr cho sản phẩm dành cho pg; bài pr cho sản phẩm mới ra mắt; bài viết pr cho sản phẩm nước giải khát; bài viết pr sản phẩm của học vien; cau trúc viêt bài pr sản phẩm; các bài viết pr sản phẩm; các bài viết pr sản phẩm handmade; cách làm 1 bài pr cho 1 sản phẩm; neên đăn bài pr sản phẩm trên báo nào; sản phẩm mới của samsung bài pr; tieu đề bài pr giới thiệu sản phẩm; viết bài pr sản phẩm kiếm tiền; viết bài pr sản phẩm mới; viết bài pr sản phẩm thu hút khách hàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>PR doanh nghiệp / thương hiệu</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>bài pr thương hiệu</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>/bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>bài pr doanh nghiệp; bài pr cho doanh nghiệp; viết bài pr cho doanh nghiệp; bài pr từ thương hiệu; bài pr về doanh nghiệp; bài viết pr doanh nghiệp may mặc; bài viết pr tăng độ nhận diện thương hiệu; có được bán bài pr doanh nghiệp không; hướng dẫn viết bài pr cho doanh nghiệp; nguyeên tắc iets một bài pr thương hiệu; viết bài pr cho thương hiệu cho doanh nghiệp; viết bài pr cho thương hiệu công ty con; viết bài pr cho thương hiệu giày nike; viết bài pr doanh nghiệp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Định nghĩa "bài PR là gì"</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>viết bài pr là gì</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>/bai-pr-la-gi/</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>bài pr là gì; bài pr có chân dung quảng cáo là gì; bài pr có chân dung quảng cáo là gì marketing; bài viết pr tiếng anh là gì; diễn văn bài phát biểu là gì trong pr; lead bài pr là gì; sabo là gì trong viết bài pr; viết bài pr editorial là gì; viết bài pr nghĩa là gì; đăng bài pr là gì</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Mẫu/ví dụ theo ngành (chưa có)</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>bài viết pr về du lịch</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Thêm chip-grid ngành vào /bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>bài pr về nhà hàng; bài viết pr khách sạn; bài pr cho bất động sản; bài pr cực hay về nhà hàng; bài pr mỹ phẩm; bài pr về nhà hàng nga tại việt nam; bài viết pr du lịch cần những gì; bài viết pr khu du lịch sinh thái; bài viết pr khách sạn mẫu; bài viết pr một khu du lịch; bài viết pr nhà hàng; bài viết pr nhà hàng trên báo mạng; các bài pr cho một chương trình bất động sản; mẫu bài pr bất động sản theo công thức; mẫu bài viết pr về khách sạn; tiêu chí bài pr bất động sản hay; top bài pr bất động sản đặc sắc; vieết bài pr cho khách sạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Viết bài PR chuẩn SEO</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>viết bài pr chuẩn seo</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>Thêm mục vào /cach-viet-bai-pr-chuan-bao-chi/, link /mua-textlink/ + /dich-vu-backlink/</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>cách viết bài pr chuẩn seo; dịch viết bài pr chuẩn seo; dịch vụ viết bài pr chuẩn seo; kỹ năng viết bài pr chuẩn seo; kỹ năng viết bài pr chuẩn seo ebook; seongon checklist bài pr chuẩn seo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>PR bản thân / xin việc (Jiko PR)</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>bài mẫu pr bản thân bằng tiếng nhật</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>Ngoài phạm vi</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>bài pr bản thân; bài pr bản thân bằng tiếng nhật; bài viết pr bản thân; bài viết pr về bản thân; các bài viết pr cho game học tiếng nhật; nhờ các facebook cá nhân viết bài pr; yêu cầu về bài pr cá nhân</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>CTV / tuyển người viết</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>ctv viết bài pr</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Ngoài phạm vi</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>cộng tác viên viết bài pr; agency tuyển ctv viết bài pr; agency tuyển team viết bài pr; agency tuyển viết bài pr; mục đích đăng bài tuyển dụng để pr; tuyển ctv viết bài pr; tuyển ctv viết bài pr báo chí; tuyển cộng tác viên viết bài pr; tuyển người viết bài pr; tuyển nhân viên pr viết bài website; tuyển viết bài pr agency; tuyển viết bài pr đăng báo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>PR theo sự kiện</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>viết bài pr cho sự kiện</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Mục con trong /bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>bài pr sau sự kiện; bài pr sự kiện; bài pr sự kiện về quốc tế thiếu nhi; bài viết pr sự kiện; bài viết pr sự kiện ô tô; caác bài viết pr sự kiện; caách viết bài pr sự kiện; các bài viết pr cho sự kiện; những bài viết pr cho sự kiện ngày hội sách</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -23914,63 +24537,63 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>NGOAI PHAM VI - KHONG VIET, KHONG GOP</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>PR bản thân / xin việc (Jiko PR)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>8 tu khoa - 20 luot/thang</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Vi du: bài mẫu pr bản thân bằng tiếng nhật, bài pr bản thân, bài pr bản thân bằng tiếng nhật, bài viết pr bản thân, bài viết pr về bản thân, các bài viết pr cho game học tiếng nhật, nhờ các facebook cá nhân viết bài pr, yêu cầu về bài pr cá nhân</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>CTV / tuyển người viết</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>13 tu khoa - 20 luot/thang</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>Vi du: ctv viết bài pr, cộng tác viên viết bài pr, agency tuyển ctv viết bài pr, agency tuyển team viết bài pr, agency tuyển viết bài pr, mục đích đăng bài tuyển dụng để pr, tuyển ctv viết bài pr, tuyển ctv viết bài pr báo chí, tuyển cộng tác viên viết bài pr, tuyển người viết bài pr</t>
         </is>

--- a/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
+++ b/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>Viet 1 bai rieng ve quy trinh viet (Digicom viet hay khach tu viet), viet mien phi khi dat tu 3 dau bao (dung uu dai hien co), chi phi neu viet rieng. CTA chinh dan ve /booking-bao-pr/. Duoc link vao tu /bai-pr-la-gi/ va /cach-viet-bai-pr-chuan-bao-chi/.</t>
+          <t>Viet 1 bai rieng ve quy trinh viet (Digicom viet hay khach tu viet), viet mien phi khi dat tu 3 dau bao (dung uu dai hien co), chi phi neu viet rieng. Neu them 1 doan cho doi tuong 'PR ca nhan/doanh nhan' (Hieu xac nhan day la nhu cau thuc: nguoi muon booking bao de PR cho chinh minh, khong phai viet CV xin viec - tu khoa 'bai pr ban than/ca nhan'). CTA chinh dan ve /booking-bao-pr/. Duoc link vao tu /bai-pr-la-gi/ va /cach-viet-bai-pr-chuan-bao-chi/.</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1500,11 +1500,11 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
+          <t>PR bản thân - xin việc/du học Nhật (Jiko PR)</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C13" s="11" t="n">
         <v>20</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
@@ -1569,21 +1569,44 @@
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
           <t>Nhiễu (loại)</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Loại</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2281,7 +2304,7 @@
       <c r="E20" s="17" t="inlineStr"/>
       <c r="F20" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
+          <t>PR bản thân - xin việc/du học Nhật (Jiko PR)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -2291,7 +2314,7 @@
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
@@ -6761,17 +6784,17 @@
       <c r="E180" s="17" t="inlineStr"/>
       <c r="F180" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
-        </is>
-      </c>
-      <c r="G180" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="G180" s="21" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
         </is>
       </c>
       <c r="H180" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6812,7 @@
       <c r="E181" s="17" t="inlineStr"/>
       <c r="F181" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
+          <t>PR bản thân - xin việc/du học Nhật (Jiko PR)</t>
         </is>
       </c>
       <c r="G181" s="20" t="inlineStr">
@@ -6799,7 +6822,7 @@
       </c>
       <c r="H181" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
@@ -9337,17 +9360,17 @@
       <c r="E272" s="17" t="inlineStr"/>
       <c r="F272" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
-        </is>
-      </c>
-      <c r="G272" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="G272" s="21" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
         </is>
       </c>
       <c r="H272" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
@@ -10401,17 +10424,17 @@
       <c r="E310" s="17" t="inlineStr"/>
       <c r="F310" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
-        </is>
-      </c>
-      <c r="G310" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="G310" s="21" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
         </is>
       </c>
       <c r="H310" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
@@ -15133,7 +15156,7 @@
       <c r="E479" s="17" t="inlineStr"/>
       <c r="F479" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
+          <t>PR bản thân - xin việc/du học Nhật (Jiko PR)</t>
         </is>
       </c>
       <c r="G479" s="20" t="inlineStr">
@@ -15143,7 +15166,7 @@
       </c>
       <c r="H479" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
@@ -20593,17 +20616,17 @@
       <c r="E674" s="17" t="inlineStr"/>
       <c r="F674" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
-        </is>
-      </c>
-      <c r="G674" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="G674" s="21" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
         </is>
       </c>
       <c r="H674" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
@@ -23533,17 +23556,17 @@
       <c r="E779" s="17" t="inlineStr"/>
       <c r="F779" s="15" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
-        </is>
-      </c>
-      <c r="G779" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="G779" s="21" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
         </is>
       </c>
       <c r="H779" s="17" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43934,7 @@
     <row r="764">
       <c r="A764" s="22" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
+          <t>PR bản thân - xin việc/du học Nhật (Jiko PR)</t>
         </is>
       </c>
       <c r="B764" s="23" t="inlineStr">
@@ -43934,7 +43957,7 @@
       </c>
       <c r="F764" s="26" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
@@ -43947,7 +43970,7 @@
       </c>
       <c r="C765" s="32" t="inlineStr">
         <is>
-          <t>bài pr bản thân</t>
+          <t>bài pr bản thân bằng tiếng nhật</t>
         </is>
       </c>
       <c r="D765" s="33" t="n">
@@ -43960,12 +43983,12 @@
       </c>
       <c r="F765" s="34" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
     <row r="766">
-      <c r="A766" s="27" t="n"/>
+      <c r="A766" s="31" t="n"/>
       <c r="B766" s="32" t="inlineStr">
         <is>
           <t>—</t>
@@ -43973,7 +43996,7 @@
       </c>
       <c r="C766" s="32" t="inlineStr">
         <is>
-          <t>bài pr bản thân bằng tiếng nhật</t>
+          <t>các bài viết pr cho game học tiếng nhật</t>
         </is>
       </c>
       <c r="D766" s="33" t="n">
@@ -43986,75 +44009,79 @@
       </c>
       <c r="F766" s="34" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
     <row r="767">
-      <c r="A767" s="27" t="n"/>
-      <c r="B767" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C767" s="32" t="inlineStr">
-        <is>
-          <t>bài viết pr bản thân</t>
-        </is>
-      </c>
-      <c r="D767" s="33" t="n">
-        <v>0</v>
+      <c r="A767" s="22" t="inlineStr">
+        <is>
+          <t>CTV / tuyển người viết</t>
+        </is>
+      </c>
+      <c r="B767" s="23" t="inlineStr">
+        <is>
+          <t>Từ khoá chính</t>
+        </is>
+      </c>
+      <c r="C767" s="23" t="inlineStr">
+        <is>
+          <t>ctv viết bài pr</t>
+        </is>
+      </c>
+      <c r="D767" s="24" t="n">
+        <v>10</v>
       </c>
       <c r="E767" s="37" t="inlineStr">
         <is>
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="F767" s="34" t="inlineStr">
-        <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+      <c r="F767" s="26" t="inlineStr">
+        <is>
+          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" s="27" t="n"/>
-      <c r="B768" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C768" s="32" t="inlineStr">
-        <is>
-          <t>bài viết pr về bản thân</t>
-        </is>
-      </c>
-      <c r="D768" s="33" t="n">
-        <v>0</v>
+      <c r="B768" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C768" s="28" t="inlineStr">
+        <is>
+          <t>cộng tác viên viết bài pr</t>
+        </is>
+      </c>
+      <c r="D768" s="29" t="n">
+        <v>10</v>
       </c>
       <c r="E768" s="37" t="inlineStr">
         <is>
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="F768" s="34" t="inlineStr">
-        <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+      <c r="F768" s="30" t="inlineStr">
+        <is>
+          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" s="27" t="n"/>
-      <c r="B769" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C769" s="32" t="inlineStr">
-        <is>
-          <t>các bài viết pr cho game học tiếng nhật</t>
-        </is>
-      </c>
-      <c r="D769" s="33" t="n">
+      <c r="B769" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C769" s="28" t="inlineStr">
+        <is>
+          <t>agency tuyển ctv viết bài pr</t>
+        </is>
+      </c>
+      <c r="D769" s="29" t="n">
         <v>0</v>
       </c>
       <c r="E769" s="37" t="inlineStr">
@@ -44062,25 +44089,25 @@
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="F769" s="34" t="inlineStr">
-        <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+      <c r="F769" s="30" t="inlineStr">
+        <is>
+          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" s="27" t="n"/>
-      <c r="B770" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C770" s="32" t="inlineStr">
-        <is>
-          <t>nhờ các facebook cá nhân viết bài pr</t>
-        </is>
-      </c>
-      <c r="D770" s="33" t="n">
+      <c r="B770" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C770" s="28" t="inlineStr">
+        <is>
+          <t>agency tuyển team viết bài pr</t>
+        </is>
+      </c>
+      <c r="D770" s="29" t="n">
         <v>0</v>
       </c>
       <c r="E770" s="37" t="inlineStr">
@@ -44088,25 +44115,25 @@
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="F770" s="34" t="inlineStr">
-        <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+      <c r="F770" s="30" t="inlineStr">
+        <is>
+          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="771">
-      <c r="A771" s="31" t="n"/>
-      <c r="B771" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C771" s="32" t="inlineStr">
-        <is>
-          <t>yêu cầu về bài pr cá nhân</t>
-        </is>
-      </c>
-      <c r="D771" s="33" t="n">
+      <c r="A771" s="27" t="n"/>
+      <c r="B771" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C771" s="28" t="inlineStr">
+        <is>
+          <t>agency tuyển viết bài pr</t>
+        </is>
+      </c>
+      <c r="D771" s="29" t="n">
         <v>0</v>
       </c>
       <c r="E771" s="37" t="inlineStr">
@@ -44114,37 +44141,33 @@
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="F771" s="34" t="inlineStr">
-        <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+      <c r="F771" s="30" t="inlineStr">
+        <is>
+          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
         </is>
       </c>
     </row>
     <row r="772">
-      <c r="A772" s="22" t="inlineStr">
-        <is>
-          <t>CTV / tuyển người viết</t>
-        </is>
-      </c>
-      <c r="B772" s="23" t="inlineStr">
-        <is>
-          <t>Từ khoá chính</t>
-        </is>
-      </c>
-      <c r="C772" s="23" t="inlineStr">
-        <is>
-          <t>ctv viết bài pr</t>
-        </is>
-      </c>
-      <c r="D772" s="24" t="n">
-        <v>10</v>
+      <c r="A772" s="27" t="n"/>
+      <c r="B772" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C772" s="28" t="inlineStr">
+        <is>
+          <t>mục đích đăng bài tuyển dụng để pr</t>
+        </is>
+      </c>
+      <c r="D772" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="E772" s="37" t="inlineStr">
         <is>
           <t>Ngoài phạm vi</t>
         </is>
       </c>
-      <c r="F772" s="26" t="inlineStr">
+      <c r="F772" s="30" t="inlineStr">
         <is>
           <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
         </is>
@@ -44159,11 +44182,11 @@
       </c>
       <c r="C773" s="28" t="inlineStr">
         <is>
-          <t>cộng tác viên viết bài pr</t>
+          <t>tuyển ctv viết bài pr</t>
         </is>
       </c>
       <c r="D773" s="29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E773" s="37" t="inlineStr">
         <is>
@@ -44185,7 +44208,7 @@
       </c>
       <c r="C774" s="28" t="inlineStr">
         <is>
-          <t>agency tuyển ctv viết bài pr</t>
+          <t>tuyển ctv viết bài pr báo chí</t>
         </is>
       </c>
       <c r="D774" s="29" t="n">
@@ -44211,7 +44234,7 @@
       </c>
       <c r="C775" s="28" t="inlineStr">
         <is>
-          <t>agency tuyển team viết bài pr</t>
+          <t>tuyển cộng tác viên viết bài pr</t>
         </is>
       </c>
       <c r="D775" s="29" t="n">
@@ -44237,7 +44260,7 @@
       </c>
       <c r="C776" s="28" t="inlineStr">
         <is>
-          <t>agency tuyển viết bài pr</t>
+          <t>tuyển người viết bài pr</t>
         </is>
       </c>
       <c r="D776" s="29" t="n">
@@ -44263,7 +44286,7 @@
       </c>
       <c r="C777" s="28" t="inlineStr">
         <is>
-          <t>mục đích đăng bài tuyển dụng để pr</t>
+          <t>tuyển nhân viên pr viết bài website</t>
         </is>
       </c>
       <c r="D777" s="29" t="n">
@@ -44289,7 +44312,7 @@
       </c>
       <c r="C778" s="28" t="inlineStr">
         <is>
-          <t>tuyển ctv viết bài pr</t>
+          <t>tuyển viết bài pr agency</t>
         </is>
       </c>
       <c r="D778" s="29" t="n">
@@ -44307,7 +44330,7 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" s="27" t="n"/>
+      <c r="A779" s="31" t="n"/>
       <c r="B779" s="28" t="inlineStr">
         <is>
           <t>—</t>
@@ -44315,7 +44338,7 @@
       </c>
       <c r="C779" s="28" t="inlineStr">
         <is>
-          <t>tuyển ctv viết bài pr báo chí</t>
+          <t>tuyển viết bài pr đăng báo</t>
         </is>
       </c>
       <c r="D779" s="29" t="n">
@@ -44333,160 +44356,160 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" s="27" t="n"/>
-      <c r="B780" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C780" s="28" t="inlineStr">
-        <is>
-          <t>tuyển cộng tác viên viết bài pr</t>
-        </is>
-      </c>
-      <c r="D780" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E780" s="37" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
-        </is>
-      </c>
-      <c r="F780" s="30" t="inlineStr">
-        <is>
-          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
+      <c r="A780" s="22" t="inlineStr">
+        <is>
+          <t>PR theo sự kiện</t>
+        </is>
+      </c>
+      <c r="B780" s="23" t="inlineStr">
+        <is>
+          <t>Từ khoá chính</t>
+        </is>
+      </c>
+      <c r="C780" s="23" t="inlineStr">
+        <is>
+          <t>viết bài pr cho sự kiện</t>
+        </is>
+      </c>
+      <c r="D780" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E780" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="F780" s="26" t="inlineStr">
+        <is>
+          <t>Mục con trong /bai-pr-mau/</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" s="27" t="n"/>
-      <c r="B781" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C781" s="28" t="inlineStr">
-        <is>
-          <t>tuyển người viết bài pr</t>
-        </is>
-      </c>
-      <c r="D781" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E781" s="37" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
-        </is>
-      </c>
-      <c r="F781" s="30" t="inlineStr">
-        <is>
-          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
+      <c r="B781" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C781" s="32" t="inlineStr">
+        <is>
+          <t>bài pr sau sự kiện</t>
+        </is>
+      </c>
+      <c r="D781" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E781" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="F781" s="34" t="inlineStr">
+        <is>
+          <t>Mục con trong /bai-pr-mau/</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" s="27" t="n"/>
-      <c r="B782" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C782" s="28" t="inlineStr">
-        <is>
-          <t>tuyển nhân viên pr viết bài website</t>
-        </is>
-      </c>
-      <c r="D782" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E782" s="37" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
-        </is>
-      </c>
-      <c r="F782" s="30" t="inlineStr">
-        <is>
-          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
+      <c r="B782" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C782" s="32" t="inlineStr">
+        <is>
+          <t>bài pr sự kiện</t>
+        </is>
+      </c>
+      <c r="D782" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E782" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="F782" s="34" t="inlineStr">
+        <is>
+          <t>Mục con trong /bai-pr-mau/</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" s="27" t="n"/>
-      <c r="B783" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C783" s="28" t="inlineStr">
-        <is>
-          <t>tuyển viết bài pr agency</t>
-        </is>
-      </c>
-      <c r="D783" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E783" s="37" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
-        </is>
-      </c>
-      <c r="F783" s="30" t="inlineStr">
-        <is>
-          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
+      <c r="B783" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C783" s="32" t="inlineStr">
+        <is>
+          <t>bài pr sự kiện về quốc tế thiếu nhi</t>
+        </is>
+      </c>
+      <c r="D783" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E783" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="F783" s="34" t="inlineStr">
+        <is>
+          <t>Mục con trong /bai-pr-mau/</t>
         </is>
       </c>
     </row>
     <row r="784">
-      <c r="A784" s="31" t="n"/>
-      <c r="B784" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C784" s="28" t="inlineStr">
-        <is>
-          <t>tuyển viết bài pr đăng báo</t>
-        </is>
-      </c>
-      <c r="D784" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E784" s="37" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi</t>
-        </is>
-      </c>
-      <c r="F784" s="30" t="inlineStr">
-        <is>
-          <t>Intent ứng tuyển, không phải khách mua dịch vụ</t>
+      <c r="A784" s="27" t="n"/>
+      <c r="B784" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C784" s="32" t="inlineStr">
+        <is>
+          <t>bài viết pr sự kiện</t>
+        </is>
+      </c>
+      <c r="D784" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E784" s="25" t="inlineStr">
+        <is>
+          <t>Đã phủ (cụm PR)</t>
+        </is>
+      </c>
+      <c r="F784" s="34" t="inlineStr">
+        <is>
+          <t>Mục con trong /bai-pr-mau/</t>
         </is>
       </c>
     </row>
     <row r="785">
-      <c r="A785" s="22" t="inlineStr">
-        <is>
-          <t>PR theo sự kiện</t>
-        </is>
-      </c>
-      <c r="B785" s="23" t="inlineStr">
-        <is>
-          <t>Từ khoá chính</t>
-        </is>
-      </c>
-      <c r="C785" s="23" t="inlineStr">
-        <is>
-          <t>viết bài pr cho sự kiện</t>
-        </is>
-      </c>
-      <c r="D785" s="24" t="n">
-        <v>10</v>
+      <c r="A785" s="27" t="n"/>
+      <c r="B785" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C785" s="32" t="inlineStr">
+        <is>
+          <t>bài viết pr sự kiện ô tô</t>
+        </is>
+      </c>
+      <c r="D785" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E785" s="25" t="inlineStr">
         <is>
           <t>Đã phủ (cụm PR)</t>
         </is>
       </c>
-      <c r="F785" s="26" t="inlineStr">
+      <c r="F785" s="34" t="inlineStr">
         <is>
           <t>Mục con trong /bai-pr-mau/</t>
         </is>
@@ -44501,7 +44524,7 @@
       </c>
       <c r="C786" s="32" t="inlineStr">
         <is>
-          <t>bài pr sau sự kiện</t>
+          <t>caác bài viết pr sự kiện</t>
         </is>
       </c>
       <c r="D786" s="33" t="n">
@@ -44527,7 +44550,7 @@
       </c>
       <c r="C787" s="32" t="inlineStr">
         <is>
-          <t>bài pr sự kiện</t>
+          <t>caách viết bài pr sự kiện</t>
         </is>
       </c>
       <c r="D787" s="33" t="n">
@@ -44553,7 +44576,7 @@
       </c>
       <c r="C788" s="32" t="inlineStr">
         <is>
-          <t>bài pr sự kiện về quốc tế thiếu nhi</t>
+          <t>các bài viết pr cho sự kiện</t>
         </is>
       </c>
       <c r="D788" s="33" t="n">
@@ -44571,7 +44594,7 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" s="27" t="n"/>
+      <c r="A789" s="31" t="n"/>
       <c r="B789" s="32" t="inlineStr">
         <is>
           <t>—</t>
@@ -44579,7 +44602,7 @@
       </c>
       <c r="C789" s="32" t="inlineStr">
         <is>
-          <t>bài viết pr sự kiện</t>
+          <t>những bài viết pr cho sự kiện ngày hội sách</t>
         </is>
       </c>
       <c r="D789" s="33" t="n">
@@ -44597,144 +44620,149 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" s="27" t="n"/>
-      <c r="B790" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C790" s="32" t="inlineStr">
-        <is>
-          <t>bài viết pr sự kiện ô tô</t>
-        </is>
-      </c>
-      <c r="D790" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E790" s="25" t="inlineStr">
-        <is>
-          <t>Đã phủ (cụm PR)</t>
-        </is>
-      </c>
-      <c r="F790" s="34" t="inlineStr">
-        <is>
-          <t>Mục con trong /bai-pr-mau/</t>
+      <c r="A790" s="22" t="inlineStr">
+        <is>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="B790" s="23" t="inlineStr">
+        <is>
+          <t>Từ khoá chính</t>
+        </is>
+      </c>
+      <c r="C790" s="23" t="inlineStr">
+        <is>
+          <t>bài pr bản thân</t>
+        </is>
+      </c>
+      <c r="D790" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E790" s="36" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="F790" s="26" t="inlineStr">
+        <is>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
     <row r="791">
       <c r="A791" s="27" t="n"/>
-      <c r="B791" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C791" s="32" t="inlineStr">
-        <is>
-          <t>caác bài viết pr sự kiện</t>
-        </is>
-      </c>
-      <c r="D791" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E791" s="25" t="inlineStr">
-        <is>
-          <t>Đã phủ (cụm PR)</t>
-        </is>
-      </c>
-      <c r="F791" s="34" t="inlineStr">
-        <is>
-          <t>Mục con trong /bai-pr-mau/</t>
+      <c r="B791" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C791" s="28" t="inlineStr">
+        <is>
+          <t>bài viết pr bản thân</t>
+        </is>
+      </c>
+      <c r="D791" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E791" s="36" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="F791" s="30" t="inlineStr">
+        <is>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" s="27" t="n"/>
-      <c r="B792" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C792" s="32" t="inlineStr">
-        <is>
-          <t>caách viết bài pr sự kiện</t>
-        </is>
-      </c>
-      <c r="D792" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E792" s="25" t="inlineStr">
-        <is>
-          <t>Đã phủ (cụm PR)</t>
-        </is>
-      </c>
-      <c r="F792" s="34" t="inlineStr">
-        <is>
-          <t>Mục con trong /bai-pr-mau/</t>
+      <c r="B792" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C792" s="28" t="inlineStr">
+        <is>
+          <t>bài viết pr về bản thân</t>
+        </is>
+      </c>
+      <c r="D792" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E792" s="36" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="F792" s="30" t="inlineStr">
+        <is>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" s="27" t="n"/>
-      <c r="B793" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C793" s="32" t="inlineStr">
-        <is>
-          <t>các bài viết pr cho sự kiện</t>
-        </is>
-      </c>
-      <c r="D793" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E793" s="25" t="inlineStr">
-        <is>
-          <t>Đã phủ (cụm PR)</t>
-        </is>
-      </c>
-      <c r="F793" s="34" t="inlineStr">
-        <is>
-          <t>Mục con trong /bai-pr-mau/</t>
+      <c r="B793" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C793" s="28" t="inlineStr">
+        <is>
+          <t>nhờ các facebook cá nhân viết bài pr</t>
+        </is>
+      </c>
+      <c r="D793" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E793" s="36" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="F793" s="30" t="inlineStr">
+        <is>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" s="31" t="n"/>
-      <c r="B794" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C794" s="32" t="inlineStr">
-        <is>
-          <t>những bài viết pr cho sự kiện ngày hội sách</t>
-        </is>
-      </c>
-      <c r="D794" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E794" s="25" t="inlineStr">
-        <is>
-          <t>Đã phủ (cụm PR)</t>
-        </is>
-      </c>
-      <c r="F794" s="34" t="inlineStr">
-        <is>
-          <t>Mục con trong /bai-pr-mau/</t>
+      <c r="B794" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C794" s="28" t="inlineStr">
+        <is>
+          <t>yêu cầu về bài pr cá nhân</t>
+        </is>
+      </c>
+      <c r="D794" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E794" s="36" t="inlineStr">
+        <is>
+          <t>Gap - mở rộng bài cluster</t>
+        </is>
+      </c>
+      <c r="F794" s="30" t="inlineStr">
+        <is>
+          <t>Đọc lại là nhu cầu booking báo để PR cho chính cá nhân (doanh nhân/chuyên gia muốn lên báo) - KHÔNG phải viết CV xin việc. Nhắc như 1 đối tượng khách trong bài mới 'Dịch vụ Viết Bài PR' (mục A) hoặc mở rộng /bai-pr-mau/, CTA về /booking-bao-pr/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A764:A771"/>
-    <mergeCell ref="A785:A794"/>
+  <mergeCells count="15">
+    <mergeCell ref="A764:A766"/>
+    <mergeCell ref="A790:A794"/>
+    <mergeCell ref="A767:A779"/>
     <mergeCell ref="A565:A690"/>
     <mergeCell ref="A332:A398"/>
     <mergeCell ref="A2:A71"/>
     <mergeCell ref="A738:A756"/>
-    <mergeCell ref="A772:A784"/>
+    <mergeCell ref="A780:A789"/>
     <mergeCell ref="A757:A763"/>
     <mergeCell ref="A72:A331"/>
     <mergeCell ref="A551:A564"/>
@@ -44771,28 +44799,28 @@
     <row r="3">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>PR bản thân / xin việc (Jiko PR)</t>
+          <t>PR bản thân - xin việc/du học Nhật (Jiko PR)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
-          <t>8 tu khoa - 20 luot/thang</t>
+          <t>3 tu khoa - 20 luot/thang</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>SERP là site tuyển dụng/du học, khác PR báo chí</t>
+          <t>Tự giới thiệu khi phỏng vấn/xin việc/du học Nhật (自己PR) hoặc game học tiếng Nhật - không liên quan báo chí/booking</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="42" t="inlineStr">
         <is>
-          <t>Vi du: bài mẫu pr bản thân bằng tiếng nhật, bài pr bản thân, bài pr bản thân bằng tiếng nhật, bài viết pr bản thân, bài viết pr về bản thân, các bài viết pr cho game học tiếng nhật, nhờ các facebook cá nhân viết bài pr, yêu cầu về bài pr cá nhân</t>
+          <t>Vi du: bài mẫu pr bản thân bằng tiếng nhật, bài pr bản thân bằng tiếng nhật, các bài viết pr cho game học tiếng nhật</t>
         </is>
       </c>
     </row>

--- a/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
+++ b/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F794"/>
+  <dimension ref="A1:F791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>gía dịch vụ viết bài pr</t>
+          <t>hợp đồng viết bài pr</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
@@ -714,7 +714,7 @@
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>báo giá dịch vụ viết bài pr</t>
+          <t>bài pr bao nhiêu tiền</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
@@ -728,7 +728,7 @@
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>báo giá viết bài pr cho sản phẩm</t>
+          <t>cần người viết bài pr</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
@@ -742,7 +742,7 @@
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>dịch vụ viết bài pr chuyên nghiệp</t>
+          <t>tìm người viết bài pr</t>
         </is>
       </c>
       <c r="F11" s="9" t="n">
@@ -756,7 +756,7 @@
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>cách đánh giá bài viết pr hiệu quả</t>
+          <t>gía dịch vụ viết bài pr</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
@@ -770,7 +770,7 @@
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>báo giá viết bài pr trên http genk.vn</t>
+          <t>tìm người viết bài pr fb</t>
         </is>
       </c>
       <c r="F13" s="9" t="n">
@@ -784,7 +784,7 @@
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài viết pr trên website cho phu nư</t>
+          <t>cần tìm người viết bài pr</t>
         </is>
       </c>
       <c r="F14" s="9" t="n">
@@ -792,13 +792,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>bảng báo giá viết bài pr trên baogiaothong.vn</t>
+          <t>báo giá dịch vụ viết bài pr</t>
         </is>
       </c>
       <c r="F15" s="9" t="n">
@@ -806,31 +806,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Có bài, cần bổ sung thêm</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>PR mẫu theo ngành (khách sạn/nhà hàng/du lịch...)</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Thêm chip-grid ngành vào /bai-pr-mau/</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>bài viết pr về du lịch</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>20</v>
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>báo giá viết bài pr cho sản phẩm</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -840,11 +826,11 @@
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nhà hàng</t>
+          <t>viết bài pr bao nhiêu tiền 1 bài</t>
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -854,11 +840,11 @@
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr khách sạn</t>
+          <t>dịch vụ viết bài pr chuyên nghiệp</t>
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -868,7 +854,7 @@
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>bài pr mỹ phẩm</t>
+          <t>cách đánh giá bài viết pr hiệu quả</t>
         </is>
       </c>
       <c r="F19" s="9" t="n">
@@ -882,7 +868,7 @@
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr nhà hàng</t>
+          <t>báo giá viết bài pr trên http genk.vn</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
@@ -896,7 +882,7 @@
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho bất động sản</t>
+          <t>báo giá bài viết pr trên website cho phu nư</t>
         </is>
       </c>
       <c r="F21" s="9" t="n">
@@ -904,13 +890,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr khách sạn mẫu</t>
+          <t>bảng báo giá viết bài pr trên baogiaothong.vn</t>
         </is>
       </c>
       <c r="F22" s="9" t="n">
@@ -918,17 +904,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>bài pr cực hay về nhà hàng</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>0</v>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Có bài, cần bổ sung thêm</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>PR mẫu theo ngành (khách sạn/nhà hàng/du lịch...)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Thêm chip-grid ngành vào /bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>bài viết pr về du lịch</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -938,11 +938,11 @@
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>vieết bài pr cho khách sạn</t>
+          <t>bài pr về nhà hàng</t>
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -952,11 +952,11 @@
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr một khu du lịch</t>
+          <t>bài viết pr khách sạn</t>
         </is>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -966,7 +966,7 @@
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài viết pr về khách sạn</t>
+          <t>bài pr mỹ phẩm</t>
         </is>
       </c>
       <c r="F26" s="9" t="n">
@@ -980,7 +980,7 @@
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>top bài pr bất động sản đặc sắc</t>
+          <t>bài viết pr nhà hàng</t>
         </is>
       </c>
       <c r="F27" s="9" t="n">
@@ -994,7 +994,7 @@
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr du lịch cần những gì</t>
+          <t>bài pr cho bất động sản</t>
         </is>
       </c>
       <c r="F28" s="9" t="n">
@@ -1008,7 +1008,7 @@
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>tiêu chí bài pr bất động sản hay</t>
+          <t>bài viết pr khách sạn mẫu</t>
         </is>
       </c>
       <c r="F29" s="9" t="n">
@@ -1022,7 +1022,7 @@
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr khu du lịch sinh thái</t>
+          <t>bài pr cực hay về nhà hàng</t>
         </is>
       </c>
       <c r="F30" s="9" t="n">
@@ -1036,7 +1036,7 @@
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr nhà hàng trên báo mạng</t>
+          <t>vieết bài pr cho khách sạn</t>
         </is>
       </c>
       <c r="F31" s="9" t="n">
@@ -1050,7 +1050,7 @@
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nhà hàng nga tại việt nam</t>
+          <t>bài viết pr một khu du lịch</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
@@ -1064,7 +1064,7 @@
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài pr bất động sản theo công thức</t>
+          <t>mẫu bài viết pr về khách sạn</t>
         </is>
       </c>
       <c r="F33" s="9" t="n">
@@ -1072,13 +1072,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>các bài pr cho một chương trình bất động sản</t>
+          <t>top bài pr bất động sản đặc sắc</t>
         </is>
       </c>
       <c r="F34" s="9" t="n">
@@ -1086,31 +1086,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Có bài, cần bổ sung thêm</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Viết bài PR chuẩn SEO</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Thêm mục vào /cach-viet-bai-pr-chuan-bao-chi/, link sang /mua-textlink/ + /dich-vu-backlink/</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>viết bài pr chuẩn seo</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>20</v>
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>bài viết pr du lịch cần những gì</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1120,11 +1106,11 @@
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr chuẩn seo</t>
+          <t>tiêu chí bài pr bất động sản hay</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1134,7 +1120,7 @@
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>dịch viết bài pr chuẩn seo</t>
+          <t>bài viết pr khu du lịch sinh thái</t>
         </is>
       </c>
       <c r="F37" s="9" t="n">
@@ -1148,7 +1134,7 @@
       <c r="D38" s="7" t="n"/>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>dịch vụ viết bài pr chuẩn seo</t>
+          <t>bài viết pr nhà hàng trên báo mạng</t>
         </is>
       </c>
       <c r="F38" s="9" t="n">
@@ -1162,7 +1148,7 @@
       <c r="D39" s="7" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>kỹ năng viết bài pr chuẩn seo</t>
+          <t>bài pr về nhà hàng nga tại việt nam</t>
         </is>
       </c>
       <c r="F39" s="9" t="n">
@@ -1176,7 +1162,7 @@
       <c r="D40" s="7" t="n"/>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>seongon checklist bài pr chuẩn seo</t>
+          <t>mẫu bài pr bất động sản theo công thức</t>
         </is>
       </c>
       <c r="F40" s="9" t="n">
@@ -1190,7 +1176,7 @@
       <c r="D41" s="10" t="n"/>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>kỹ năng viết bài pr chuẩn seo ebook</t>
+          <t>các bài pr cho một chương trình bất động sản</t>
         </is>
       </c>
       <c r="F41" s="9" t="n">
@@ -1205,24 +1191,24 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>PR cá nhân / doanh nhân qua báo chí</t>
+          <t>Viết bài PR chuẩn SEO</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>Nhắc trong bài mới 'Dịch vụ Viết Bài PR' - đối tượng doanh nhân/chuyên gia muốn lên báo</t>
+          <t>Thêm mục vào /cach-viet-bai-pr-chuan-bao-chi/, link sang /mua-textlink/ + /dich-vu-backlink/</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>bài pr bản thân</t>
+          <t>viết bài pr chuẩn seo</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1232,11 +1218,11 @@
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr bản thân</t>
+          <t>cách viết bài pr chuẩn seo</t>
         </is>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44">
@@ -1246,7 +1232,7 @@
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr về bản thân</t>
+          <t>dịch viết bài pr chuẩn seo</t>
         </is>
       </c>
       <c r="F44" s="9" t="n">
@@ -1260,7 +1246,7 @@
       <c r="D45" s="7" t="n"/>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>yêu cầu về bài pr cá nhân</t>
+          <t>dịch vụ viết bài pr chuẩn seo</t>
         </is>
       </c>
       <c r="F45" s="9" t="n">
@@ -1268,13 +1254,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>nhờ các facebook cá nhân viết bài pr</t>
+          <t>kỹ năng viết bài pr chuẩn seo</t>
         </is>
       </c>
       <c r="F46" s="9" t="n">
@@ -1282,59 +1268,59 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Cách viết bài PR / công thức</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>/cach-viet-bai-pr-chuan-bao-chi/</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>290</v>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>cấu trúc bài pr</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>30</v>
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>seongon checklist bài pr chuẩn seo</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr</t>
+          <t>kỹ năng viết bài pr chuẩn seo ebook</t>
         </is>
       </c>
       <c r="F48" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>kỹ năng viết bài pr</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>30</v>
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Có bài, cần bổ sung thêm</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>PR cá nhân / doanh nhân qua báo chí</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Nhắc trong bài mới 'Dịch vụ Viết Bài PR' - đối tượng doanh nhân/chuyên gia muốn lên báo</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>bài pr bản thân</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1344,11 +1330,11 @@
       <c r="D50" s="7" t="n"/>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>công thức viết bài pr</t>
+          <t>bài viết pr bản thân</t>
         </is>
       </c>
       <c r="F50" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1358,11 +1344,11 @@
       <c r="D51" s="7" t="n"/>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr sản phẩm</t>
+          <t>bài viết pr về bản thân</t>
         </is>
       </c>
       <c r="F51" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1372,39 +1358,53 @@
       <c r="D52" s="7" t="n"/>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho sản phẩm</t>
+          <t>yêu cầu về bài pr cá nhân</t>
         </is>
       </c>
       <c r="F52" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>nhờ các facebook cá nhân viết bài pr</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Cách viết bài PR / công thức</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>/cach-viet-bai-pr-chuan-bao-chi/</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>cấu trúc bài pr</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
         <v>30</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n"/>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>các dạng bài pr</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n"/>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>bài pr theo công thức pas</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="55">
@@ -1414,11 +1414,11 @@
       <c r="D55" s="7" t="n"/>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr theo công thức 3s</t>
+          <t>cách viết bài pr</t>
         </is>
       </c>
       <c r="F55" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -1428,11 +1428,11 @@
       <c r="D56" s="7" t="n"/>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr trên facebook</t>
+          <t>kỹ năng viết bài pr</t>
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
@@ -1442,11 +1442,11 @@
       <c r="D57" s="7" t="n"/>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho doanh nghiệp</t>
+          <t>công thức viết bài pr</t>
         </is>
       </c>
       <c r="F57" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
@@ -1456,11 +1456,11 @@
       <c r="D58" s="7" t="n"/>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr sự kiện</t>
+          <t>cách viết bài pr sản phẩm</t>
         </is>
       </c>
       <c r="F58" s="9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
@@ -1470,11 +1470,11 @@
       <c r="D59" s="7" t="n"/>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>bố cục bài pr</t>
+          <t>cách viết bài pr cho sản phẩm</t>
         </is>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
@@ -1484,11 +1484,11 @@
       <c r="D60" s="7" t="n"/>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>phân loại bài pr</t>
+          <t>các dạng bài pr</t>
         </is>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -1498,11 +1498,11 @@
       <c r="D61" s="7" t="n"/>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>bố cục một bài pr</t>
+          <t>bài pr theo công thức pas</t>
         </is>
       </c>
       <c r="F61" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -1512,11 +1512,11 @@
       <c r="D62" s="7" t="n"/>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>bố cục bài viết pr</t>
+          <t>viết bài pr theo công thức 3s</t>
         </is>
       </c>
       <c r="F62" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
@@ -1526,11 +1526,11 @@
       <c r="D63" s="7" t="n"/>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>cách viết 1 bài pr</t>
+          <t>cách viết bài pr trên facebook</t>
         </is>
       </c>
       <c r="F63" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
@@ -1540,11 +1540,11 @@
       <c r="D64" s="7" t="n"/>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>các cách viết bài pr</t>
+          <t>cách viết bài pr cho doanh nghiệp</t>
         </is>
       </c>
       <c r="F64" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -1554,11 +1554,11 @@
       <c r="D65" s="7" t="n"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>các dạng bài viết pr</t>
+          <t>cách viết bài pr sự kiện</t>
         </is>
       </c>
       <c r="F65" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -1568,7 +1568,7 @@
       <c r="D66" s="7" t="n"/>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>các loại bài viết pr</t>
+          <t>sabo bài pr</t>
         </is>
       </c>
       <c r="F66" s="9" t="n">
@@ -1582,7 +1582,7 @@
       <c r="D67" s="7" t="n"/>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài báo pr</t>
+          <t>sườn bài pr</t>
         </is>
       </c>
       <c r="F67" s="9" t="n">
@@ -1596,7 +1596,7 @@
       <c r="D68" s="7" t="n"/>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>học cách viết bài pr</t>
+          <t>bố cục bài pr</t>
         </is>
       </c>
       <c r="F68" s="9" t="n">
@@ -1610,7 +1610,7 @@
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr sách</t>
+          <t>tiêu đề bài pr</t>
         </is>
       </c>
       <c r="F69" s="9" t="n">
@@ -1624,7 +1624,7 @@
       <c r="D70" s="7" t="n"/>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr thuê</t>
+          <t>các viết bài pr</t>
         </is>
       </c>
       <c r="F70" s="9" t="n">
@@ -1638,7 +1638,7 @@
       <c r="D71" s="7" t="n"/>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>phân loại bài viết pr</t>
+          <t>học viết bài pr</t>
         </is>
       </c>
       <c r="F71" s="9" t="n">
@@ -1652,7 +1652,7 @@
       <c r="D72" s="7" t="n"/>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>cách viết 1 bài báo pr</t>
+          <t>viết kết bài pr</t>
         </is>
       </c>
       <c r="F72" s="9" t="n">
@@ -1666,7 +1666,7 @@
       <c r="D73" s="7" t="n"/>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>kỹ năng viết bài pr fb</t>
+          <t>dàn ý một bài pr</t>
         </is>
       </c>
       <c r="F73" s="9" t="n">
@@ -1680,7 +1680,7 @@
       <c r="D74" s="7" t="n"/>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>3 công thức viết bài pr</t>
+          <t>format bài pr mớ</t>
         </is>
       </c>
       <c r="F74" s="9" t="n">
@@ -1694,7 +1694,7 @@
       <c r="D75" s="7" t="n"/>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>cấu trúc của một bài pr</t>
+          <t>phân loại bài pr</t>
         </is>
       </c>
       <c r="F75" s="9" t="n">
@@ -1708,7 +1708,7 @@
       <c r="D76" s="7" t="n"/>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr công ty</t>
+          <t>văn phong bài pr</t>
         </is>
       </c>
       <c r="F76" s="9" t="n">
@@ -1722,7 +1722,7 @@
       <c r="D77" s="7" t="n"/>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr du lịch</t>
+          <t>bố cục một bài pr</t>
         </is>
       </c>
       <c r="F77" s="9" t="n">
@@ -1736,7 +1736,7 @@
       <c r="D78" s="7" t="n"/>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr dịch vụ</t>
+          <t>format bài pr mới</t>
         </is>
       </c>
       <c r="F78" s="9" t="n">
@@ -1750,7 +1750,7 @@
       <c r="D79" s="7" t="n"/>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr hấp dẫn</t>
+          <t>bố cục bài viết pr</t>
         </is>
       </c>
       <c r="F79" s="9" t="n">
@@ -1764,7 +1764,7 @@
       <c r="D80" s="7" t="n"/>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr lên báo</t>
+          <t>chủ đề viết bài pr</t>
         </is>
       </c>
       <c r="F80" s="9" t="n">
@@ -1778,7 +1778,7 @@
       <c r="D81" s="7" t="n"/>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr đèn led</t>
+          <t>cách viết 1 bài pr</t>
         </is>
       </c>
       <c r="F81" s="9" t="n">
@@ -1792,7 +1792,7 @@
       <c r="D82" s="7" t="n"/>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>các công thức viết bài pr</t>
+          <t>caách viết 1 bài pr</t>
         </is>
       </c>
       <c r="F82" s="9" t="n">
@@ -1806,7 +1806,7 @@
       <c r="D83" s="7" t="n"/>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho page</t>
+          <t>bí quyết viết bài pr</t>
         </is>
       </c>
       <c r="F83" s="9" t="n">
@@ -1820,7 +1820,7 @@
       <c r="D84" s="7" t="n"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr nhân vật</t>
+          <t>cach viet một bài pr</t>
         </is>
       </c>
       <c r="F84" s="9" t="n">
@@ -1834,7 +1834,7 @@
       <c r="D85" s="7" t="n"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr chuyên đề</t>
+          <t>caấu trúc một bài pr</t>
         </is>
       </c>
       <c r="F85" s="9" t="n">
@@ -1848,7 +1848,7 @@
       <c r="D86" s="7" t="n"/>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr khách sạn</t>
+          <t>các cách viết bài pr</t>
         </is>
       </c>
       <c r="F86" s="9" t="n">
@@ -1862,7 +1862,7 @@
       <c r="D87" s="7" t="n"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>cách viết 1 bài pr hiệu quả</t>
+          <t>các dạng bài viết pr</t>
         </is>
       </c>
       <c r="F87" s="9" t="n">
@@ -1876,7 +1876,7 @@
       <c r="D88" s="7" t="n"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>cách viết 1 bài pr sản phẩm</t>
+          <t>các loại bài viết pr</t>
         </is>
       </c>
       <c r="F88" s="9" t="n">
@@ -1890,7 +1890,7 @@
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho công ty</t>
+          <t>cách viết bài báo pr</t>
         </is>
       </c>
       <c r="F89" s="9" t="n">
@@ -1904,7 +1904,7 @@
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho mỹ phẩm</t>
+          <t>học cách viết bài pr</t>
         </is>
       </c>
       <c r="F90" s="9" t="n">
@@ -1918,7 +1918,7 @@
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho sự kiện</t>
+          <t>khóa học viết bài pr</t>
         </is>
       </c>
       <c r="F91" s="9" t="n">
@@ -1932,7 +1932,7 @@
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr pha t biê u</t>
+          <t>kỹ thuật viết bài pr</t>
         </is>
       </c>
       <c r="F92" s="9" t="n">
@@ -1946,7 +1946,7 @@
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr về sản phẩm</t>
+          <t>cách lập dàn ý bài pr</t>
         </is>
       </c>
       <c r="F93" s="9" t="n">
@@ -1960,7 +1960,7 @@
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>kỹ năng viết bài pr bán hàng</t>
+          <t>cách thức viết bài pr</t>
         </is>
       </c>
       <c r="F94" s="9" t="n">
@@ -1974,7 +1974,7 @@
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr theo công thức 3s</t>
+          <t>cách viết bài pr sách</t>
         </is>
       </c>
       <c r="F95" s="9" t="n">
@@ -1988,7 +1988,7 @@
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài truyền thông pr</t>
+          <t>cách viết bài pr thuê</t>
         </is>
       </c>
       <c r="F96" s="9" t="n">
@@ -2002,7 +2002,7 @@
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài chia sẻ pr brand</t>
+          <t>khung viết một bài pr</t>
         </is>
       </c>
       <c r="F97" s="9" t="n">
@@ -2016,7 +2016,7 @@
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>12 cách viết tiêu đề cho bài pr</t>
+          <t>phân biệt bài viết pr</t>
         </is>
       </c>
       <c r="F98" s="9" t="n">
@@ -2030,7 +2030,7 @@
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr ngược trong bds</t>
+          <t>phân loại bài viết pr</t>
         </is>
       </c>
       <c r="F99" s="9" t="n">
@@ -2044,7 +2044,7 @@
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr mỹ phẩm hiệu quả</t>
+          <t>cách viết 1 bài báo pr</t>
         </is>
       </c>
       <c r="F100" s="9" t="n">
@@ -2058,7 +2058,7 @@
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr về bệnh sỏi thận</t>
+          <t>kỹ năng viết bài pr fb</t>
         </is>
       </c>
       <c r="F101" s="9" t="n">
@@ -2072,7 +2072,7 @@
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>bài pr bất động sản theo công thức</t>
+          <t>làm sao để viết bài pr</t>
         </is>
       </c>
       <c r="F102" s="9" t="n">
@@ -2086,7 +2086,7 @@
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr theo công thức 3s</t>
+          <t>nghệ thuật viết bài pr</t>
         </is>
       </c>
       <c r="F103" s="9" t="n">
@@ -2100,7 +2100,7 @@
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho trường mầm non</t>
+          <t>nguyên tắc viết bài pr</t>
         </is>
       </c>
       <c r="F104" s="9" t="n">
@@ -2114,7 +2114,7 @@
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr dự án bất động sản</t>
+          <t>yêu cầu của một bài pr</t>
         </is>
       </c>
       <c r="F105" s="9" t="n">
@@ -2128,7 +2128,7 @@
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>cách viết một bài adaption trong pr</t>
+          <t>3 công thức viết bài pr</t>
         </is>
       </c>
       <c r="F106" s="9" t="n">
@@ -2142,7 +2142,7 @@
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr giới thiệu sản phẩm</t>
+          <t>cách thức viết 1 bài pr</t>
         </is>
       </c>
       <c r="F107" s="9" t="n">
@@ -2156,7 +2156,7 @@
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr trên facebook group</t>
+          <t>cấu trúc của một bài pr</t>
         </is>
       </c>
       <c r="F108" s="9" t="n">
@@ -2170,7 +2170,7 @@
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr trên fanpage hấp dẫn</t>
+          <t>kinh nghiệm viết bài pr</t>
         </is>
       </c>
       <c r="F109" s="9" t="n">
@@ -2184,7 +2184,7 @@
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho sản phẩm công nghệ</t>
+          <t>tiêu chí của một bài pr</t>
         </is>
       </c>
       <c r="F110" s="9" t="n">
@@ -2198,7 +2198,7 @@
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr giới thiệu về workshop</t>
+          <t>các phần của bài viết pr</t>
         </is>
       </c>
       <c r="F111" s="9" t="n">
@@ -2212,7 +2212,7 @@
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài quản cáo pr trên facebook</t>
+          <t>các thể loại bài viết pr</t>
         </is>
       </c>
       <c r="F112" s="9" t="n">
@@ -2226,7 +2226,7 @@
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr cho trung tâm ngoại ngữ</t>
+          <t>cách viết bài pr công ty</t>
         </is>
       </c>
       <c r="F113" s="9" t="n">
@@ -2240,7 +2240,7 @@
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr chương trình khuyến mãi</t>
+          <t>cách viết bài pr du lịch</t>
         </is>
       </c>
       <c r="F114" s="9" t="n">
@@ -2254,7 +2254,7 @@
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài quảng cáo pr trên facebook</t>
+          <t>cách viết bài pr dịch vụ</t>
         </is>
       </c>
       <c r="F115" s="9" t="n">
@@ -2262,13 +2262,13 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="n"/>
-      <c r="B116" s="10" t="n"/>
-      <c r="C116" s="10" t="n"/>
-      <c r="D116" s="10" t="n"/>
+      <c r="A116" s="7" t="n"/>
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>kỹ năng viết bài pr tăng doanh số bán hàng</t>
+          <t>cách viết bài pr hấp dẫn</t>
         </is>
       </c>
       <c r="F116" s="9" t="n">
@@ -2276,31 +2276,17 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>Bài PR nói chung (đuôi dài)</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>/bai-pr-la-gi/ + /cach-viet-bai-pr-chuan-bao-chi/ trả lời tổng quát</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="n">
-        <v>210</v>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>bài pr</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="n">
-        <v>110</v>
+      <c r="A117" s="7" t="n"/>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>cách viết bài pr lên báo</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2310,11 +2296,11 @@
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>bài báo pr</t>
+          <t>cách viết bài pr đèn led</t>
         </is>
       </c>
       <c r="F118" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2324,11 +2310,11 @@
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr</t>
+          <t>kỹ thuật viết bài pr pdf</t>
         </is>
       </c>
       <c r="F119" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2338,11 +2324,11 @@
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr</t>
+          <t>caách viết bài pr sự kiện</t>
         </is>
       </c>
       <c r="F120" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2352,11 +2338,11 @@
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr spa</t>
+          <t>các công thức viết bài pr</t>
         </is>
       </c>
       <c r="F121" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2366,11 +2352,11 @@
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr báo chí</t>
+          <t>cách viết bài pr cho page</t>
         </is>
       </c>
       <c r="F122" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2380,7 +2366,7 @@
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo</t>
+          <t>cách viết bài pr nhân vật</t>
         </is>
       </c>
       <c r="F123" s="9" t="n">
@@ -2394,7 +2380,7 @@
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>bài pr len</t>
+          <t>format bài pr gửi báo chí</t>
         </is>
       </c>
       <c r="F124" s="9" t="n">
@@ -2408,7 +2394,7 @@
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>các bài pr</t>
+          <t>cách viết bài pr chuyên đề</t>
         </is>
       </c>
       <c r="F125" s="9" t="n">
@@ -2422,7 +2408,7 @@
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>balo bài pr</t>
+          <t>cách viết bài pr khách sạn</t>
         </is>
       </c>
       <c r="F126" s="9" t="n">
@@ -2436,7 +2422,7 @@
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>bài đăng pr</t>
+          <t>phần mở đầu của một bài pr</t>
         </is>
       </c>
       <c r="F127" s="9" t="n">
@@ -2450,7 +2436,7 @@
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>sabo bài pr</t>
+          <t>cách viết 1 bài pr hiệu quả</t>
         </is>
       </c>
       <c r="F128" s="9" t="n">
@@ -2464,7 +2450,7 @@
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>sườn bài pr</t>
+          <t>cách viết 1 bài pr sản phẩm</t>
         </is>
       </c>
       <c r="F129" s="9" t="n">
@@ -2478,7 +2464,7 @@
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>bài pr nội bộ</t>
+          <t>caách viết bài pr về công ty</t>
         </is>
       </c>
       <c r="F130" s="9" t="n">
@@ -2492,7 +2478,7 @@
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>bài pr xe tải</t>
+          <t>cách viết bài pr cho công ty</t>
         </is>
       </c>
       <c r="F131" s="9" t="n">
@@ -2506,7 +2492,7 @@
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>bài pr đại lý</t>
+          <t>cách viết bài pr cho mỹ phẩm</t>
         </is>
       </c>
       <c r="F132" s="9" t="n">
@@ -2520,7 +2506,7 @@
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>nestle bài pr</t>
+          <t>cách viết bài pr cho sự kiện</t>
         </is>
       </c>
       <c r="F133" s="9" t="n">
@@ -2534,7 +2520,7 @@
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>bài pr 400 chữ</t>
+          <t>cách viết bài pr pha t biê u</t>
         </is>
       </c>
       <c r="F134" s="9" t="n">
@@ -2548,7 +2534,7 @@
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>bài pr ly cafe</t>
+          <t>cách viết bài pr về sản phẩm</t>
         </is>
       </c>
       <c r="F135" s="9" t="n">
@@ -2562,7 +2548,7 @@
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr fb</t>
+          <t>kỹ năng viết bài pr bán hàng</t>
         </is>
       </c>
       <c r="F136" s="9" t="n">
@@ -2576,7 +2562,7 @@
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>chapeau bài pr</t>
+          <t>bài viết pr theo công thức 3s</t>
         </is>
       </c>
       <c r="F137" s="9" t="n">
@@ -2590,7 +2576,7 @@
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>tiêu đề bài pr</t>
+          <t>cách viết bài truyền thông pr</t>
         </is>
       </c>
       <c r="F138" s="9" t="n">
@@ -2604,7 +2590,7 @@
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>adverter bài pr</t>
+          <t>mua sách kỹ thuật viết bài pr</t>
         </is>
       </c>
       <c r="F139" s="9" t="n">
@@ -2618,7 +2604,7 @@
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo chíu</t>
+          <t>cách viết bài chia sẻ pr brand</t>
         </is>
       </c>
       <c r="F140" s="9" t="n">
@@ -2632,7 +2618,7 @@
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho page</t>
+          <t>đặt tít bài pr sao cho hấp dẫn</t>
         </is>
       </c>
       <c r="F141" s="9" t="n">
@@ -2646,7 +2632,7 @@
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>bài pr lửa trại</t>
+          <t>12 cách viết tiêu đề cho bài pr</t>
         </is>
       </c>
       <c r="F142" s="9" t="n">
@@ -2660,7 +2646,7 @@
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>bài pr nhà sách</t>
+          <t>học viết bài pr marketing ở đâu</t>
         </is>
       </c>
       <c r="F143" s="9" t="n">
@@ -2674,7 +2660,7 @@
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>bài pr nhân vật</t>
+          <t>cách viết bài pr ngược trong bds</t>
         </is>
       </c>
       <c r="F144" s="9" t="n">
@@ -2688,7 +2674,7 @@
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>bài pr nước hoa</t>
+          <t>cách viết bài pr mỹ phẩm hiệu quả</t>
         </is>
       </c>
       <c r="F145" s="9" t="n">
@@ -2702,7 +2688,7 @@
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>bài pr về ca sỹ</t>
+          <t>cách viết bài pr về bệnh sỏi thận</t>
         </is>
       </c>
       <c r="F146" s="9" t="n">
@@ -2716,7 +2702,7 @@
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nội y</t>
+          <t>bài pr bất động sản theo công thức</t>
         </is>
       </c>
       <c r="F147" s="9" t="n">
@@ -2730,7 +2716,7 @@
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr hài</t>
+          <t>cách viết bài pr theo công thức 3s</t>
         </is>
       </c>
       <c r="F148" s="9" t="n">
@@ -2744,7 +2730,7 @@
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>các bài pr game</t>
+          <t>kỹ thuật viết bài pr quảng cáo pdf</t>
         </is>
       </c>
       <c r="F149" s="9" t="n">
@@ -2758,7 +2744,7 @@
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>các viết bài pr</t>
+          <t>cách viết bài pr cho trường mầm non</t>
         </is>
       </c>
       <c r="F150" s="9" t="n">
@@ -2772,7 +2758,7 @@
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>học viết bài pr</t>
+          <t>cách viết bài pr dự án bất động sản</t>
         </is>
       </c>
       <c r="F151" s="9" t="n">
@@ -2786,7 +2772,7 @@
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>phân cấp bài pr</t>
+          <t>cách viết một bài adaption trong pr</t>
         </is>
       </c>
       <c r="F152" s="9" t="n">
@@ -2800,7 +2786,7 @@
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>viết kết bài pr</t>
+          <t>nguyên tắc viết bài pr trên báo chí</t>
         </is>
       </c>
       <c r="F153" s="9" t="n">
@@ -2814,7 +2800,7 @@
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho texas</t>
+          <t>sách kỹ thuật viết bài pr quảng cáo</t>
         </is>
       </c>
       <c r="F154" s="9" t="n">
@@ -2828,7 +2814,7 @@
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>bài pr của acnes</t>
+          <t>coông thức strings trong viết bài pr</t>
         </is>
       </c>
       <c r="F155" s="9" t="n">
@@ -2842,7 +2828,7 @@
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>bài pr về dasani</t>
+          <t>cách viết bài pr giới thiệu sản phẩm</t>
         </is>
       </c>
       <c r="F156" s="9" t="n">
@@ -2856,7 +2842,7 @@
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>dàn ý một bài pr</t>
+          <t>cách viết bài pr trên facebook group</t>
         </is>
       </c>
       <c r="F157" s="9" t="n">
@@ -2870,7 +2856,7 @@
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>dđặt bài viết pr</t>
+          <t>cách viết bài pr trên fanpage hấp dẫn</t>
         </is>
       </c>
       <c r="F158" s="9" t="n">
@@ -2884,7 +2870,7 @@
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>format bài pr mớ</t>
+          <t>cách xác định giai đoạn của môt bài pr</t>
         </is>
       </c>
       <c r="F159" s="9" t="n">
@@ -2898,7 +2884,7 @@
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>nghề viết bài pr</t>
+          <t>cách viết bài pr cho sản phẩm công nghệ</t>
         </is>
       </c>
       <c r="F160" s="9" t="n">
@@ -2912,7 +2898,7 @@
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>nhận viết bài pr</t>
+          <t>cách viết bài pr giới thiệu về workshop</t>
         </is>
       </c>
       <c r="F161" s="9" t="n">
@@ -2926,7 +2912,7 @@
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr zalo</t>
+          <t>cách viết bài quản cáo pr trên facebook</t>
         </is>
       </c>
       <c r="F162" s="9" t="n">
@@ -2940,7 +2926,7 @@
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>văn phong bài pr</t>
+          <t>cách viết bài pr cho trung tâm ngoại ngữ</t>
         </is>
       </c>
       <c r="F163" s="9" t="n">
@@ -2954,7 +2940,7 @@
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>bài báo pr chuyên</t>
+          <t>cách viết bài pr chương trình khuyến mãi</t>
         </is>
       </c>
       <c r="F164" s="9" t="n">
@@ -2968,7 +2954,7 @@
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>bài pr khu đô thị</t>
+          <t>cách viết bài quảng cáo pr trên facebook</t>
         </is>
       </c>
       <c r="F165" s="9" t="n">
@@ -2982,7 +2968,7 @@
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>bài pr về công ty</t>
+          <t>kỹ năng viết bài pr tăng doanh số bán hàng</t>
         </is>
       </c>
       <c r="F166" s="9" t="n">
@@ -2990,13 +2976,13 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="7" t="n"/>
-      <c r="B167" s="7" t="n"/>
-      <c r="C167" s="7" t="n"/>
-      <c r="D167" s="7" t="n"/>
+      <c r="A167" s="10" t="n"/>
+      <c r="B167" s="10" t="n"/>
+      <c r="C167" s="10" t="n"/>
+      <c r="D167" s="10" t="n"/>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>bài pr về món nga</t>
+          <t>mô hình kim tự tháp ngược trong viết bài pr</t>
         </is>
       </c>
       <c r="F167" s="9" t="n">
@@ -3004,17 +2990,31 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="7" t="n"/>
-      <c r="B168" s="7" t="n"/>
-      <c r="C168" s="7" t="n"/>
-      <c r="D168" s="7" t="n"/>
-      <c r="E168" s="8" t="inlineStr">
-        <is>
-          <t>bài pr về trị mụn</t>
-        </is>
-      </c>
-      <c r="F168" s="9" t="n">
-        <v>0</v>
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Bài PR nói chung (đuôi dài)</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>/bai-pr-la-gi/ + /cach-viet-bai-pr-chuan-bao-chi/ trả lời tổng quát</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>bài pr</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="169">
@@ -3024,11 +3024,11 @@
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>bài viết chuẩn pr</t>
+          <t>bài báo pr</t>
         </is>
       </c>
       <c r="F169" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170">
@@ -3038,11 +3038,11 @@
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr đồ ăn</t>
+          <t>bài viết pr</t>
         </is>
       </c>
       <c r="F170" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171">
@@ -3052,11 +3052,11 @@
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>các bài pr về seo</t>
+          <t>viết bài pr</t>
         </is>
       </c>
       <c r="F171" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172">
@@ -3066,11 +3066,11 @@
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>dộ dài một bài pr</t>
+          <t>bài viết pr spa</t>
         </is>
       </c>
       <c r="F172" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
@@ -3080,11 +3080,11 @@
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>format bài pr mới</t>
+          <t>viết bài pr báo chí</t>
         </is>
       </c>
       <c r="F173" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174">
@@ -3094,7 +3094,7 @@
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr la gì</t>
+          <t>bài pr báo</t>
         </is>
       </c>
       <c r="F174" s="9" t="n">
@@ -3108,7 +3108,7 @@
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr toeic</t>
+          <t>bài pr len</t>
         </is>
       </c>
       <c r="F175" s="9" t="n">
@@ -3122,7 +3122,7 @@
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>1 pr 2 4-9 bài đọc</t>
+          <t>các bài pr</t>
         </is>
       </c>
       <c r="F176" s="9" t="n">
@@ -3136,7 +3136,7 @@
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>3 dang bài viết pr</t>
+          <t>balo bài pr</t>
         </is>
       </c>
       <c r="F177" s="9" t="n">
@@ -3150,7 +3150,7 @@
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>bài pr demographic</t>
+          <t>bài đăng pr</t>
         </is>
       </c>
       <c r="F178" s="9" t="n">
@@ -3164,7 +3164,7 @@
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>bài pr infographic</t>
+          <t>bài pr nội bộ</t>
         </is>
       </c>
       <c r="F179" s="9" t="n">
@@ -3178,7 +3178,7 @@
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>bài pr theo string</t>
+          <t>bài pr xe tải</t>
         </is>
       </c>
       <c r="F180" s="9" t="n">
@@ -3192,7 +3192,7 @@
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>bài pr trên kênh14</t>
+          <t>nestle bài pr</t>
         </is>
       </c>
       <c r="F181" s="9" t="n">
@@ -3206,7 +3206,7 @@
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>bài pr tăng cơ bắp</t>
+          <t>bài pr 400 chữ</t>
         </is>
       </c>
       <c r="F182" s="9" t="n">
@@ -3220,7 +3220,7 @@
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nhân vật</t>
+          <t>bài pr ly cafe</t>
         </is>
       </c>
       <c r="F183" s="9" t="n">
@@ -3234,7 +3234,7 @@
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nước tẩy</t>
+          <t>bài viết pr fb</t>
         </is>
       </c>
       <c r="F184" s="9" t="n">
@@ -3248,7 +3248,7 @@
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>bài pr về phân bón</t>
+          <t>chapeau bài pr</t>
         </is>
       </c>
       <c r="F185" s="9" t="n">
@@ -3262,7 +3262,7 @@
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>bài pr về tập đoàn</t>
+          <t>adverter bài pr</t>
         </is>
       </c>
       <c r="F186" s="9" t="n">
@@ -3276,7 +3276,7 @@
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>bài pr đại lý ô tô</t>
+          <t>bài pr báo chíu</t>
         </is>
       </c>
       <c r="F187" s="9" t="n">
@@ -3290,7 +3290,7 @@
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr layout</t>
+          <t>bài pr lửa trại</t>
         </is>
       </c>
       <c r="F188" s="9" t="n">
@@ -3304,7 +3304,7 @@
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>chủ đề viết bài pr</t>
+          <t>bài pr nhà sách</t>
         </is>
       </c>
       <c r="F189" s="9" t="n">
@@ -3318,7 +3318,7 @@
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>dđịnh nghĩa bài pr</t>
+          <t>bài pr nhân vật</t>
         </is>
       </c>
       <c r="F190" s="9" t="n">
@@ -3332,7 +3332,7 @@
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>gói bài pr cho seo</t>
+          <t>bài pr nước hoa</t>
         </is>
       </c>
       <c r="F191" s="9" t="n">
@@ -3346,7 +3346,7 @@
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>pr là hãng bày nào</t>
+          <t>bài viết pr hài</t>
         </is>
       </c>
       <c r="F192" s="9" t="n">
@@ -3360,7 +3360,7 @@
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr và seo</t>
+          <t>các bài pr game</t>
         </is>
       </c>
       <c r="F193" s="9" t="n">
@@ -3374,7 +3374,7 @@
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>xem số liệu bài pr</t>
+          <t>phân cấp bài pr</t>
         </is>
       </c>
       <c r="F194" s="9" t="n">
@@ -3388,7 +3388,7 @@
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>bài pr cao sao vàng</t>
+          <t>dđặt bài viết pr</t>
         </is>
       </c>
       <c r="F195" s="9" t="n">
@@ -3402,7 +3402,7 @@
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho gà texas</t>
+          <t>viết bài pr zalo</t>
         </is>
       </c>
       <c r="F196" s="9" t="n">
@@ -3416,7 +3416,7 @@
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>bài pr inforgraphic</t>
+          <t>bài báo pr chuyên</t>
         </is>
       </c>
       <c r="F197" s="9" t="n">
@@ -3430,7 +3430,7 @@
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>bài pr saigon times</t>
+          <t>bài pr khu đô thị</t>
         </is>
       </c>
       <c r="F198" s="9" t="n">
@@ -3444,7 +3444,7 @@
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>bài pr theo strings</t>
+          <t>bài viết chuẩn pr</t>
         </is>
       </c>
       <c r="F199" s="9" t="n">
@@ -3458,7 +3458,7 @@
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nutiboost</t>
+          <t>bài viết pr đồ ăn</t>
         </is>
       </c>
       <c r="F200" s="9" t="n">
@@ -3472,7 +3472,7 @@
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nước uống</t>
+          <t>dộ dài một bài pr</t>
         </is>
       </c>
       <c r="F201" s="9" t="n">
@@ -3486,7 +3486,7 @@
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr của now</t>
+          <t>viết bài pr toeic</t>
         </is>
       </c>
       <c r="F202" s="9" t="n">
@@ -3500,7 +3500,7 @@
       <c r="D203" s="7" t="n"/>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr dạy bơi</t>
+          <t>3 dang bài viết pr</t>
         </is>
       </c>
       <c r="F203" s="9" t="n">
@@ -3514,7 +3514,7 @@
       <c r="D204" s="7" t="n"/>
       <c r="E204" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr trà sữa</t>
+          <t>bài pr demographic</t>
         </is>
       </c>
       <c r="F204" s="9" t="n">
@@ -3528,7 +3528,7 @@
       <c r="D205" s="7" t="n"/>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr tôm hùm</t>
+          <t>bài pr infographic</t>
         </is>
       </c>
       <c r="F205" s="9" t="n">
@@ -3542,7 +3542,7 @@
       <c r="D206" s="7" t="n"/>
       <c r="E206" s="8" t="inlineStr">
         <is>
-          <t>caách viết 1 bài pr</t>
+          <t>bài pr theo string</t>
         </is>
       </c>
       <c r="F206" s="9" t="n">
@@ -3556,7 +3556,7 @@
       <c r="D207" s="7" t="n"/>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>các bài pr nước hoa</t>
+          <t>bài pr trên kênh14</t>
         </is>
       </c>
       <c r="F207" s="9" t="n">
@@ -3570,7 +3570,7 @@
       <c r="D208" s="7" t="n"/>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>demo bài pr báo vne</t>
+          <t>bài pr tăng cơ bắp</t>
         </is>
       </c>
       <c r="F208" s="9" t="n">
@@ -3584,7 +3584,7 @@
       <c r="D209" s="7" t="n"/>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>kế hoạch tin bài pr</t>
+          <t>bài viết pr layout</t>
         </is>
       </c>
       <c r="F209" s="9" t="n">
@@ -3598,7 +3598,7 @@
       <c r="D210" s="7" t="n"/>
       <c r="E210" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr công ty</t>
+          <t>pr là hãng bày nào</t>
         </is>
       </c>
       <c r="F210" s="9" t="n">
@@ -3612,7 +3612,7 @@
       <c r="D211" s="7" t="n"/>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>1 số bài viết pr son</t>
+          <t>viết bài pr và seo</t>
         </is>
       </c>
       <c r="F211" s="9" t="n">
@@ -3626,7 +3626,7 @@
       <c r="D212" s="7" t="n"/>
       <c r="E212" s="8" t="inlineStr">
         <is>
-          <t>box thông tin bài pr</t>
+          <t>xem số liệu bài pr</t>
         </is>
       </c>
       <c r="F212" s="9" t="n">
@@ -3640,7 +3640,7 @@
       <c r="D213" s="7" t="n"/>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr cho shop</t>
+          <t>bài pr cao sao vàng</t>
         </is>
       </c>
       <c r="F213" s="9" t="n">
@@ -3654,7 +3654,7 @@
       <c r="D214" s="7" t="n"/>
       <c r="E214" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr homestay</t>
+          <t>bài pr inforgraphic</t>
         </is>
       </c>
       <c r="F214" s="9" t="n">
@@ -3668,7 +3668,7 @@
       <c r="D215" s="7" t="n"/>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr nước hoa</t>
+          <t>bài pr saigon times</t>
         </is>
       </c>
       <c r="F215" s="9" t="n">
@@ -3682,7 +3682,7 @@
       <c r="D216" s="7" t="n"/>
       <c r="E216" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr về durex</t>
+          <t>bài pr theo strings</t>
         </is>
       </c>
       <c r="F216" s="9" t="n">
@@ -3696,7 +3696,7 @@
       <c r="D217" s="7" t="n"/>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>bí quyết viết bài pr</t>
+          <t>bài viết pr dạy bơi</t>
         </is>
       </c>
       <c r="F217" s="9" t="n">
@@ -3710,7 +3710,7 @@
       <c r="D218" s="7" t="n"/>
       <c r="E218" s="8" t="inlineStr">
         <is>
-          <t>cach viet một bài pr</t>
+          <t>bài viết pr trà sữa</t>
         </is>
       </c>
       <c r="F218" s="9" t="n">
@@ -3724,7 +3724,7 @@
       <c r="D219" s="7" t="n"/>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>caấu trúc một bài pr</t>
+          <t>bài viết pr tôm hùm</t>
         </is>
       </c>
       <c r="F219" s="9" t="n">
@@ -3738,7 +3738,7 @@
       <c r="D220" s="7" t="n"/>
       <c r="E220" s="8" t="inlineStr">
         <is>
-          <t>chiến lược đi bài pr</t>
+          <t>các bài pr nước hoa</t>
         </is>
       </c>
       <c r="F220" s="9" t="n">
@@ -3752,7 +3752,7 @@
       <c r="D221" s="7" t="n"/>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>chèn clip vào bài pr</t>
+          <t>demo bài pr báo vne</t>
         </is>
       </c>
       <c r="F221" s="9" t="n">
@@ -3766,7 +3766,7 @@
       <c r="D222" s="7" t="n"/>
       <c r="E222" s="8" t="inlineStr">
         <is>
-          <t>các hình thức bài pr</t>
+          <t>kế hoạch tin bài pr</t>
         </is>
       </c>
       <c r="F222" s="9" t="n">
@@ -3780,7 +3780,7 @@
       <c r="D223" s="7" t="n"/>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>hợp đồng viết bài pr</t>
+          <t>1 số bài viết pr son</t>
         </is>
       </c>
       <c r="F223" s="9" t="n">
@@ -3794,7 +3794,7 @@
       <c r="D224" s="7" t="n"/>
       <c r="E224" s="8" t="inlineStr">
         <is>
-          <t>khóa học viết bài pr</t>
+          <t>box thông tin bài pr</t>
         </is>
       </c>
       <c r="F224" s="9" t="n">
@@ -3808,7 +3808,7 @@
       <c r="D225" s="7" t="n"/>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>kỹ thuật viết bài pr</t>
+          <t>bài viết pr homestay</t>
         </is>
       </c>
       <c r="F225" s="9" t="n">
@@ -3822,7 +3822,7 @@
       <c r="D226" s="7" t="n"/>
       <c r="E226" s="8" t="inlineStr">
         <is>
-          <t>nghiên cứu về bài pr</t>
+          <t>bài viết pr nước hoa</t>
         </is>
       </c>
       <c r="F226" s="9" t="n">
@@ -3836,7 +3836,7 @@
       <c r="D227" s="7" t="n"/>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>vieết bài pr tại nhà</t>
+          <t>chèn clip vào bài pr</t>
         </is>
       </c>
       <c r="F227" s="9" t="n">
@@ -3850,7 +3850,7 @@
       <c r="D228" s="7" t="n"/>
       <c r="E228" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr hiệu quả</t>
+          <t>các hình thức bài pr</t>
         </is>
       </c>
       <c r="F228" s="9" t="n">
@@ -3864,7 +3864,7 @@
       <c r="D229" s="7" t="n"/>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr đăng báo</t>
+          <t>vieết bài pr tại nhà</t>
         </is>
       </c>
       <c r="F229" s="9" t="n">
@@ -3878,7 +3878,7 @@
       <c r="D230" s="7" t="n"/>
       <c r="E230" s="8" t="inlineStr">
         <is>
-          <t>xu hướng viết bài pr</t>
+          <t>viết bài pr hiệu quả</t>
         </is>
       </c>
       <c r="F230" s="9" t="n">
@@ -3892,7 +3892,7 @@
       <c r="D231" s="7" t="n"/>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>yý tưởng viết bài pr</t>
+          <t>viết bài pr đăng báo</t>
         </is>
       </c>
       <c r="F231" s="9" t="n">
@@ -3906,7 +3906,7 @@
       <c r="D232" s="7" t="n"/>
       <c r="E232" s="8" t="inlineStr">
         <is>
-          <t>bài pr bao nhiêu tiền</t>
+          <t>xu hướng viết bài pr</t>
         </is>
       </c>
       <c r="F232" s="9" t="n">
@@ -3920,7 +3920,7 @@
       <c r="D233" s="7" t="n"/>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo lecourrier</t>
+          <t>yý tưởng viết bài pr</t>
         </is>
       </c>
       <c r="F233" s="9" t="n">
@@ -3934,7 +3934,7 @@
       <c r="D234" s="7" t="n"/>
       <c r="E234" s="8" t="inlineStr">
         <is>
-          <t>bài pr kem chống nắng</t>
+          <t>bài pr báo lecourrier</t>
         </is>
       </c>
       <c r="F234" s="9" t="n">
@@ -3948,7 +3948,7 @@
       <c r="D235" s="7" t="n"/>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>bài pr tiếng anh là j</t>
+          <t>bài pr kem chống nắng</t>
         </is>
       </c>
       <c r="F235" s="9" t="n">
@@ -3962,7 +3962,7 @@
       <c r="D236" s="7" t="n"/>
       <c r="E236" s="8" t="inlineStr">
         <is>
-          <t>bài pr về nước dasani</t>
+          <t>bài pr tiếng anh là j</t>
         </is>
       </c>
       <c r="F236" s="9" t="n">
@@ -4032,7 +4032,7 @@
       <c r="D241" s="7" t="n"/>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>cách lập dàn ý bài pr</t>
+          <t>dđể viết tốt 1 bài pr</t>
         </is>
       </c>
       <c r="F241" s="9" t="n">
@@ -4046,7 +4046,7 @@
       <c r="D242" s="7" t="n"/>
       <c r="E242" s="8" t="inlineStr">
         <is>
-          <t>cách thức viết bài pr</t>
+          <t>bài học pr từ sunlight</t>
         </is>
       </c>
       <c r="F242" s="9" t="n">
@@ -4060,7 +4060,7 @@
       <c r="D243" s="7" t="n"/>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>cần người viết bài pr</t>
+          <t>bài viết pr vietnambiz</t>
         </is>
       </c>
       <c r="F243" s="9" t="n">
@@ -4074,7 +4074,7 @@
       <c r="D244" s="7" t="n"/>
       <c r="E244" s="8" t="inlineStr">
         <is>
-          <t>dđể viết tốt 1 bài pr</t>
+          <t>công cụ số liệu bài pr</t>
         </is>
       </c>
       <c r="F244" s="9" t="n">
@@ -4088,7 +4088,7 @@
       <c r="D245" s="7" t="n"/>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>khung viết một bài pr</t>
+          <t>bài pr và bài quảng cáo</t>
         </is>
       </c>
       <c r="F245" s="9" t="n">
@@ -4102,7 +4102,7 @@
       <c r="D246" s="7" t="n"/>
       <c r="E246" s="8" t="inlineStr">
         <is>
-          <t>nhân viên viết bài pr</t>
+          <t>bài viết pr marketingai</t>
         </is>
       </c>
       <c r="F246" s="9" t="n">
@@ -4116,7 +4116,7 @@
       <c r="D247" s="7" t="n"/>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>phân biệt bài viết pr</t>
+          <t>các bài viết pr strings</t>
         </is>
       </c>
       <c r="F247" s="9" t="n">
@@ -4130,7 +4130,7 @@
       <c r="D248" s="7" t="n"/>
       <c r="E248" s="8" t="inlineStr">
         <is>
-          <t>thế nào là bài báo pr</t>
+          <t>viết bài pr first sight</t>
         </is>
       </c>
       <c r="F248" s="9" t="n">
@@ -4144,7 +4144,7 @@
       <c r="D249" s="7" t="n"/>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>tìm người viết bài pr</t>
+          <t>bài biết pr cho nội thất</t>
         </is>
       </c>
       <c r="F249" s="9" t="n">
@@ -4158,7 +4158,7 @@
       <c r="D250" s="7" t="n"/>
       <c r="E250" s="8" t="inlineStr">
         <is>
-          <t>bài học pr từ sunlight</t>
+          <t>bài demographic trong pr</t>
         </is>
       </c>
       <c r="F250" s="9" t="n">
@@ -4172,7 +4172,7 @@
       <c r="D251" s="7" t="n"/>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr của now.vn</t>
+          <t>bài dịch về nhân viên pr</t>
         </is>
       </c>
       <c r="F251" s="9" t="n">
@@ -4186,7 +4186,7 @@
       <c r="D252" s="7" t="n"/>
       <c r="E252" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr vietnambiz</t>
+          <t>bài pr kem đánh răng p s</t>
         </is>
       </c>
       <c r="F252" s="9" t="n">
@@ -4200,7 +4200,7 @@
       <c r="D253" s="7" t="n"/>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr về công ty</t>
+          <t>bài pr máy lọc khí sharp</t>
         </is>
       </c>
       <c r="F253" s="9" t="n">
@@ -4214,7 +4214,7 @@
       <c r="D254" s="7" t="n"/>
       <c r="E254" s="8" t="inlineStr">
         <is>
-          <t>bài đọc 2 1 pr 3 18-22</t>
+          <t>bài pr tổng kết cuối nam</t>
         </is>
       </c>
       <c r="F254" s="9" t="n">
@@ -4228,7 +4228,7 @@
       <c r="D255" s="7" t="n"/>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>công cụ số liệu bài pr</t>
+          <t>các bài báo pr sacombank</t>
         </is>
       </c>
       <c r="F255" s="9" t="n">
@@ -4242,7 +4242,7 @@
       <c r="D256" s="7" t="n"/>
       <c r="E256" s="8" t="inlineStr">
         <is>
-          <t>freelancer viết bài pr</t>
+          <t>bài giảng pr truyền thông</t>
         </is>
       </c>
       <c r="F256" s="9" t="n">
@@ -4256,7 +4256,7 @@
       <c r="D257" s="7" t="n"/>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>làm sao để viết bài pr</t>
+          <t>bài pr budweiser trên báo</t>
         </is>
       </c>
       <c r="F257" s="9" t="n">
@@ -4270,7 +4270,7 @@
       <c r="D258" s="7" t="n"/>
       <c r="E258" s="8" t="inlineStr">
         <is>
-          <t>nghệ thuật viết bài pr</t>
+          <t>bài pr gồm những phần nào</t>
         </is>
       </c>
       <c r="F258" s="9" t="n">
@@ -4284,7 +4284,7 @@
       <c r="D259" s="7" t="n"/>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>nguyên tắc viết bài pr</t>
+          <t>bài pr trưởng ban đối nội</t>
         </is>
       </c>
       <c r="F259" s="9" t="n">
@@ -4298,7 +4298,7 @@
       <c r="D260" s="7" t="n"/>
       <c r="E260" s="8" t="inlineStr">
         <is>
-          <t>những bài pr nổi tiếng</t>
+          <t>bài viết pr sàn văn phòng</t>
         </is>
       </c>
       <c r="F260" s="9" t="n">
@@ -4312,7 +4312,7 @@
       <c r="D261" s="7" t="n"/>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>trình bày khái niệm pr</t>
+          <t>những bài pr đăng cuối năm</t>
         </is>
       </c>
       <c r="F261" s="9" t="n">
@@ -4326,7 +4326,7 @@
       <c r="D262" s="7" t="n"/>
       <c r="E262" s="8" t="inlineStr">
         <is>
-          <t>từ khóa seo cho bài pr</t>
+          <t>bài pr sách nguyễn nhật ánh</t>
         </is>
       </c>
       <c r="F262" s="9" t="n">
@@ -4340,7 +4340,7 @@
       <c r="D263" s="7" t="n"/>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr về món nga</t>
+          <t>bài viết pr do nhà báo viết</t>
         </is>
       </c>
       <c r="F263" s="9" t="n">
@@ -4354,7 +4354,7 @@
       <c r="D264" s="7" t="n"/>
       <c r="E264" s="8" t="inlineStr">
         <is>
-          <t>yêu cầu của một bài pr</t>
+          <t>hoọc anh văn để viết bài pr</t>
         </is>
       </c>
       <c r="F264" s="9" t="n">
@@ -4368,7 +4368,7 @@
       <c r="D265" s="7" t="n"/>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>bài pr và bài quảng cáo</t>
+          <t>64 từ khóa trong viết bài pr</t>
         </is>
       </c>
       <c r="F265" s="9" t="n">
@@ -4382,7 +4382,7 @@
       <c r="D266" s="7" t="n"/>
       <c r="E266" s="8" t="inlineStr">
         <is>
-          <t>bài pr về sữa nutiboost</t>
+          <t>bài pr có chèn tvc quảng cáo</t>
         </is>
       </c>
       <c r="F266" s="9" t="n">
@@ -4396,7 +4396,7 @@
       <c r="D267" s="7" t="n"/>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr marketingai</t>
+          <t>bài viết testimonal trong pr</t>
         </is>
       </c>
       <c r="F267" s="9" t="n">
@@ -4410,7 +4410,7 @@
       <c r="D268" s="7" t="n"/>
       <c r="E268" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr strings</t>
+          <t>trình bày các công cụ của pr</t>
         </is>
       </c>
       <c r="F268" s="9" t="n">
@@ -4424,7 +4424,7 @@
       <c r="D269" s="7" t="n"/>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>cách thức viết 1 bài pr</t>
+          <t>bài pr bia budweiser trên báo</t>
         </is>
       </c>
       <c r="F269" s="9" t="n">
@@ -4438,7 +4438,7 @@
       <c r="D270" s="7" t="n"/>
       <c r="E270" s="8" t="inlineStr">
         <is>
-          <t>kinh nghiệm viết bài pr</t>
+          <t>báo bài pr trên saigontourist</t>
         </is>
       </c>
       <c r="F270" s="9" t="n">
@@ -4452,7 +4452,7 @@
       <c r="D271" s="7" t="n"/>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>tiêu chí của một bài pr</t>
+          <t>nhung bài viết pr bán nhà đất</t>
         </is>
       </c>
       <c r="F271" s="9" t="n">
@@ -4466,7 +4466,7 @@
       <c r="D272" s="7" t="n"/>
       <c r="E272" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr first sight</t>
+          <t>phân tích một bài pr trên báo</t>
         </is>
       </c>
       <c r="F272" s="9" t="n">
@@ -4480,7 +4480,7 @@
       <c r="D273" s="7" t="n"/>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>bài biết pr cho nội thất</t>
+          <t>bao gia bài pr báo saigon time</t>
         </is>
       </c>
       <c r="F273" s="9" t="n">
@@ -4494,7 +4494,7 @@
       <c r="D274" s="7" t="n"/>
       <c r="E274" s="8" t="inlineStr">
         <is>
-          <t>bài demographic trong pr</t>
+          <t>bài pr báo saigon times online</t>
         </is>
       </c>
       <c r="F274" s="9" t="n">
@@ -4508,7 +4508,7 @@
       <c r="D275" s="7" t="n"/>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>bài dịch về nhân viên pr</t>
+          <t>báo bài pr trên saigon tourist</t>
         </is>
       </c>
       <c r="F275" s="9" t="n">
@@ -4522,7 +4522,7 @@
       <c r="D276" s="7" t="n"/>
       <c r="E276" s="8" t="inlineStr">
         <is>
-          <t>bài pr kem đánh răng p s</t>
+          <t>các bài pr theo kiểu editorial</t>
         </is>
       </c>
       <c r="F276" s="9" t="n">
@@ -4536,7 +4536,7 @@
       <c r="D277" s="7" t="n"/>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>bài pr máy lọc khí sharp</t>
+          <t>cách chuẩn bị bài phát biểu pr</t>
         </is>
       </c>
       <c r="F277" s="9" t="n">
@@ -4550,7 +4550,7 @@
       <c r="D278" s="7" t="n"/>
       <c r="E278" s="8" t="inlineStr">
         <is>
-          <t>bài pr tổng kết cuối nam</t>
+          <t>viết bài quảng pr cho phân bón</t>
         </is>
       </c>
       <c r="F278" s="9" t="n">
@@ -4564,7 +4564,7 @@
       <c r="D279" s="7" t="n"/>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr về nha trang</t>
+          <t>đọc &amp; phân tích các bài pr sau</t>
         </is>
       </c>
       <c r="F279" s="9" t="n">
@@ -4578,7 +4578,7 @@
       <c r="D280" s="7" t="n"/>
       <c r="E280" s="8" t="inlineStr">
         <is>
-          <t>các bài báo pr sacombank</t>
+          <t>diễn văn bài phát biểu trong pr</t>
         </is>
       </c>
       <c r="F280" s="9" t="n">
@@ -4592,7 +4592,7 @@
       <c r="D281" s="7" t="n"/>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>các phần của bài viết pr</t>
+          <t>phân biệt 1 bài báo và 1 bài pr</t>
         </is>
       </c>
       <c r="F281" s="9" t="n">
@@ -4606,7 +4606,7 @@
       <c r="D282" s="7" t="n"/>
       <c r="E282" s="8" t="inlineStr">
         <is>
-          <t>các thể loại bài viết pr</t>
+          <t>by-liner bài pr có qc chân trang</t>
         </is>
       </c>
       <c r="F282" s="9" t="n">
@@ -4620,7 +4620,7 @@
       <c r="D283" s="7" t="n"/>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>kế hoạch viết cho bài pr</t>
+          <t>xem báo giaá bài pr các báo ở đâu</t>
         </is>
       </c>
       <c r="F283" s="9" t="n">
@@ -4634,7 +4634,7 @@
       <c r="D284" s="7" t="n"/>
       <c r="E284" s="8" t="inlineStr">
         <is>
-          <t>kỹ thuật viết bài pr pdf</t>
+          <t>bài viết pr và quảng cáo khác nhau</t>
         </is>
       </c>
       <c r="F284" s="9" t="n">
@@ -4648,7 +4648,7 @@
       <c r="D285" s="7" t="n"/>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>tìm người viết bài pr fb</t>
+          <t>vieế bài pr theo cong thức strings</t>
         </is>
       </c>
       <c r="F285" s="9" t="n">
@@ -4662,7 +4662,7 @@
       <c r="D286" s="7" t="n"/>
       <c r="E286" s="8" t="inlineStr">
         <is>
-          <t>tìm việc làm viết bài pr</t>
+          <t>tìm từ khóa trên bài viết pr online</t>
         </is>
       </c>
       <c r="F286" s="9" t="n">
@@ -4676,7 +4676,7 @@
       <c r="D287" s="7" t="n"/>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>bài giảng pr truyền thông</t>
+          <t>vị trí pr bài viết trên báo điện tử</t>
         </is>
       </c>
       <c r="F287" s="9" t="n">
@@ -4690,7 +4690,7 @@
       <c r="D288" s="7" t="n"/>
       <c r="E288" s="8" t="inlineStr">
         <is>
-          <t>bài pr budweiser trên báo</t>
+          <t>bài báo pr chuyên mục tài trợ tư vấn</t>
         </is>
       </c>
       <c r="F288" s="9" t="n">
@@ -4704,7 +4704,7 @@
       <c r="D289" s="7" t="n"/>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>bài pr gồm những phần nào</t>
+          <t>bài pr trên thời báo kinh tế sài gòn</t>
         </is>
       </c>
       <c r="F289" s="9" t="n">
@@ -4718,7 +4718,7 @@
       <c r="D290" s="7" t="n"/>
       <c r="E290" s="8" t="inlineStr">
         <is>
-          <t>bài pr trưởng ban đối nội</t>
+          <t>tìm từ khóa trên bài viết pr onliine</t>
         </is>
       </c>
       <c r="F290" s="9" t="n">
@@ -4732,7 +4732,7 @@
       <c r="D291" s="7" t="n"/>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr sàn văn phòng</t>
+          <t>unica kĩ thuật viết bài pr quảng cáo</t>
         </is>
       </c>
       <c r="F291" s="9" t="n">
@@ -4746,7 +4746,7 @@
       <c r="D292" s="7" t="n"/>
       <c r="E292" s="8" t="inlineStr">
         <is>
-          <t>cần tìm người viết bài pr</t>
+          <t>viết bài pr chia sẻ lên các diễn đàn</t>
         </is>
       </c>
       <c r="F292" s="9" t="n">
@@ -4760,7 +4760,7 @@
       <c r="D293" s="7" t="n"/>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>format bài pr gửi báo chí</t>
+          <t>bài báo pr thuộc công cụ quảng cáo nào</t>
         </is>
       </c>
       <c r="F293" s="9" t="n">
@@ -4774,7 +4774,7 @@
       <c r="D294" s="7" t="n"/>
       <c r="E294" s="8" t="inlineStr">
         <is>
-          <t>những bài pr nổi tiếng fb</t>
+          <t>bài pr aroma resort trên dântrí bị xóa</t>
         </is>
       </c>
       <c r="F294" s="9" t="n">
@@ -4788,7 +4788,7 @@
       <c r="D295" s="7" t="n"/>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho cảng biển</t>
+          <t>caác bài phát biểu trong chiến dịch pr</t>
         </is>
       </c>
       <c r="F295" s="9" t="n">
@@ -4802,7 +4802,7 @@
       <c r="D296" s="7" t="n"/>
       <c r="E296" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr công ty honda</t>
+          <t>bài viết cho báo chí và bài viết cho pr</t>
         </is>
       </c>
       <c r="F296" s="9" t="n">
@@ -4816,7 +4816,7 @@
       <c r="D297" s="7" t="n"/>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>neên đi bài pr như thế nào</t>
+          <t>cách trình bày campaign trong báo cáo pr</t>
         </is>
       </c>
       <c r="F297" s="9" t="n">
@@ -4824,13 +4824,13 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="7" t="n"/>
-      <c r="B298" s="7" t="n"/>
-      <c r="C298" s="7" t="n"/>
-      <c r="D298" s="7" t="n"/>
+      <c r="A298" s="10" t="n"/>
+      <c r="B298" s="10" t="n"/>
+      <c r="C298" s="10" t="n"/>
+      <c r="D298" s="10" t="n"/>
       <c r="E298" s="8" t="inlineStr">
         <is>
-          <t>những bài pr đăng cuối năm</t>
+          <t>bài pr trên báo giúp tăng uy tín trên google</t>
         </is>
       </c>
       <c r="F298" s="9" t="n">
@@ -4838,17 +4838,31 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="7" t="n"/>
-      <c r="B299" s="7" t="n"/>
-      <c r="C299" s="7" t="n"/>
-      <c r="D299" s="7" t="n"/>
-      <c r="E299" s="8" t="inlineStr">
-        <is>
-          <t>phần mở đầu của một bài pr</t>
-        </is>
-      </c>
-      <c r="F299" s="9" t="n">
-        <v>0</v>
+      <c r="A299" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>Bài PR mẫu / ví dụ</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>/bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="D299" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>bài pr mẫu</t>
+        </is>
+      </c>
+      <c r="F299" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="300">
@@ -4858,11 +4872,11 @@
       <c r="D300" s="7" t="n"/>
       <c r="E300" s="8" t="inlineStr">
         <is>
-          <t>bài báo pr về sàn văn phòng</t>
+          <t>bài pr hay</t>
         </is>
       </c>
       <c r="F300" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="301">
@@ -4872,11 +4886,11 @@
       <c r="D301" s="7" t="n"/>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>bài pr sách nguyễn nhật ánh</t>
+          <t>các bài pr mẫu</t>
         </is>
       </c>
       <c r="F301" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="302">
@@ -4886,11 +4900,11 @@
       <c r="D302" s="7" t="n"/>
       <c r="E302" s="8" t="inlineStr">
         <is>
-          <t>bài pr về digital marketing</t>
+          <t>những bài pr hay</t>
         </is>
       </c>
       <c r="F302" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="303">
@@ -4900,11 +4914,11 @@
       <c r="D303" s="7" t="n"/>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr do nhà báo viết</t>
+          <t>những mẫu bài pr hay</t>
         </is>
       </c>
       <c r="F303" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="304">
@@ -4914,11 +4928,11 @@
       <c r="D304" s="7" t="n"/>
       <c r="E304" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr về rong nho</t>
+          <t>mẫu bài viết pr sự kiện</t>
         </is>
       </c>
       <c r="F304" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="305">
@@ -4928,11 +4942,11 @@
       <c r="D305" s="7" t="n"/>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>hoọc anh văn để viết bài pr</t>
+          <t>những bài viết pr sản phẩm hay</t>
         </is>
       </c>
       <c r="F305" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="306">
@@ -4942,11 +4956,11 @@
       <c r="D306" s="7" t="n"/>
       <c r="E306" s="8" t="inlineStr">
         <is>
-          <t>quy cách đi bài pr trên báo</t>
+          <t>các bài pr hay</t>
         </is>
       </c>
       <c r="F306" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="307">
@@ -4956,11 +4970,11 @@
       <c r="D307" s="7" t="n"/>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho studio cưới</t>
+          <t>bài viết pr mẫu</t>
         </is>
       </c>
       <c r="F307" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="308">
@@ -4970,11 +4984,11 @@
       <c r="D308" s="7" t="n"/>
       <c r="E308" s="8" t="inlineStr">
         <is>
-          <t>64 từ khóa trong viết bài pr</t>
+          <t>mẫu bài pr sản phẩm</t>
         </is>
       </c>
       <c r="F308" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="309">
@@ -4984,7 +4998,7 @@
       <c r="D309" s="7" t="n"/>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>bài pr có chèn tvc quảng cáo</t>
+          <t>bài mẫu pr</t>
         </is>
       </c>
       <c r="F309" s="9" t="n">
@@ -4998,7 +5012,7 @@
       <c r="D310" s="7" t="n"/>
       <c r="E310" s="8" t="inlineStr">
         <is>
-          <t>bài viết testimonal trong pr</t>
+          <t>mẫu 1 bài pr</t>
         </is>
       </c>
       <c r="F310" s="9" t="n">
@@ -5012,7 +5026,7 @@
       <c r="D311" s="7" t="n"/>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>caách viết bài pr về công ty</t>
+          <t>ví dụ bài pr</t>
         </is>
       </c>
       <c r="F311" s="9" t="n">
@@ -5026,7 +5040,7 @@
       <c r="D312" s="7" t="n"/>
       <c r="E312" s="8" t="inlineStr">
         <is>
-          <t>trình bày các công cụ của pr</t>
+          <t>mẫu bài pr hay</t>
         </is>
       </c>
       <c r="F312" s="9" t="n">
@@ -5040,7 +5054,7 @@
       <c r="D313" s="7" t="n"/>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>vieết bài pr sao cho thu hút</t>
+          <t>bài viết pr hay</t>
         </is>
       </c>
       <c r="F313" s="9" t="n">
@@ -5054,7 +5068,7 @@
       <c r="D314" s="7" t="n"/>
       <c r="E314" s="8" t="inlineStr">
         <is>
-          <t>bài pr bia budweiser trên báo</t>
+          <t>mẫu bài pr xe tải</t>
         </is>
       </c>
       <c r="F314" s="9" t="n">
@@ -5068,7 +5082,7 @@
       <c r="D315" s="7" t="n"/>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>báo bài pr trên saigontourist</t>
+          <t>một số bài pr hay</t>
         </is>
       </c>
       <c r="F315" s="9" t="n">
@@ -5082,7 +5096,7 @@
       <c r="D316" s="7" t="n"/>
       <c r="E316" s="8" t="inlineStr">
         <is>
-          <t>mua sách kỹ thuật viết bài pr</t>
+          <t>một số bài pr mẫu</t>
         </is>
       </c>
       <c r="F316" s="9" t="n">
@@ -5096,7 +5110,7 @@
       <c r="D317" s="7" t="n"/>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>nhung bài viết pr bán nhà đất</t>
+          <t>bài mẫu pr sự kiện</t>
         </is>
       </c>
       <c r="F317" s="9" t="n">
@@ -5110,7 +5124,7 @@
       <c r="D318" s="7" t="n"/>
       <c r="E318" s="8" t="inlineStr">
         <is>
-          <t>phân tích một bài pr trên báo</t>
+          <t>các bài pr pas mẫu</t>
         </is>
       </c>
       <c r="F318" s="9" t="n">
@@ -5124,7 +5138,7 @@
       <c r="D319" s="7" t="n"/>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>bao gia bài pr báo saigon time</t>
+          <t>bài pr nhân vật hay</t>
         </is>
       </c>
       <c r="F319" s="9" t="n">
@@ -5138,7 +5152,7 @@
       <c r="D320" s="7" t="n"/>
       <c r="E320" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo saigon times online</t>
+          <t>bài pr sản phẩm hay</t>
         </is>
       </c>
       <c r="F320" s="9" t="n">
@@ -5152,7 +5166,7 @@
       <c r="D321" s="7" t="n"/>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho trang sức kim cương</t>
+          <t>bài pr sản phẩm mẫu</t>
         </is>
       </c>
       <c r="F321" s="9" t="n">
@@ -5166,7 +5180,7 @@
       <c r="D322" s="7" t="n"/>
       <c r="E322" s="8" t="inlineStr">
         <is>
-          <t>báo bài pr trên saigon tourist</t>
+          <t>một bài pr ấn tượng</t>
         </is>
       </c>
       <c r="F322" s="9" t="n">
@@ -5180,7 +5194,7 @@
       <c r="D323" s="7" t="n"/>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>các bài pr theo kiểu editorial</t>
+          <t>cách viết bài pr hay</t>
         </is>
       </c>
       <c r="F323" s="9" t="n">
@@ -5194,7 +5208,7 @@
       <c r="D324" s="7" t="n"/>
       <c r="E324" s="8" t="inlineStr">
         <is>
-          <t>cách chuẩn bị bài phát biểu pr</t>
+          <t>mẫu bài pr theo aida</t>
         </is>
       </c>
       <c r="F324" s="9" t="n">
@@ -5208,7 +5222,7 @@
       <c r="D325" s="7" t="n"/>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr công ty với 200 từ</t>
+          <t>những bài pr pas mẫu</t>
         </is>
       </c>
       <c r="F325" s="9" t="n">
@@ -5222,7 +5236,7 @@
       <c r="D326" s="7" t="n"/>
       <c r="E326" s="8" t="inlineStr">
         <is>
-          <t>viết bài quảng pr cho phân bón</t>
+          <t>bài mẫu pr về món nga</t>
         </is>
       </c>
       <c r="F326" s="9" t="n">
@@ -5236,7 +5250,7 @@
       <c r="D327" s="7" t="n"/>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>đặt tít bài pr sao cho hấp dẫn</t>
+          <t>bài pr mẫu về công ty</t>
         </is>
       </c>
       <c r="F327" s="9" t="n">
@@ -5250,7 +5264,7 @@
       <c r="D328" s="7" t="n"/>
       <c r="E328" s="8" t="inlineStr">
         <is>
-          <t>đọc &amp; phân tích các bài pr sau</t>
+          <t>bài pr nhà hangfd hay</t>
         </is>
       </c>
       <c r="F328" s="9" t="n">
@@ -5264,7 +5278,7 @@
       <c r="D329" s="7" t="n"/>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr branding cho bán lẻ</t>
+          <t>những bài pr game hay</t>
         </is>
       </c>
       <c r="F329" s="9" t="n">
@@ -5278,7 +5292,7 @@
       <c r="D330" s="7" t="n"/>
       <c r="E330" s="8" t="inlineStr">
         <is>
-          <t>caác bài pr cho dầu gội trị gàu</t>
+          <t>những bài pr hay nhất</t>
         </is>
       </c>
       <c r="F330" s="9" t="n">
@@ -5292,7 +5306,7 @@
       <c r="D331" s="7" t="n"/>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>diễn văn bài phát biểu trong pr</t>
+          <t>những bài viết pr hay</t>
         </is>
       </c>
       <c r="F331" s="9" t="n">
@@ -5306,7 +5320,7 @@
       <c r="D332" s="7" t="n"/>
       <c r="E332" s="8" t="inlineStr">
         <is>
-          <t>học viết bài pr marketing ở đâu</t>
+          <t>bài pr mẫu về nhân vật</t>
         </is>
       </c>
       <c r="F332" s="9" t="n">
@@ -5320,7 +5334,7 @@
       <c r="D333" s="7" t="n"/>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>phân biệt 1 bài báo và 1 bài pr</t>
+          <t>bài viết pr mẫu xe hơi</t>
         </is>
       </c>
       <c r="F333" s="9" t="n">
@@ -5334,7 +5348,7 @@
       <c r="D334" s="7" t="n"/>
       <c r="E334" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr về địa điểm tổ chức</t>
+          <t>các bài pr sự kiện mẫu</t>
         </is>
       </c>
       <c r="F334" s="9" t="n">
@@ -5348,7 +5362,7 @@
       <c r="D335" s="7" t="n"/>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>by-liner bài pr có qc chân trang</t>
+          <t>mẫu bài pr cho sự kiện</t>
         </is>
       </c>
       <c r="F335" s="9" t="n">
@@ -5362,7 +5376,7 @@
       <c r="D336" s="7" t="n"/>
       <c r="E336" s="8" t="inlineStr">
         <is>
-          <t>bài pr của kols viết như thế nào</t>
+          <t>những bài pr nổi tiếng</t>
         </is>
       </c>
       <c r="F336" s="9" t="n">
@@ -5376,7 +5390,7 @@
       <c r="D337" s="7" t="n"/>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>caácc bài pr cho dầu gội trị gàu</t>
+          <t>cách tạo một bài pr hay</t>
         </is>
       </c>
       <c r="F337" s="9" t="n">
@@ -5390,7 +5404,7 @@
       <c r="D338" s="7" t="n"/>
       <c r="E338" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr bao nhiêu tiền 1 bài</t>
+          <t>bài viết pr sản phẩm mẫu</t>
         </is>
       </c>
       <c r="F338" s="9" t="n">
@@ -5404,7 +5418,7 @@
       <c r="D339" s="7" t="n"/>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr cho muối tôm tây ninh</t>
+          <t>các bài phỏng pr vấn mẫu</t>
         </is>
       </c>
       <c r="F339" s="9" t="n">
@@ -5418,7 +5432,7 @@
       <c r="D340" s="7" t="n"/>
       <c r="E340" s="8" t="inlineStr">
         <is>
-          <t>xem báo giaá bài pr các báo ở đâu</t>
+          <t>mẫu bài viết pr sản phẩm</t>
         </is>
       </c>
       <c r="F340" s="9" t="n">
@@ -5432,7 +5446,7 @@
       <c r="D341" s="7" t="n"/>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr và quảng cáo khác nhau</t>
+          <t>một số bài pr mẫu sự kiện</t>
         </is>
       </c>
       <c r="F341" s="9" t="n">
@@ -5446,7 +5460,7 @@
       <c r="D342" s="7" t="n"/>
       <c r="E342" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr về đồ nội thất cao cấp</t>
+          <t>những bài pr nổi tiếng fb</t>
         </is>
       </c>
       <c r="F342" s="9" t="n">
@@ -5460,7 +5474,7 @@
       <c r="D343" s="7" t="n"/>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr về bác sĩ hàn quốc</t>
+          <t>những bài viết pr hay nhất</t>
         </is>
       </c>
       <c r="F343" s="9" t="n">
@@ -5474,7 +5488,7 @@
       <c r="D344" s="7" t="n"/>
       <c r="E344" s="8" t="inlineStr">
         <is>
-          <t>cơ sở lý thuyết về bài pr của kols</t>
+          <t>bài viết pr về sản phẩm hay</t>
         </is>
       </c>
       <c r="F344" s="9" t="n">
@@ -5488,7 +5502,7 @@
       <c r="D345" s="7" t="n"/>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>kỹ thuật viết bài pr quảng cáo pdf</t>
+          <t>các bài pr hay về dược phẩm</t>
         </is>
       </c>
       <c r="F345" s="9" t="n">
@@ -5502,7 +5516,7 @@
       <c r="D346" s="7" t="n"/>
       <c r="E346" s="8" t="inlineStr">
         <is>
-          <t>vieế bài pr theo cong thức strings</t>
+          <t>ví dụ các bài pr về món nga</t>
         </is>
       </c>
       <c r="F346" s="9" t="n">
@@ -5516,7 +5530,7 @@
       <c r="D347" s="7" t="n"/>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho phụ gia ngành giấy</t>
+          <t>các bài viết pr sản phẩm hay</t>
         </is>
       </c>
       <c r="F347" s="9" t="n">
@@ -5530,7 +5544,7 @@
       <c r="D348" s="7" t="n"/>
       <c r="E348" s="8" t="inlineStr">
         <is>
-          <t>nguyên tắc viết bài pr trên báo chí</t>
+          <t>cách giật tít hay cho bài pr</t>
         </is>
       </c>
       <c r="F348" s="9" t="n">
@@ -5544,7 +5558,7 @@
       <c r="D349" s="7" t="n"/>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>những bài viết pr cho ngày hội sách</t>
+          <t>bài pr mẫu theo công thức pas</t>
         </is>
       </c>
       <c r="F349" s="9" t="n">
@@ -5558,7 +5572,7 @@
       <c r="D350" s="7" t="n"/>
       <c r="E350" s="8" t="inlineStr">
         <is>
-          <t>sách kỹ thuật viết bài pr quảng cáo</t>
+          <t>caách giật tít hay cho bài pr</t>
         </is>
       </c>
       <c r="F350" s="9" t="n">
@@ -5572,7 +5586,7 @@
       <c r="D351" s="7" t="n"/>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>tìm từ khóa trên bài viết pr online</t>
+          <t>cách viết bài pr sản phẩm hay</t>
         </is>
       </c>
       <c r="F351" s="9" t="n">
@@ -5586,7 +5600,7 @@
       <c r="D352" s="7" t="n"/>
       <c r="E352" s="8" t="inlineStr">
         <is>
-          <t>vị trí pr bài viết trên báo điện tử</t>
+          <t>những bài viết pr về shop hay</t>
         </is>
       </c>
       <c r="F352" s="9" t="n">
@@ -5600,7 +5614,7 @@
       <c r="D353" s="7" t="n"/>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>xác định công chúng của bài viết pr</t>
+          <t>mẫu bài pr theo công thức aida</t>
         </is>
       </c>
       <c r="F353" s="9" t="n">
@@ -5614,7 +5628,7 @@
       <c r="D354" s="7" t="n"/>
       <c r="E354" s="8" t="inlineStr">
         <is>
-          <t>xây dựng thông điệp của bài viết pr</t>
+          <t>những bài pr hầm rượu vang hay</t>
         </is>
       </c>
       <c r="F354" s="9" t="n">
@@ -5628,7 +5642,7 @@
       <c r="D355" s="7" t="n"/>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>bài báo pr chuyên mục tài trợ tư vấn</t>
+          <t>tập hợp các bài viết hay về pr</t>
         </is>
       </c>
       <c r="F355" s="9" t="n">
@@ -5642,7 +5656,7 @@
       <c r="D356" s="7" t="n"/>
       <c r="E356" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho công ty thiết kế nội thất</t>
+          <t>bài pr mẫu của tổ chức giáo dục</t>
         </is>
       </c>
       <c r="F356" s="9" t="n">
@@ -5656,7 +5670,7 @@
       <c r="D357" s="7" t="n"/>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>bài pr trên thời báo kinh tế sài gòn</t>
+          <t>ví dụ các công thức viết bài pr</t>
         </is>
       </c>
       <c r="F357" s="9" t="n">
@@ -5670,7 +5684,7 @@
       <c r="D358" s="7" t="n"/>
       <c r="E358" s="8" t="inlineStr">
         <is>
-          <t>coông thức strings trong viết bài pr</t>
+          <t>các nhân vật viết pr bài viết hay</t>
         </is>
       </c>
       <c r="F358" s="9" t="n">
@@ -5684,7 +5698,7 @@
       <c r="D359" s="7" t="n"/>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>tìm từ khóa trên bài viết pr onliine</t>
+          <t>nhung bài viết pr bán nhà đất hay</t>
         </is>
       </c>
       <c r="F359" s="9" t="n">
@@ -5698,7 +5712,7 @@
       <c r="D360" s="7" t="n"/>
       <c r="E360" s="8" t="inlineStr">
         <is>
-          <t>unica kĩ thuật viết bài pr quảng cáo</t>
+          <t>tham khảo các mẫu bài pr đỉnh cao</t>
         </is>
       </c>
       <c r="F360" s="9" t="n">
@@ -5712,7 +5726,7 @@
       <c r="D361" s="7" t="n"/>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr chia sẻ lên các diễn đàn</t>
+          <t>các facebooer viết pr bài viết hay</t>
         </is>
       </c>
       <c r="F361" s="9" t="n">
@@ -5726,7 +5740,7 @@
       <c r="D362" s="7" t="n"/>
       <c r="E362" s="8" t="inlineStr">
         <is>
-          <t>bài pr về bộ phận chăm sóc khách hàng</t>
+          <t>các facebooker viết pr bài viết hay</t>
         </is>
       </c>
       <c r="F362" s="9" t="n">
@@ -5740,7 +5754,7 @@
       <c r="D363" s="7" t="n"/>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr quyên góp áo trắng cho em</t>
+          <t>đặt tít hay cho bài pr sản phẩm sơn</t>
         </is>
       </c>
       <c r="F363" s="9" t="n">
@@ -5754,7 +5768,7 @@
       <c r="D364" s="7" t="n"/>
       <c r="E364" s="8" t="inlineStr">
         <is>
-          <t>lượt view trung bình cho bài pr hieeu</t>
+          <t>một bài pr mẫu cho ra mắt sản phẩm mới</t>
         </is>
       </c>
       <c r="F364" s="9" t="n">
@@ -5768,7 +5782,7 @@
       <c r="D365" s="7" t="n"/>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>bài báo pr thuộc công cụ quảng cáo nào</t>
+          <t>cách nhận biết baì pr hay bài marketing</t>
         </is>
       </c>
       <c r="F365" s="9" t="n">
@@ -5782,7 +5796,7 @@
       <c r="D366" s="7" t="n"/>
       <c r="E366" s="8" t="inlineStr">
         <is>
-          <t>bài pr aroma resort trên dântrí bị xóa</t>
+          <t>ví dụ các công thức viết bài pr facebook</t>
         </is>
       </c>
       <c r="F366" s="9" t="n">
@@ -5790,13 +5804,13 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="7" t="n"/>
-      <c r="B367" s="7" t="n"/>
-      <c r="C367" s="7" t="n"/>
-      <c r="D367" s="7" t="n"/>
+      <c r="A367" s="10" t="n"/>
+      <c r="B367" s="10" t="n"/>
+      <c r="C367" s="10" t="n"/>
+      <c r="D367" s="10" t="n"/>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>caác bài phát biểu trong chiến dịch pr</t>
+          <t>các facebooker viết pr bài viết hay nổi tiếng</t>
         </is>
       </c>
       <c r="F367" s="9" t="n">
@@ -5804,17 +5818,31 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="7" t="n"/>
-      <c r="B368" s="7" t="n"/>
-      <c r="C368" s="7" t="n"/>
-      <c r="D368" s="7" t="n"/>
-      <c r="E368" s="8" t="inlineStr">
-        <is>
-          <t>cách xác định giai đoạn của môt bài pr</t>
-        </is>
-      </c>
-      <c r="F368" s="9" t="n">
-        <v>0</v>
+      <c r="A368" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>Báo giá theo đầu báo cụ thể</t>
+        </is>
+      </c>
+      <c r="C368" s="3" t="inlineStr">
+        <is>
+          <t>15 trang /book-bao-*/ + /booking-bao-pr/</t>
+        </is>
+      </c>
+      <c r="D368" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="E368" s="5" t="inlineStr">
+        <is>
+          <t>báo giá bài pr vnexpress</t>
+        </is>
+      </c>
+      <c r="F368" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="369">
@@ -5824,11 +5852,11 @@
       <c r="D369" s="7" t="n"/>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>bài viết cho báo chí và bài viết cho pr</t>
+          <t>báo giá đăng bài pr trên kenh14</t>
         </is>
       </c>
       <c r="F369" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="370">
@@ -5838,11 +5866,11 @@
       <c r="D370" s="7" t="n"/>
       <c r="E370" s="8" t="inlineStr">
         <is>
-          <t>caác bài viết pr cho các dầu gội trị gàu</t>
+          <t>báo giá bài pr 24h</t>
         </is>
       </c>
       <c r="F370" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="371">
@@ -5852,11 +5880,11 @@
       <c r="D371" s="7" t="n"/>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>cách trình bày campaign trong báo cáo pr</t>
+          <t>báo giá bài pr cafef</t>
         </is>
       </c>
       <c r="F371" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="372">
@@ -5866,11 +5894,11 @@
       <c r="D372" s="7" t="n"/>
       <c r="E372" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr món ăn cho người mới bắt đầu</t>
+          <t>báo giá bài pr kenh14</t>
         </is>
       </c>
       <c r="F372" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="373">
@@ -5880,11 +5908,11 @@
       <c r="D373" s="7" t="n"/>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>những bài viết pr cho trung tâm tiếng anh</t>
+          <t>báo giá bài pr vietnamnet</t>
         </is>
       </c>
       <c r="F373" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="374">
@@ -5894,11 +5922,11 @@
       <c r="D374" s="7" t="n"/>
       <c r="E374" s="8" t="inlineStr">
         <is>
-          <t>mô hình kim tự tháp ngược trong viết bài pr</t>
+          <t>báo giá bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F374" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="375">
@@ -5908,53 +5936,39 @@
       <c r="D375" s="7" t="n"/>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>bài pr trên báo giúp tăng uy tín trên google</t>
+          <t>báo giá đăng bài pr trên kênh 14</t>
         </is>
       </c>
       <c r="F375" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="10" t="n"/>
-      <c r="B376" s="10" t="n"/>
-      <c r="C376" s="10" t="n"/>
-      <c r="D376" s="10" t="n"/>
+      <c r="A376" s="7" t="n"/>
+      <c r="B376" s="7" t="n"/>
+      <c r="C376" s="7" t="n"/>
+      <c r="D376" s="7" t="n"/>
       <c r="E376" s="8" t="inlineStr">
         <is>
-          <t>toplist.vn là trang web viết các bài pr lừa đảo</t>
+          <t>báo giá đăng bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F376" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B377" s="3" t="inlineStr">
-        <is>
-          <t>Bài PR mẫu / ví dụ</t>
-        </is>
-      </c>
-      <c r="C377" s="3" t="inlineStr">
-        <is>
-          <t>/bai-pr-mau/</t>
-        </is>
-      </c>
-      <c r="D377" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="E377" s="5" t="inlineStr">
-        <is>
-          <t>bài pr mẫu</t>
-        </is>
-      </c>
-      <c r="F377" s="6" t="n">
-        <v>30</v>
+      <c r="A377" s="7" t="n"/>
+      <c r="B377" s="7" t="n"/>
+      <c r="C377" s="7" t="n"/>
+      <c r="D377" s="7" t="n"/>
+      <c r="E377" s="8" t="inlineStr">
+        <is>
+          <t>bài pr zing</t>
+        </is>
+      </c>
+      <c r="F377" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -5964,11 +5978,11 @@
       <c r="D378" s="7" t="n"/>
       <c r="E378" s="8" t="inlineStr">
         <is>
-          <t>bài pr hay</t>
+          <t>bài pr cafef</t>
         </is>
       </c>
       <c r="F378" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -5978,11 +5992,11 @@
       <c r="D379" s="7" t="n"/>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>các bài pr mẫu</t>
+          <t>cafef bài pr</t>
         </is>
       </c>
       <c r="F379" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -5992,11 +6006,11 @@
       <c r="D380" s="7" t="n"/>
       <c r="E380" s="8" t="inlineStr">
         <is>
-          <t>những bài pr hay</t>
+          <t>bài pr kenh14</t>
         </is>
       </c>
       <c r="F380" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -6006,11 +6020,11 @@
       <c r="D381" s="7" t="n"/>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>những mẫu bài pr hay</t>
+          <t>bài pr dân trí</t>
         </is>
       </c>
       <c r="F381" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -6020,11 +6034,11 @@
       <c r="D382" s="7" t="n"/>
       <c r="E382" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài viết pr sự kiện</t>
+          <t>bài pr ngoisao</t>
         </is>
       </c>
       <c r="F382" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -6034,11 +6048,11 @@
       <c r="D383" s="7" t="n"/>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>những bài viết pr sản phẩm hay</t>
+          <t>cafef bài pr giá</t>
         </is>
       </c>
       <c r="F383" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -6048,11 +6062,11 @@
       <c r="D384" s="7" t="n"/>
       <c r="E384" s="8" t="inlineStr">
         <is>
-          <t>các bài pr hay</t>
+          <t>bài pr thanh niên</t>
         </is>
       </c>
       <c r="F384" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -6062,11 +6076,11 @@
       <c r="D385" s="7" t="n"/>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr mẫu</t>
+          <t>giá bài pr forbes</t>
         </is>
       </c>
       <c r="F385" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -6076,11 +6090,11 @@
       <c r="D386" s="7" t="n"/>
       <c r="E386" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài pr sản phẩm</t>
+          <t>lên bài pr baomoi</t>
         </is>
       </c>
       <c r="F386" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -6090,7 +6104,7 @@
       <c r="D387" s="7" t="n"/>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>bài mẫu pr</t>
+          <t>bài pr ngoisao.net</t>
         </is>
       </c>
       <c r="F387" s="9" t="n">
@@ -6104,7 +6118,7 @@
       <c r="D388" s="7" t="n"/>
       <c r="E388" s="8" t="inlineStr">
         <is>
-          <t>mẫu 1 bài pr</t>
+          <t>báo giá bài pr voh</t>
         </is>
       </c>
       <c r="F388" s="9" t="n">
@@ -6118,7 +6132,7 @@
       <c r="D389" s="7" t="n"/>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>ví dụ bài pr</t>
+          <t>báo giá bài pr vov</t>
         </is>
       </c>
       <c r="F389" s="9" t="n">
@@ -6132,7 +6146,7 @@
       <c r="D390" s="7" t="n"/>
       <c r="E390" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài pr hay</t>
+          <t>baáo giá bài pr eva</t>
         </is>
       </c>
       <c r="F390" s="9" t="n">
@@ -6146,7 +6160,7 @@
       <c r="D391" s="7" t="n"/>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr hay</t>
+          <t>book bài pr admicro</t>
         </is>
       </c>
       <c r="F391" s="9" t="n">
@@ -6160,7 +6174,7 @@
       <c r="D392" s="7" t="n"/>
       <c r="E392" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài pr xe tải</t>
+          <t>bao giá bài pr dmtin</t>
         </is>
       </c>
       <c r="F392" s="9" t="n">
@@ -6174,7 +6188,7 @@
       <c r="D393" s="7" t="n"/>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>một số bài pr hay</t>
+          <t>bài pr báo msn online</t>
         </is>
       </c>
       <c r="F393" s="9" t="n">
@@ -6188,7 +6202,7 @@
       <c r="D394" s="7" t="n"/>
       <c r="E394" s="8" t="inlineStr">
         <is>
-          <t>một số bài pr mẫu</t>
+          <t>bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F394" s="9" t="n">
@@ -6202,7 +6216,7 @@
       <c r="D395" s="7" t="n"/>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>bài mẫu pr sự kiện</t>
+          <t>báo giá bài pr eva.vn</t>
         </is>
       </c>
       <c r="F395" s="9" t="n">
@@ -6216,7 +6230,7 @@
       <c r="D396" s="7" t="n"/>
       <c r="E396" s="8" t="inlineStr">
         <is>
-          <t>các bài pr pas mẫu</t>
+          <t>baáo giá bài pr dantri</t>
         </is>
       </c>
       <c r="F396" s="9" t="n">
@@ -6230,7 +6244,7 @@
       <c r="D397" s="7" t="n"/>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>bài pr nhân vật hay</t>
+          <t>bài pr báo sggp online</t>
         </is>
       </c>
       <c r="F397" s="9" t="n">
@@ -6244,7 +6258,7 @@
       <c r="D398" s="7" t="n"/>
       <c r="E398" s="8" t="inlineStr">
         <is>
-          <t>bài pr sản phẩm hay</t>
+          <t>báo giá bài pr afamily</t>
         </is>
       </c>
       <c r="F398" s="9" t="n">
@@ -6258,7 +6272,7 @@
       <c r="D399" s="7" t="n"/>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>bài pr sản phẩm mẫu</t>
+          <t>báo giá bài pr báo mtv</t>
         </is>
       </c>
       <c r="F399" s="9" t="n">
@@ -6272,7 +6286,7 @@
       <c r="D400" s="7" t="n"/>
       <c r="E400" s="8" t="inlineStr">
         <is>
-          <t>một bài pr ấn tượng</t>
+          <t>giá book bài pr kenh14</t>
         </is>
       </c>
       <c r="F400" s="9" t="n">
@@ -6286,7 +6300,7 @@
       <c r="D401" s="7" t="n"/>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr hay</t>
+          <t>đăng bài pr trên cafef</t>
         </is>
       </c>
       <c r="F401" s="9" t="n">
@@ -6300,7 +6314,7 @@
       <c r="D402" s="7" t="n"/>
       <c r="E402" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài pr theo aida</t>
+          <t>báo giá bài pr báo ione</t>
         </is>
       </c>
       <c r="F402" s="9" t="n">
@@ -6314,7 +6328,7 @@
       <c r="D403" s="7" t="n"/>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>những bài pr pas mẫu</t>
+          <t>báo giá bài pr trên 24h</t>
         </is>
       </c>
       <c r="F403" s="9" t="n">
@@ -6328,7 +6342,7 @@
       <c r="D404" s="7" t="n"/>
       <c r="E404" s="8" t="inlineStr">
         <is>
-          <t>bài mẫu pr về món nga</t>
+          <t>báo giá bài pr trên eva</t>
         </is>
       </c>
       <c r="F404" s="9" t="n">
@@ -6342,7 +6356,7 @@
       <c r="D405" s="7" t="n"/>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>bài pr mẫu về công ty</t>
+          <t>báo giá bài pr vnreview</t>
         </is>
       </c>
       <c r="F405" s="9" t="n">
@@ -6356,7 +6370,7 @@
       <c r="D406" s="7" t="n"/>
       <c r="E406" s="8" t="inlineStr">
         <is>
-          <t>bài pr nhà hangfd hay</t>
+          <t>giá bài pr trên dân trí</t>
         </is>
       </c>
       <c r="F406" s="9" t="n">
@@ -6370,7 +6384,7 @@
       <c r="D407" s="7" t="n"/>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>những bài pr game hay</t>
+          <t>đăng bài pr trên eva.vn</t>
         </is>
       </c>
       <c r="F407" s="9" t="n">
@@ -6384,7 +6398,7 @@
       <c r="D408" s="7" t="n"/>
       <c r="E408" s="8" t="inlineStr">
         <is>
-          <t>những bài pr hay nhất</t>
+          <t>bao giá bài pr theleader</t>
         </is>
       </c>
       <c r="F408" s="9" t="n">
@@ -6398,7 +6412,7 @@
       <c r="D409" s="7" t="n"/>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>những bài viết pr hay</t>
+          <t>baáo giá bài pr báo vsao</t>
         </is>
       </c>
       <c r="F409" s="9" t="n">
@@ -6412,7 +6426,7 @@
       <c r="D410" s="7" t="n"/>
       <c r="E410" s="8" t="inlineStr">
         <is>
-          <t>bài pr mẫu về nhân vật</t>
+          <t>baáo giá lên bài pr soha</t>
         </is>
       </c>
       <c r="F410" s="9" t="n">
@@ -6426,7 +6440,7 @@
       <c r="D411" s="7" t="n"/>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr mẫu xe hơi</t>
+          <t>baáo giá lên bài pr zing</t>
         </is>
       </c>
       <c r="F411" s="9" t="n">
@@ -6440,7 +6454,7 @@
       <c r="D412" s="7" t="n"/>
       <c r="E412" s="8" t="inlineStr">
         <is>
-          <t>các bài pr sự kiện mẫu</t>
+          <t>báo giá bài pr ione 2017</t>
         </is>
       </c>
       <c r="F412" s="9" t="n">
@@ -6454,7 +6468,7 @@
       <c r="D413" s="7" t="n"/>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài pr cho sự kiện</t>
+          <t>báo giá bài pr marrybaby</t>
         </is>
       </c>
       <c r="F413" s="9" t="n">
@@ -6468,7 +6482,7 @@
       <c r="D414" s="7" t="n"/>
       <c r="E414" s="8" t="inlineStr">
         <is>
-          <t>cách tạo một bài pr hay</t>
+          <t>báo giá bài pr thanhnien</t>
         </is>
       </c>
       <c r="F414" s="9" t="n">
@@ -6482,7 +6496,7 @@
       <c r="D415" s="7" t="n"/>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr sản phẩm mẫu</t>
+          <t>báo giá bài pr theleader</t>
         </is>
       </c>
       <c r="F415" s="9" t="n">
@@ -6496,7 +6510,7 @@
       <c r="D416" s="7" t="n"/>
       <c r="E416" s="8" t="inlineStr">
         <is>
-          <t>các bài phỏng pr vấn mẫu</t>
+          <t>báo giá bài pr trên zing</t>
         </is>
       </c>
       <c r="F416" s="9" t="n">
@@ -6510,7 +6524,7 @@
       <c r="D417" s="7" t="n"/>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài viết pr sản phẩm</t>
+          <t>baáo giá bài pr vnexpress</t>
         </is>
       </c>
       <c r="F417" s="9" t="n">
@@ -6524,7 +6538,7 @@
       <c r="D418" s="7" t="n"/>
       <c r="E418" s="8" t="inlineStr">
         <is>
-          <t>một số bài pr mẫu sự kiện</t>
+          <t>baáo giá bài pr zing news</t>
         </is>
       </c>
       <c r="F418" s="9" t="n">
@@ -6538,7 +6552,7 @@
       <c r="D419" s="7" t="n"/>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>những bài viết pr hay nhất</t>
+          <t>baáo giá lên bài pr cafef</t>
         </is>
       </c>
       <c r="F419" s="9" t="n">
@@ -6552,7 +6566,7 @@
       <c r="D420" s="7" t="n"/>
       <c r="E420" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr về sản phẩm hay</t>
+          <t>báo giá bài pr 24h.com.vn</t>
         </is>
       </c>
       <c r="F420" s="9" t="n">
@@ -6566,7 +6580,7 @@
       <c r="D421" s="7" t="n"/>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>các bài pr hay về dược phẩm</t>
+          <t>báo giá bài pr báo xaluan</t>
         </is>
       </c>
       <c r="F421" s="9" t="n">
@@ -6580,7 +6594,7 @@
       <c r="D422" s="7" t="n"/>
       <c r="E422" s="8" t="inlineStr">
         <is>
-          <t>ví dụ các bài pr về món nga</t>
+          <t>báo giá bài pr trên foody</t>
         </is>
       </c>
       <c r="F422" s="9" t="n">
@@ -6594,7 +6608,7 @@
       <c r="D423" s="7" t="n"/>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr sản phẩm hay</t>
+          <t>chi phí bài pr của kenh14</t>
         </is>
       </c>
       <c r="F423" s="9" t="n">
@@ -6608,7 +6622,7 @@
       <c r="D424" s="7" t="n"/>
       <c r="E424" s="8" t="inlineStr">
         <is>
-          <t>cách giật tít hay cho bài pr</t>
+          <t>giá 1 bài pr trên elle.vn</t>
         </is>
       </c>
       <c r="F424" s="9" t="n">
@@ -6622,7 +6636,7 @@
       <c r="D425" s="7" t="n"/>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>bài pr mẫu theo công thức pas</t>
+          <t>giá bài pr báo lecourrier</t>
         </is>
       </c>
       <c r="F425" s="9" t="n">
@@ -6636,7 +6650,7 @@
       <c r="D426" s="7" t="n"/>
       <c r="E426" s="8" t="inlineStr">
         <is>
-          <t>caách giật tít hay cho bài pr</t>
+          <t>giá bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F426" s="9" t="n">
@@ -6650,7 +6664,7 @@
       <c r="D427" s="7" t="n"/>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>cách viết bài pr sản phẩm hay</t>
+          <t>giá bài viết pr trên zing</t>
         </is>
       </c>
       <c r="F427" s="9" t="n">
@@ -6664,7 +6678,7 @@
       <c r="D428" s="7" t="n"/>
       <c r="E428" s="8" t="inlineStr">
         <is>
-          <t>những bài viết pr về shop hay</t>
+          <t>bao giaá viết bài pr cafef</t>
         </is>
       </c>
       <c r="F428" s="9" t="n">
@@ -6678,7 +6692,7 @@
       <c r="D429" s="7" t="n"/>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>mẫu bài pr theo công thức aida</t>
+          <t>baáo giá bài pr báo đầu tư</t>
         </is>
       </c>
       <c r="F429" s="9" t="n">
@@ -6692,7 +6706,7 @@
       <c r="D430" s="7" t="n"/>
       <c r="E430" s="8" t="inlineStr">
         <is>
-          <t>những bài pr hầm rượu vang hay</t>
+          <t>baáo giá bài pr vietnamnet</t>
         </is>
       </c>
       <c r="F430" s="9" t="n">
@@ -6706,7 +6720,7 @@
       <c r="D431" s="7" t="n"/>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>tập hợp các bài viết hay về pr</t>
+          <t>baáo giá bài pr vir online</t>
         </is>
       </c>
       <c r="F431" s="9" t="n">
@@ -6720,7 +6734,7 @@
       <c r="D432" s="7" t="n"/>
       <c r="E432" s="8" t="inlineStr">
         <is>
-          <t>bài pr mẫu của tổ chức giáo dục</t>
+          <t>baáo giá lên bài pr eva.vn</t>
         </is>
       </c>
       <c r="F432" s="9" t="n">
@@ -6734,7 +6748,7 @@
       <c r="D433" s="7" t="n"/>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>ví dụ các công thức viết bài pr</t>
+          <t>baáo giá lên bài pr ictnew</t>
         </is>
       </c>
       <c r="F433" s="9" t="n">
@@ -6748,7 +6762,7 @@
       <c r="D434" s="7" t="n"/>
       <c r="E434" s="8" t="inlineStr">
         <is>
-          <t>các nhân vật viết pr bài viết hay</t>
+          <t>baáo giá lên bài pr otofun</t>
         </is>
       </c>
       <c r="F434" s="9" t="n">
@@ -6762,7 +6776,7 @@
       <c r="D435" s="7" t="n"/>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>nhung bài viết pr bán nhà đất hay</t>
+          <t>bài pr báo vtc news online</t>
         </is>
       </c>
       <c r="F435" s="9" t="n">
@@ -6776,7 +6790,7 @@
       <c r="D436" s="7" t="n"/>
       <c r="E436" s="8" t="inlineStr">
         <is>
-          <t>tham khảo các mẫu bài pr đỉnh cao</t>
+          <t>báo giá bài pr báo thitkho</t>
         </is>
       </c>
       <c r="F436" s="9" t="n">
@@ -6790,7 +6804,7 @@
       <c r="D437" s="7" t="n"/>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>các facebooer viết pr bài viết hay</t>
+          <t>báo giá bài pr kenh14 2017</t>
         </is>
       </c>
       <c r="F437" s="9" t="n">
@@ -6804,7 +6818,7 @@
       <c r="D438" s="7" t="n"/>
       <c r="E438" s="8" t="inlineStr">
         <is>
-          <t>các facebooker viết pr bài viết hay</t>
+          <t>báo giá bài pr ngoisao.net</t>
         </is>
       </c>
       <c r="F438" s="9" t="n">
@@ -6818,7 +6832,7 @@
       <c r="D439" s="7" t="n"/>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>đặt tít hay cho bài pr sản phẩm sơn</t>
+          <t>báo giá bài pr trên eva.vn</t>
         </is>
       </c>
       <c r="F439" s="9" t="n">
@@ -6832,7 +6846,7 @@
       <c r="D440" s="7" t="n"/>
       <c r="E440" s="8" t="inlineStr">
         <is>
-          <t>một bài pr mẫu cho ra mắt sản phẩm mới</t>
+          <t>viết bài pr trên báo cafef</t>
         </is>
       </c>
       <c r="F440" s="9" t="n">
@@ -6846,7 +6860,7 @@
       <c r="D441" s="7" t="n"/>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>cách nhận biết baì pr hay bài marketing</t>
+          <t>đăng bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F441" s="9" t="n">
@@ -6860,7 +6874,7 @@
       <c r="D442" s="7" t="n"/>
       <c r="E442" s="8" t="inlineStr">
         <is>
-          <t>ví dụ các công thức viết bài pr facebook</t>
+          <t>baáo giá bài pr baodautu.vn</t>
         </is>
       </c>
       <c r="F442" s="9" t="n">
@@ -6868,13 +6882,13 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="10" t="n"/>
-      <c r="B443" s="10" t="n"/>
-      <c r="C443" s="10" t="n"/>
-      <c r="D443" s="10" t="n"/>
+      <c r="A443" s="7" t="n"/>
+      <c r="B443" s="7" t="n"/>
+      <c r="C443" s="7" t="n"/>
+      <c r="D443" s="7" t="n"/>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>các facebooker viết pr bài viết hay nổi tiếng</t>
+          <t>baáo giá lên bài pr cafebiz</t>
         </is>
       </c>
       <c r="F443" s="9" t="n">
@@ -6882,31 +6896,17 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B444" s="3" t="inlineStr">
-        <is>
-          <t>Báo giá theo đầu báo cụ thể</t>
-        </is>
-      </c>
-      <c r="C444" s="3" t="inlineStr">
-        <is>
-          <t>15 trang /book-bao-*/ + /booking-bao-pr/</t>
-        </is>
-      </c>
-      <c r="D444" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="E444" s="5" t="inlineStr">
-        <is>
-          <t>báo giá bài pr vnexpress</t>
-        </is>
-      </c>
-      <c r="F444" s="6" t="n">
-        <v>30</v>
+      <c r="A444" s="7" t="n"/>
+      <c r="B444" s="7" t="n"/>
+      <c r="C444" s="7" t="n"/>
+      <c r="D444" s="7" t="n"/>
+      <c r="E444" s="8" t="inlineStr">
+        <is>
+          <t>baáo giá lên bài pr dân trí</t>
+        </is>
+      </c>
+      <c r="F444" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -6916,11 +6916,11 @@
       <c r="D445" s="7" t="n"/>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên kenh14</t>
+          <t>bài pr báo pháp luật online</t>
         </is>
       </c>
       <c r="F445" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -6930,11 +6930,11 @@
       <c r="D446" s="7" t="n"/>
       <c r="E446" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr 24h</t>
+          <t>báo giá bài pr báo vsao.com</t>
         </is>
       </c>
       <c r="F446" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
@@ -6944,11 +6944,11 @@
       <c r="D447" s="7" t="n"/>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr cafef</t>
+          <t>báo giá bài pr trên afamily</t>
         </is>
       </c>
       <c r="F447" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -6958,11 +6958,11 @@
       <c r="D448" s="7" t="n"/>
       <c r="E448" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr kenh14</t>
+          <t>báo giá bài pr trên dân trí</t>
         </is>
       </c>
       <c r="F448" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449">
@@ -6972,11 +6972,11 @@
       <c r="D449" s="7" t="n"/>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr vietnamnet</t>
+          <t>báo giá bài pr tạp chí elle</t>
         </is>
       </c>
       <c r="F449" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450">
@@ -6986,11 +6986,11 @@
       <c r="D450" s="7" t="n"/>
       <c r="E450" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên vnexpress</t>
+          <t>đăng bài pr trên vietnamnet</t>
         </is>
       </c>
       <c r="F450" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -7000,11 +7000,11 @@
       <c r="D451" s="7" t="n"/>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên kênh 14</t>
+          <t>bao giá bài pr xaluan online</t>
         </is>
       </c>
       <c r="F451" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -7014,11 +7014,11 @@
       <c r="D452" s="7" t="n"/>
       <c r="E452" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên vnexpress</t>
+          <t>báo giá bài pr báo theleader</t>
         </is>
       </c>
       <c r="F452" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -7028,7 +7028,7 @@
       <c r="D453" s="7" t="n"/>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>bài pr zing</t>
+          <t>báo giá bài pr báo vnexpress</t>
         </is>
       </c>
       <c r="F453" s="9" t="n">
@@ -7042,7 +7042,7 @@
       <c r="D454" s="7" t="n"/>
       <c r="E454" s="8" t="inlineStr">
         <is>
-          <t>bài pr cafef</t>
+          <t>báo giá bài pr dantri.com.vn</t>
         </is>
       </c>
       <c r="F454" s="9" t="n">
@@ -7056,7 +7056,7 @@
       <c r="D455" s="7" t="n"/>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>cafef bài pr</t>
+          <t>báo giá bài pr trên kienthuc</t>
         </is>
       </c>
       <c r="F455" s="9" t="n">
@@ -7070,7 +7070,7 @@
       <c r="D456" s="7" t="n"/>
       <c r="E456" s="8" t="inlineStr">
         <is>
-          <t>bài pr kenh14</t>
+          <t>báo giá đăng bài pr trên 24h</t>
         </is>
       </c>
       <c r="F456" s="9" t="n">
@@ -7084,7 +7084,7 @@
       <c r="D457" s="7" t="n"/>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>bài pr dân trí</t>
+          <t>giá bài pr trên thời sự vtv1</t>
         </is>
       </c>
       <c r="F457" s="9" t="n">
@@ -7098,7 +7098,7 @@
       <c r="D458" s="7" t="n"/>
       <c r="E458" s="8" t="inlineStr">
         <is>
-          <t>bài pr ngoisao</t>
+          <t>giá bài pr tạp chí tài chính</t>
         </is>
       </c>
       <c r="F458" s="9" t="n">
@@ -7112,7 +7112,7 @@
       <c r="D459" s="7" t="n"/>
       <c r="E459" s="8" t="inlineStr">
         <is>
-          <t>cafef bài pr giá</t>
+          <t>đăng bài pr trên báo dân trí</t>
         </is>
       </c>
       <c r="F459" s="9" t="n">
@@ -7126,7 +7126,7 @@
       <c r="D460" s="7" t="n"/>
       <c r="E460" s="8" t="inlineStr">
         <is>
-          <t>bài pr thanh niên</t>
+          <t>đăng bài pr trên giadinh.net</t>
         </is>
       </c>
       <c r="F460" s="9" t="n">
@@ -7140,7 +7140,7 @@
       <c r="D461" s="7" t="n"/>
       <c r="E461" s="8" t="inlineStr">
         <is>
-          <t>lên bài pr baomoi</t>
+          <t>bao gia bài pr giaoduc.net.vn</t>
         </is>
       </c>
       <c r="F461" s="9" t="n">
@@ -7154,7 +7154,7 @@
       <c r="D462" s="7" t="n"/>
       <c r="E462" s="8" t="inlineStr">
         <is>
-          <t>bài pr ngoisao.net</t>
+          <t>bao giá bài pr xa luan online</t>
         </is>
       </c>
       <c r="F462" s="9" t="n">
@@ -7168,7 +7168,7 @@
       <c r="D463" s="7" t="n"/>
       <c r="E463" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr vov</t>
+          <t>baáo giá lên bài pr vneconomy</t>
         </is>
       </c>
       <c r="F463" s="9" t="n">
@@ -7182,7 +7182,7 @@
       <c r="D464" s="7" t="n"/>
       <c r="E464" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr eva</t>
+          <t>baáo giá lên bài pr vnexpress</t>
         </is>
       </c>
       <c r="F464" s="9" t="n">
@@ -7196,7 +7196,7 @@
       <c r="D465" s="7" t="n"/>
       <c r="E465" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo msn online</t>
+          <t>báo giá bài pr người lao động</t>
         </is>
       </c>
       <c r="F465" s="9" t="n">
@@ -7210,7 +7210,7 @@
       <c r="D466" s="7" t="n"/>
       <c r="E466" s="8" t="inlineStr">
         <is>
-          <t>bài pr trên vnexpress</t>
+          <t>báo giá bài pr trên marrybaby</t>
         </is>
       </c>
       <c r="F466" s="9" t="n">
@@ -7224,7 +7224,7 @@
       <c r="D467" s="7" t="n"/>
       <c r="E467" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr eva.vn</t>
+          <t>báo giá bài pr trên trang voh</t>
         </is>
       </c>
       <c r="F467" s="9" t="n">
@@ -7238,7 +7238,7 @@
       <c r="D468" s="7" t="n"/>
       <c r="E468" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo sggp online</t>
+          <t>báo giá bài pr trên webtretho</t>
         </is>
       </c>
       <c r="F468" s="9" t="n">
@@ -7252,7 +7252,7 @@
       <c r="D469" s="7" t="n"/>
       <c r="E469" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr afamily</t>
+          <t>báo giá bài pr vnexpress 2019</t>
         </is>
       </c>
       <c r="F469" s="9" t="n">
@@ -7266,7 +7266,7 @@
       <c r="D470" s="7" t="n"/>
       <c r="E470" s="8" t="inlineStr">
         <is>
-          <t>giá book bài pr kenh14</t>
+          <t>báo giá đăng bài pr trên soha</t>
         </is>
       </c>
       <c r="F470" s="9" t="n">
@@ -7280,7 +7280,7 @@
       <c r="D471" s="7" t="n"/>
       <c r="E471" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên cafef</t>
+          <t>báo giá đăng bài pr trên zing</t>
         </is>
       </c>
       <c r="F471" s="9" t="n">
@@ -7294,7 +7294,7 @@
       <c r="D472" s="7" t="n"/>
       <c r="E472" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên 24h</t>
+          <t>cách thuê dân trí pr bài viết</t>
         </is>
       </c>
       <c r="F472" s="9" t="n">
@@ -7308,7 +7308,7 @@
       <c r="D473" s="7" t="n"/>
       <c r="E473" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên eva</t>
+          <t>giá bài pr trên docbao online</t>
         </is>
       </c>
       <c r="F473" s="9" t="n">
@@ -7322,7 +7322,7 @@
       <c r="D474" s="7" t="n"/>
       <c r="E474" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr vnreview</t>
+          <t>liên hệ bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F474" s="9" t="n">
@@ -7336,7 +7336,7 @@
       <c r="D475" s="7" t="n"/>
       <c r="E475" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên dân trí</t>
+          <t>baáo giá bài pr người lao động</t>
         </is>
       </c>
       <c r="F475" s="9" t="n">
@@ -7350,7 +7350,7 @@
       <c r="D476" s="7" t="n"/>
       <c r="E476" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên eva.vn</t>
+          <t>baáo giá lên bài pr 24h.com.vn</t>
         </is>
       </c>
       <c r="F476" s="9" t="n">
@@ -7364,7 +7364,7 @@
       <c r="D477" s="7" t="n"/>
       <c r="E477" s="8" t="inlineStr">
         <is>
-          <t>bao giá bài pr theleader</t>
+          <t>baáo giá lên bài pr afamily.vn</t>
         </is>
       </c>
       <c r="F477" s="9" t="n">
@@ -7378,7 +7378,7 @@
       <c r="D478" s="7" t="n"/>
       <c r="E478" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr soha</t>
+          <t>baáo giá lên bài pr thanh niên</t>
         </is>
       </c>
       <c r="F478" s="9" t="n">
@@ -7392,7 +7392,7 @@
       <c r="D479" s="7" t="n"/>
       <c r="E479" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr zing</t>
+          <t>baáo giá lên bài pr vietnamnet</t>
         </is>
       </c>
       <c r="F479" s="9" t="n">
@@ -7406,7 +7406,7 @@
       <c r="D480" s="7" t="n"/>
       <c r="E480" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr theleader</t>
+          <t>baáo giá đăng bài pr trên soha</t>
         </is>
       </c>
       <c r="F480" s="9" t="n">
@@ -7420,7 +7420,7 @@
       <c r="D481" s="7" t="n"/>
       <c r="E481" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên zing</t>
+          <t>bài pr báo sggp hoa van online</t>
         </is>
       </c>
       <c r="F481" s="9" t="n">
@@ -7434,7 +7434,7 @@
       <c r="D482" s="7" t="n"/>
       <c r="E482" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr vnexpress</t>
+          <t>báo giá booking bài pr admicro</t>
         </is>
       </c>
       <c r="F482" s="9" t="n">
@@ -7448,7 +7448,7 @@
       <c r="D483" s="7" t="n"/>
       <c r="E483" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr zing news</t>
+          <t>báo giá bài pr báo vtc điện tử</t>
         </is>
       </c>
       <c r="F483" s="9" t="n">
@@ -7462,7 +7462,7 @@
       <c r="D484" s="7" t="n"/>
       <c r="E484" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr cafef</t>
+          <t>báo giá bài pr báo đầu tư 2019</t>
         </is>
       </c>
       <c r="F484" s="9" t="n">
@@ -7476,7 +7476,7 @@
       <c r="D485" s="7" t="n"/>
       <c r="E485" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr 24h.com.vn</t>
+          <t>báo giá bài pr lao động online</t>
         </is>
       </c>
       <c r="F485" s="9" t="n">
@@ -7490,7 +7490,7 @@
       <c r="D486" s="7" t="n"/>
       <c r="E486" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo xaluan</t>
+          <t>báo giá bài pr trên vietnamnet</t>
         </is>
       </c>
       <c r="F486" s="9" t="n">
@@ -7504,7 +7504,7 @@
       <c r="D487" s="7" t="n"/>
       <c r="E487" s="8" t="inlineStr">
         <is>
-          <t>chi phí bài pr của kenh14</t>
+          <t>báo giá đăng bài pr trên cafef</t>
         </is>
       </c>
       <c r="F487" s="9" t="n">
@@ -7518,7 +7518,7 @@
       <c r="D488" s="7" t="n"/>
       <c r="E488" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên vnexpress</t>
+          <t>bảng giá đăng bài pr vneconomy</t>
         </is>
       </c>
       <c r="F488" s="9" t="n">
@@ -7532,7 +7532,7 @@
       <c r="D489" s="7" t="n"/>
       <c r="E489" s="8" t="inlineStr">
         <is>
-          <t>giá bài viết pr trên zing</t>
+          <t>giá bài pr trên depplus online</t>
         </is>
       </c>
       <c r="F489" s="9" t="n">
@@ -7546,7 +7546,7 @@
       <c r="D490" s="7" t="n"/>
       <c r="E490" s="8" t="inlineStr">
         <is>
-          <t>bao giaá viết bài pr cafef</t>
+          <t>giá đăng bài pr vnexpress 2017</t>
         </is>
       </c>
       <c r="F490" s="9" t="n">
@@ -7560,7 +7560,7 @@
       <c r="D491" s="7" t="n"/>
       <c r="E491" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr báo đầu tư</t>
+          <t>agency book bài pr trên báo cnn</t>
         </is>
       </c>
       <c r="F491" s="9" t="n">
@@ -7574,7 +7574,7 @@
       <c r="D492" s="7" t="n"/>
       <c r="E492" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr vietnamnet</t>
+          <t>baáo giá bài pr báo đầu tư 2019</t>
         </is>
       </c>
       <c r="F492" s="9" t="n">
@@ -7588,7 +7588,7 @@
       <c r="D493" s="7" t="n"/>
       <c r="E493" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr vir online</t>
+          <t>baáo giá lên bài pr baodautu.vn</t>
         </is>
       </c>
       <c r="F493" s="9" t="n">
@@ -7602,7 +7602,7 @@
       <c r="D494" s="7" t="n"/>
       <c r="E494" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr eva.vn</t>
+          <t>baáo giá lên bài pr giadinh.net</t>
         </is>
       </c>
       <c r="F494" s="9" t="n">
@@ -7616,7 +7616,7 @@
       <c r="D495" s="7" t="n"/>
       <c r="E495" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr ictnew</t>
+          <t>báo giá bài pr báo công an giấy</t>
         </is>
       </c>
       <c r="F495" s="9" t="n">
@@ -7630,7 +7630,7 @@
       <c r="D496" s="7" t="n"/>
       <c r="E496" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr otofun</t>
+          <t>báo giá bài pr báo xone điện tử</t>
         </is>
       </c>
       <c r="F496" s="9" t="n">
@@ -7644,7 +7644,7 @@
       <c r="D497" s="7" t="n"/>
       <c r="E497" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo vtc news online</t>
+          <t>báo giá bài pr trên baodautu.vn</t>
         </is>
       </c>
       <c r="F497" s="9" t="n">
@@ -7658,7 +7658,7 @@
       <c r="D498" s="7" t="n"/>
       <c r="E498" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr kenh14 2017</t>
+          <t>báo giá bài pr trên ngoisao net</t>
         </is>
       </c>
       <c r="F498" s="9" t="n">
@@ -7672,7 +7672,7 @@
       <c r="D499" s="7" t="n"/>
       <c r="E499" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr ngoisao.net</t>
+          <t>báo giá bài pr vneconomy online</t>
         </is>
       </c>
       <c r="F499" s="9" t="n">
@@ -7686,7 +7686,7 @@
       <c r="D500" s="7" t="n"/>
       <c r="E500" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên eva.vn</t>
+          <t>bảng giá book bài pr trên ivivu</t>
         </is>
       </c>
       <c r="F500" s="9" t="n">
@@ -7700,7 +7700,7 @@
       <c r="D501" s="7" t="n"/>
       <c r="E501" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr trên báo cafef</t>
+          <t>giá bài quảng cáo pr baomoi.com</t>
         </is>
       </c>
       <c r="F501" s="9" t="n">
@@ -7714,7 +7714,7 @@
       <c r="D502" s="7" t="n"/>
       <c r="E502" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên vnexpress</t>
+          <t>baáo giá bài pr báo vsao điện tử</t>
         </is>
       </c>
       <c r="F502" s="9" t="n">
@@ -7728,7 +7728,7 @@
       <c r="D503" s="7" t="n"/>
       <c r="E503" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr baodautu.vn</t>
+          <t>báo giá bài pr báo giấy tuổi trẻ</t>
         </is>
       </c>
       <c r="F503" s="9" t="n">
@@ -7742,7 +7742,7 @@
       <c r="D504" s="7" t="n"/>
       <c r="E504" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr cafebiz</t>
+          <t>báo giá bài pr báo mtvwe điện tử</t>
         </is>
       </c>
       <c r="F504" s="9" t="n">
@@ -7756,7 +7756,7 @@
       <c r="D505" s="7" t="n"/>
       <c r="E505" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr dân trí</t>
+          <t>báo giá bài pr tiền phong online</t>
         </is>
       </c>
       <c r="F505" s="9" t="n">
@@ -7770,7 +7770,7 @@
       <c r="D506" s="7" t="n"/>
       <c r="E506" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo pháp luật online</t>
+          <t>báo giá bài pr trên thanhnien.vn</t>
         </is>
       </c>
       <c r="F506" s="9" t="n">
@@ -7784,7 +7784,7 @@
       <c r="D507" s="7" t="n"/>
       <c r="E507" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên afamily</t>
+          <t>chi phí đăng bài pr trên cafebiz</t>
         </is>
       </c>
       <c r="F507" s="9" t="n">
@@ -7798,7 +7798,7 @@
       <c r="D508" s="7" t="n"/>
       <c r="E508" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên dân trí</t>
+          <t>chi phí đăng bài pr trên ictnews</t>
         </is>
       </c>
       <c r="F508" s="9" t="n">
@@ -7812,7 +7812,7 @@
       <c r="D509" s="7" t="n"/>
       <c r="E509" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr tạp chí elle</t>
+          <t>giá bài pr báo lecourrier online</t>
         </is>
       </c>
       <c r="F509" s="9" t="n">
@@ -7826,7 +7826,7 @@
       <c r="D510" s="7" t="n"/>
       <c r="E510" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên vietnamnet</t>
+          <t>giá bài quảng cáo pr basomoi.com</t>
         </is>
       </c>
       <c r="F510" s="9" t="n">
@@ -7840,7 +7840,7 @@
       <c r="D511" s="7" t="n"/>
       <c r="E511" s="8" t="inlineStr">
         <is>
-          <t>bao giá bài pr xaluan online</t>
+          <t>giá bài quảng cáo pr new.zing.vn</t>
         </is>
       </c>
       <c r="F511" s="9" t="n">
@@ -7854,7 +7854,7 @@
       <c r="D512" s="7" t="n"/>
       <c r="E512" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo theleader</t>
+          <t>agency book bài pr trên times new</t>
         </is>
       </c>
       <c r="F512" s="9" t="n">
@@ -7868,7 +7868,7 @@
       <c r="D513" s="7" t="n"/>
       <c r="E513" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo vnexpress</t>
+          <t>baáo giá lên bài pr thethaovanhoa</t>
         </is>
       </c>
       <c r="F513" s="9" t="n">
@@ -7882,7 +7882,7 @@
       <c r="D514" s="7" t="n"/>
       <c r="E514" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên 24h</t>
+          <t>báo giá bài pr báo mtv we điện tử</t>
         </is>
       </c>
       <c r="F514" s="9" t="n">
@@ -7896,7 +7896,7 @@
       <c r="D515" s="7" t="n"/>
       <c r="E515" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên thời sự vtv1</t>
+          <t>báo giá bài pr dantri.com.vn 2017</t>
         </is>
       </c>
       <c r="F515" s="9" t="n">
@@ -7910,7 +7910,7 @@
       <c r="D516" s="7" t="n"/>
       <c r="E516" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr tạp chí tài chính</t>
+          <t>báo giá bài pr doanh nhân sài gòn</t>
         </is>
       </c>
       <c r="F516" s="9" t="n">
@@ -7924,7 +7924,7 @@
       <c r="D517" s="7" t="n"/>
       <c r="E517" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên báo dân trí</t>
+          <t>bảng giá đăng bài pr trên báo 24h</t>
         </is>
       </c>
       <c r="F517" s="9" t="n">
@@ -7938,7 +7938,7 @@
       <c r="D518" s="7" t="n"/>
       <c r="E518" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên giadinh.net</t>
+          <t>chi phí viết bài pr trên new zing</t>
         </is>
       </c>
       <c r="F518" s="9" t="n">
@@ -7952,7 +7952,7 @@
       <c r="D519" s="7" t="n"/>
       <c r="E519" s="8" t="inlineStr">
         <is>
-          <t>bao gia bài pr giaoduc.net.vn</t>
+          <t>bao giá bài pr báo xa luan điện tử</t>
         </is>
       </c>
       <c r="F519" s="9" t="n">
@@ -7966,7 +7966,7 @@
       <c r="D520" s="7" t="n"/>
       <c r="E520" s="8" t="inlineStr">
         <is>
-          <t>bao giá bài pr xa luan online</t>
+          <t>baáo giá lên bài pr vietnamexpress</t>
         </is>
       </c>
       <c r="F520" s="9" t="n">
@@ -7980,7 +7980,7 @@
       <c r="D521" s="7" t="n"/>
       <c r="E521" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr vnexpress</t>
+          <t>báo giá book bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F521" s="9" t="n">
@@ -7994,7 +7994,7 @@
       <c r="D522" s="7" t="n"/>
       <c r="E522" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr người lao động</t>
+          <t>báo giá bài pr báo lao động online</t>
         </is>
       </c>
       <c r="F522" s="9" t="n">
@@ -8008,7 +8008,7 @@
       <c r="D523" s="7" t="n"/>
       <c r="E523" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên webtretho</t>
+          <t>báo giá bài pr người lao động 2019</t>
         </is>
       </c>
       <c r="F523" s="9" t="n">
@@ -8022,7 +8022,7 @@
       <c r="D524" s="7" t="n"/>
       <c r="E524" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr vnexpress 2019</t>
+          <t>báo giá bài pr trên vnexpress 2017</t>
         </is>
       </c>
       <c r="F524" s="9" t="n">
@@ -8036,7 +8036,7 @@
       <c r="D525" s="7" t="n"/>
       <c r="E525" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên soha</t>
+          <t>báo giá bài pr trên vnexpress 2018</t>
         </is>
       </c>
       <c r="F525" s="9" t="n">
@@ -8050,7 +8050,7 @@
       <c r="D526" s="7" t="n"/>
       <c r="E526" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên zing</t>
+          <t>chi phí viết bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F526" s="9" t="n">
@@ -8064,7 +8064,7 @@
       <c r="D527" s="7" t="n"/>
       <c r="E527" s="8" t="inlineStr">
         <is>
-          <t>cách thuê dân trí pr bài viết</t>
+          <t>giá bài quảng cáo pr trên tinxe.vn</t>
         </is>
       </c>
       <c r="F527" s="9" t="n">
@@ -8078,7 +8078,7 @@
       <c r="D528" s="7" t="n"/>
       <c r="E528" s="8" t="inlineStr">
         <is>
-          <t>liên hệ bài pr trên vnexpress</t>
+          <t>book bài pr trên báo nước ngoài cnn</t>
         </is>
       </c>
       <c r="F528" s="9" t="n">
@@ -8092,7 +8092,7 @@
       <c r="D529" s="7" t="n"/>
       <c r="E529" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr người lao động</t>
+          <t>báo giá bài pr trên báo baodautu.vn</t>
         </is>
       </c>
       <c r="F529" s="9" t="n">
@@ -8106,7 +8106,7 @@
       <c r="D530" s="7" t="n"/>
       <c r="E530" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr 24h.com.vn</t>
+          <t>báo giá bài pr trên kienthucdoisong</t>
         </is>
       </c>
       <c r="F530" s="9" t="n">
@@ -8120,7 +8120,7 @@
       <c r="D531" s="7" t="n"/>
       <c r="E531" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr afamily.vn</t>
+          <t>báo giá bài pr trên lao động online</t>
         </is>
       </c>
       <c r="F531" s="9" t="n">
@@ -8134,7 +8134,7 @@
       <c r="D532" s="7" t="n"/>
       <c r="E532" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr thanh niên</t>
+          <t>báo giá đăng bài pr trên 24h.com.vn</t>
         </is>
       </c>
       <c r="F532" s="9" t="n">
@@ -8148,7 +8148,7 @@
       <c r="D533" s="7" t="n"/>
       <c r="E533" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr vietnamnet</t>
+          <t>baáo giá bài pr trên báo baodautu.vn</t>
         </is>
       </c>
       <c r="F533" s="9" t="n">
@@ -8162,7 +8162,7 @@
       <c r="D534" s="7" t="n"/>
       <c r="E534" s="8" t="inlineStr">
         <is>
-          <t>baáo giá đăng bài pr trên soha</t>
+          <t>booking bài pr báo batdongsan.com.vn</t>
         </is>
       </c>
       <c r="F534" s="9" t="n">
@@ -8176,7 +8176,7 @@
       <c r="D535" s="7" t="n"/>
       <c r="E535" s="8" t="inlineStr">
         <is>
-          <t>bài pr báo sggp hoa van online</t>
+          <t>báo giá bài pr báo giấy sggp hoa văn</t>
         </is>
       </c>
       <c r="F535" s="9" t="n">
@@ -8190,7 +8190,7 @@
       <c r="D536" s="7" t="n"/>
       <c r="E536" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo vtc điện tử</t>
+          <t>báo giá bài pr người lao động online</t>
         </is>
       </c>
       <c r="F536" s="9" t="n">
@@ -8204,7 +8204,7 @@
       <c r="D537" s="7" t="n"/>
       <c r="E537" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo đầu tư 2019</t>
+          <t>giá bài pr trên sggp hoa van dien tử</t>
         </is>
       </c>
       <c r="F537" s="9" t="n">
@@ -8218,7 +8218,7 @@
       <c r="D538" s="7" t="n"/>
       <c r="E538" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr lao động online</t>
+          <t>giá bài pr trên trang infonet online</t>
         </is>
       </c>
       <c r="F538" s="9" t="n">
@@ -8232,7 +8232,7 @@
       <c r="D539" s="7" t="n"/>
       <c r="E539" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên vietnamnet</t>
+          <t>baáo giá bài pr an ninh thủ đô online</t>
         </is>
       </c>
       <c r="F539" s="9" t="n">
@@ -8246,7 +8246,7 @@
       <c r="D540" s="7" t="n"/>
       <c r="E540" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên cafef</t>
+          <t>baáo giá bài pr báo thanh niên online</t>
         </is>
       </c>
       <c r="F540" s="9" t="n">
@@ -8260,7 +8260,7 @@
       <c r="D541" s="7" t="n"/>
       <c r="E541" s="8" t="inlineStr">
         <is>
-          <t>giá đăng bài pr vnexpress 2017</t>
+          <t>baáo giá lên bài pr batdongsan.com.vn</t>
         </is>
       </c>
       <c r="F541" s="9" t="n">
@@ -8274,7 +8274,7 @@
       <c r="D542" s="7" t="n"/>
       <c r="E542" s="8" t="inlineStr">
         <is>
-          <t>agency book bài pr trên báo cnn</t>
+          <t>báo giá đăng bài pr batdongsan.com.vn</t>
         </is>
       </c>
       <c r="F542" s="9" t="n">
@@ -8288,7 +8288,7 @@
       <c r="D543" s="7" t="n"/>
       <c r="E543" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr báo đầu tư 2019</t>
+          <t>báo giá đăng bài pr trên baoquocte.vn</t>
         </is>
       </c>
       <c r="F543" s="9" t="n">
@@ -8302,7 +8302,7 @@
       <c r="D544" s="7" t="n"/>
       <c r="E544" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr baodautu.vn</t>
+          <t>demo các vị trí bài pr trên vnexpress</t>
         </is>
       </c>
       <c r="F544" s="9" t="n">
@@ -8316,7 +8316,7 @@
       <c r="D545" s="7" t="n"/>
       <c r="E545" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr giadinh.net</t>
+          <t>bảng giá đăng bài pr trên báo tuổi trẻ</t>
         </is>
       </c>
       <c r="F545" s="9" t="n">
@@ -8330,7 +8330,7 @@
       <c r="D546" s="7" t="n"/>
       <c r="E546" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo công an giấy</t>
+          <t>giá bài quảng cáo pr trên autobikes.vn</t>
         </is>
       </c>
       <c r="F546" s="9" t="n">
@@ -8344,7 +8344,7 @@
       <c r="D547" s="7" t="n"/>
       <c r="E547" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên baodautu.vn</t>
+          <t>bao giá bài pr thế giới tiếp thị online</t>
         </is>
       </c>
       <c r="F547" s="9" t="n">
@@ -8358,7 +8358,7 @@
       <c r="D548" s="7" t="n"/>
       <c r="E548" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên ngoisao net</t>
+          <t>bài pr aroma resort trên dân trí bị xóa</t>
         </is>
       </c>
       <c r="F548" s="9" t="n">
@@ -8372,7 +8372,7 @@
       <c r="D549" s="7" t="n"/>
       <c r="E549" s="8" t="inlineStr">
         <is>
-          <t>giá bài quảng cáo pr baomoi.com</t>
+          <t>hỗ trợ đăng bài pr trên nhịp sống sendo</t>
         </is>
       </c>
       <c r="F549" s="9" t="n">
@@ -8386,7 +8386,7 @@
       <c r="D550" s="7" t="n"/>
       <c r="E550" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo giấy tuổi trẻ</t>
+          <t>book bài pr trên tạp chí bác sĩ gia đình</t>
         </is>
       </c>
       <c r="F550" s="9" t="n">
@@ -8400,7 +8400,7 @@
       <c r="D551" s="7" t="n"/>
       <c r="E551" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr tiền phong online</t>
+          <t>booking bài pr trên tiếp thị và gia đình</t>
         </is>
       </c>
       <c r="F551" s="9" t="n">
@@ -8414,7 +8414,7 @@
       <c r="D552" s="7" t="n"/>
       <c r="E552" s="8" t="inlineStr">
         <is>
-          <t>chi phí đăng bài pr trên cafebiz</t>
+          <t>báo giá bài pr sài gòn giải phóng online</t>
         </is>
       </c>
       <c r="F552" s="9" t="n">
@@ -8428,7 +8428,7 @@
       <c r="D553" s="7" t="n"/>
       <c r="E553" s="8" t="inlineStr">
         <is>
-          <t>chi phí đăng bài pr trên ictnews</t>
+          <t>báo giá bài pr báo giấy tiếp thị gia đình</t>
         </is>
       </c>
       <c r="F553" s="9" t="n">
@@ -8442,7 +8442,7 @@
       <c r="D554" s="7" t="n"/>
       <c r="E554" s="8" t="inlineStr">
         <is>
-          <t>giá bài quảng cáo pr new.zing.vn</t>
+          <t>format bài pr gửi báo chí times new roman</t>
         </is>
       </c>
       <c r="F554" s="9" t="n">
@@ -8456,7 +8456,7 @@
       <c r="D555" s="7" t="n"/>
       <c r="E555" s="8" t="inlineStr">
         <is>
-          <t>agency book bài pr trên times new</t>
+          <t>baáo giá bài pr tiếp thị gia đình báo giấy</t>
         </is>
       </c>
       <c r="F555" s="9" t="n">
@@ -8470,7 +8470,7 @@
       <c r="D556" s="7" t="n"/>
       <c r="E556" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr doanh nhân sài gòn</t>
+          <t>baáo giá gói đăng bài pr trên ngôi sao.net</t>
         </is>
       </c>
       <c r="F556" s="9" t="n">
@@ -8484,7 +8484,7 @@
       <c r="D557" s="7" t="n"/>
       <c r="E557" s="8" t="inlineStr">
         <is>
-          <t>bảng giá đăng bài pr trên báo 24h</t>
+          <t>báo giá bài pr báo công an nhân dân online</t>
         </is>
       </c>
       <c r="F557" s="9" t="n">
@@ -8498,7 +8498,7 @@
       <c r="D558" s="7" t="n"/>
       <c r="E558" s="8" t="inlineStr">
         <is>
-          <t>chi phí viết bài pr trên new zing</t>
+          <t>chi phí thuê viết bài pr trên tạp chí elle</t>
         </is>
       </c>
       <c r="F558" s="9" t="n">
@@ -8512,7 +8512,7 @@
       <c r="D559" s="7" t="n"/>
       <c r="E559" s="8" t="inlineStr">
         <is>
-          <t>bao giá bài pr báo xa luan điện tử</t>
+          <t>báo giá bài pr báo tiếp thị gia đình online</t>
         </is>
       </c>
       <c r="F559" s="9" t="n">
@@ -8526,7 +8526,7 @@
       <c r="D560" s="7" t="n"/>
       <c r="E560" s="8" t="inlineStr">
         <is>
-          <t>báo giá book bài pr trên vnexpress</t>
+          <t>báo giá bài pr trên trang thegioivanhoa.net</t>
         </is>
       </c>
       <c r="F560" s="9" t="n">
@@ -8540,7 +8540,7 @@
       <c r="D561" s="7" t="n"/>
       <c r="E561" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo lao động online</t>
+          <t>giá chạy bài pr trên vneconomy là bao nhiêu</t>
         </is>
       </c>
       <c r="F561" s="9" t="n">
@@ -8554,7 +8554,7 @@
       <c r="D562" s="7" t="n"/>
       <c r="E562" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr người lao động 2019</t>
+          <t>baáo giá bài pr thiếu niên tiền phong online</t>
         </is>
       </c>
       <c r="F562" s="9" t="n">
@@ -8568,7 +8568,7 @@
       <c r="D563" s="7" t="n"/>
       <c r="E563" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên vnexpress 2017</t>
+          <t>báo giá bài pr báo pháp luật việt nam online</t>
         </is>
       </c>
       <c r="F563" s="9" t="n">
@@ -8582,7 +8582,7 @@
       <c r="D564" s="7" t="n"/>
       <c r="E564" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên vnexpress 2018</t>
+          <t>baáo giá bài pr vietnam economic times online</t>
         </is>
       </c>
       <c r="F564" s="9" t="n">
@@ -8596,7 +8596,7 @@
       <c r="D565" s="7" t="n"/>
       <c r="E565" s="8" t="inlineStr">
         <is>
-          <t>chi phí viết bài pr trên vnexpress</t>
+          <t>báo giá bài pr trên trang thế giới văn hóa.net</t>
         </is>
       </c>
       <c r="F565" s="9" t="n">
@@ -8604,13 +8604,13 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="7" t="n"/>
-      <c r="B566" s="7" t="n"/>
-      <c r="C566" s="7" t="n"/>
-      <c r="D566" s="7" t="n"/>
+      <c r="A566" s="10" t="n"/>
+      <c r="B566" s="10" t="n"/>
+      <c r="C566" s="10" t="n"/>
+      <c r="D566" s="10" t="n"/>
       <c r="E566" s="8" t="inlineStr">
         <is>
-          <t>book bài pr trên báo nước ngoài cnn</t>
+          <t>báo giá bài pr vietnam investment review online</t>
         </is>
       </c>
       <c r="F566" s="9" t="n">
@@ -8618,17 +8618,31 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="7" t="n"/>
-      <c r="B567" s="7" t="n"/>
-      <c r="C567" s="7" t="n"/>
-      <c r="D567" s="7" t="n"/>
-      <c r="E567" s="8" t="inlineStr">
-        <is>
-          <t>báo giá bài pr trên báo baodautu.vn</t>
-        </is>
-      </c>
-      <c r="F567" s="9" t="n">
-        <v>0</v>
+      <c r="A567" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B567" s="3" t="inlineStr">
+        <is>
+          <t>Giá / đăng / booking chung</t>
+        </is>
+      </c>
+      <c r="C567" s="3" t="inlineStr">
+        <is>
+          <t>/booking-bao-pr/ (hub giá)</t>
+        </is>
+      </c>
+      <c r="D567" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="E567" s="5" t="inlineStr">
+        <is>
+          <t>đăng bài pr</t>
+        </is>
+      </c>
+      <c r="F567" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="568">
@@ -8638,11 +8652,11 @@
       <c r="D568" s="7" t="n"/>
       <c r="E568" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên lao động online</t>
+          <t>giá bài pr</t>
         </is>
       </c>
       <c r="F568" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="569">
@@ -8652,11 +8666,11 @@
       <c r="D569" s="7" t="n"/>
       <c r="E569" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên 24h.com.vn</t>
+          <t>book bài pr</t>
         </is>
       </c>
       <c r="F569" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="570">
@@ -8666,11 +8680,11 @@
       <c r="D570" s="7" t="n"/>
       <c r="E570" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr trên báo baodautu.vn</t>
+          <t>báo giá bài pr</t>
         </is>
       </c>
       <c r="F570" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="571">
@@ -8680,11 +8694,11 @@
       <c r="D571" s="7" t="n"/>
       <c r="E571" s="8" t="inlineStr">
         <is>
-          <t>booking bài pr báo batdongsan.com.vn</t>
+          <t>giá đăng bài pr</t>
         </is>
       </c>
       <c r="F571" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="572">
@@ -8694,11 +8708,11 @@
       <c r="D572" s="7" t="n"/>
       <c r="E572" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo giấy sggp hoa văn</t>
+          <t>booking bài pr</t>
         </is>
       </c>
       <c r="F572" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="573">
@@ -8708,11 +8722,11 @@
       <c r="D573" s="7" t="n"/>
       <c r="E573" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr người lao động online</t>
+          <t>đăng bài pr trên báo</t>
         </is>
       </c>
       <c r="F573" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="574">
@@ -8722,7 +8736,7 @@
       <c r="D574" s="7" t="n"/>
       <c r="E574" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên sggp hoa van dien tử</t>
+          <t>baáo giá bài pr</t>
         </is>
       </c>
       <c r="F574" s="9" t="n">
@@ -8736,7 +8750,7 @@
       <c r="D575" s="7" t="n"/>
       <c r="E575" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr an ninh thủ đô online</t>
+          <t>kênh đăng bài pr</t>
         </is>
       </c>
       <c r="F575" s="9" t="n">
@@ -8750,7 +8764,7 @@
       <c r="D576" s="7" t="n"/>
       <c r="E576" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr báo thanh niên online</t>
+          <t>viết bài pr thuê</t>
         </is>
       </c>
       <c r="F576" s="9" t="n">
@@ -8764,7 +8778,7 @@
       <c r="D577" s="7" t="n"/>
       <c r="E577" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr batdongsan.com.vn</t>
+          <t>báo giá bài pr vo</t>
         </is>
       </c>
       <c r="F577" s="9" t="n">
@@ -8778,7 +8792,7 @@
       <c r="D578" s="7" t="n"/>
       <c r="E578" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr batdongsan.com.vn</t>
+          <t>đăng bài pr ở đâu</t>
         </is>
       </c>
       <c r="F578" s="9" t="n">
@@ -8792,7 +8806,7 @@
       <c r="D579" s="7" t="n"/>
       <c r="E579" s="8" t="inlineStr">
         <is>
-          <t>demo các vị trí bài pr trên vnexpress</t>
+          <t>agency book bài pr</t>
         </is>
       </c>
       <c r="F579" s="9" t="n">
@@ -8806,7 +8820,7 @@
       <c r="D580" s="7" t="n"/>
       <c r="E580" s="8" t="inlineStr">
         <is>
-          <t>bảng giá đăng bài pr trên báo tuổi trẻ</t>
+          <t>agency đăng bài pr</t>
         </is>
       </c>
       <c r="F580" s="9" t="n">
@@ -8820,7 +8834,7 @@
       <c r="D581" s="7" t="n"/>
       <c r="E581" s="8" t="inlineStr">
         <is>
-          <t>bao giá bài pr thế giới tiếp thị online</t>
+          <t>booking viết bài pr</t>
         </is>
       </c>
       <c r="F581" s="9" t="n">
@@ -8834,7 +8848,7 @@
       <c r="D582" s="7" t="n"/>
       <c r="E582" s="8" t="inlineStr">
         <is>
-          <t>bài pr aroma resort trên dân trí bị xóa</t>
+          <t>chi phí book bài pr</t>
         </is>
       </c>
       <c r="F582" s="9" t="n">
@@ -8848,7 +8862,7 @@
       <c r="D583" s="7" t="n"/>
       <c r="E583" s="8" t="inlineStr">
         <is>
-          <t>book bài pr trên tạp chí bác sĩ gia đình</t>
+          <t>chuỗi bài pr giá rẻ</t>
         </is>
       </c>
       <c r="F583" s="9" t="n">
@@ -8862,7 +8876,7 @@
       <c r="D584" s="7" t="n"/>
       <c r="E584" s="8" t="inlineStr">
         <is>
-          <t>booking bài pr trên tiếp thị và gia đình</t>
+          <t>chiến lược đi bài pr</t>
         </is>
       </c>
       <c r="F584" s="9" t="n">
@@ -8876,7 +8890,7 @@
       <c r="D585" s="7" t="n"/>
       <c r="E585" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr sài gòn giải phóng online</t>
+          <t>viết bài pr facebook</t>
         </is>
       </c>
       <c r="F585" s="9" t="n">
@@ -8890,7 +8904,7 @@
       <c r="D586" s="7" t="n"/>
       <c r="E586" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo giấy tiếp thị gia đình</t>
+          <t>báo giá bài pr online</t>
         </is>
       </c>
       <c r="F586" s="9" t="n">
@@ -8904,7 +8918,7 @@
       <c r="D587" s="7" t="n"/>
       <c r="E587" s="8" t="inlineStr">
         <is>
-          <t>format bài pr gửi báo chí times new roman</t>
+          <t>gói mua bài pr giá rẻ</t>
         </is>
       </c>
       <c r="F587" s="9" t="n">
@@ -8918,7 +8932,7 @@
       <c r="D588" s="7" t="n"/>
       <c r="E588" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr tiếp thị gia đình báo giấy</t>
+          <t>báo giá bài pr kenh 14</t>
         </is>
       </c>
       <c r="F588" s="9" t="n">
@@ -8932,7 +8946,7 @@
       <c r="D589" s="7" t="n"/>
       <c r="E589" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo công an nhân dân online</t>
+          <t>công ty booking bài pr</t>
         </is>
       </c>
       <c r="F589" s="9" t="n">
@@ -8946,7 +8960,7 @@
       <c r="D590" s="7" t="n"/>
       <c r="E590" s="8" t="inlineStr">
         <is>
-          <t>chi phí thuê viết bài pr trên tạp chí elle</t>
+          <t>báo giá bài pr ict news</t>
         </is>
       </c>
       <c r="F590" s="9" t="n">
@@ -8960,7 +8974,7 @@
       <c r="D591" s="7" t="n"/>
       <c r="E591" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo tiếp thị gia đình online</t>
+          <t>giá dang bài pr báo mới</t>
         </is>
       </c>
       <c r="F591" s="9" t="n">
@@ -8974,7 +8988,7 @@
       <c r="D592" s="7" t="n"/>
       <c r="E592" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr thiếu niên tiền phong online</t>
+          <t>đăng bài pr báo điện tử</t>
         </is>
       </c>
       <c r="F592" s="9" t="n">
@@ -8988,7 +9002,7 @@
       <c r="D593" s="7" t="n"/>
       <c r="E593" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo pháp luật việt nam online</t>
+          <t>các bài pr mảng giáo dục</t>
         </is>
       </c>
       <c r="F593" s="9" t="n">
@@ -9002,7 +9016,7 @@
       <c r="D594" s="7" t="n"/>
       <c r="E594" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr vietnam economic times online</t>
+          <t>booking bài pr báo online</t>
         </is>
       </c>
       <c r="F594" s="9" t="n">
@@ -9010,13 +9024,13 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="10" t="n"/>
-      <c r="B595" s="10" t="n"/>
-      <c r="C595" s="10" t="n"/>
-      <c r="D595" s="10" t="n"/>
+      <c r="A595" s="7" t="n"/>
+      <c r="B595" s="7" t="n"/>
+      <c r="C595" s="7" t="n"/>
+      <c r="D595" s="7" t="n"/>
       <c r="E595" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr vietnam investment review online</t>
+          <t>báo giá bài pr the leader</t>
         </is>
       </c>
       <c r="F595" s="9" t="n">
@@ -9024,31 +9038,17 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B596" s="3" t="inlineStr">
-        <is>
-          <t>Giá / đăng / booking chung</t>
-        </is>
-      </c>
-      <c r="C596" s="3" t="inlineStr">
-        <is>
-          <t>/booking-bao-pr/ (hub giá)</t>
-        </is>
-      </c>
-      <c r="D596" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="E596" s="5" t="inlineStr">
-        <is>
-          <t>đăng bài pr</t>
-        </is>
-      </c>
-      <c r="F596" s="6" t="n">
-        <v>30</v>
+      <c r="A596" s="7" t="n"/>
+      <c r="B596" s="7" t="n"/>
+      <c r="C596" s="7" t="n"/>
+      <c r="D596" s="7" t="n"/>
+      <c r="E596" s="8" t="inlineStr">
+        <is>
+          <t>giá 1 bài pr thông thường</t>
+        </is>
+      </c>
+      <c r="F596" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="597">
@@ -9058,11 +9058,11 @@
       <c r="D597" s="7" t="n"/>
       <c r="E597" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr</t>
+          <t>giá 1 bài pr trên kenh 14</t>
         </is>
       </c>
       <c r="F597" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="598">
@@ -9072,11 +9072,11 @@
       <c r="D598" s="7" t="n"/>
       <c r="E598" s="8" t="inlineStr">
         <is>
-          <t>book bài pr</t>
+          <t>neên đi bài pr như thế nào</t>
         </is>
       </c>
       <c r="F598" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="599">
@@ -9086,11 +9086,11 @@
       <c r="D599" s="7" t="n"/>
       <c r="E599" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr</t>
+          <t>baáo giá lên bài pr tuoitre</t>
         </is>
       </c>
       <c r="F599" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="600">
@@ -9100,11 +9100,11 @@
       <c r="D600" s="7" t="n"/>
       <c r="E600" s="8" t="inlineStr">
         <is>
-          <t>giá đăng bài pr</t>
+          <t>báo giá bài pr bạch mỹ liên</t>
         </is>
       </c>
       <c r="F600" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="601">
@@ -9114,11 +9114,11 @@
       <c r="D601" s="7" t="n"/>
       <c r="E601" s="8" t="inlineStr">
         <is>
-          <t>booking bài pr</t>
+          <t>báo giá bài pr trên báo mới</t>
         </is>
       </c>
       <c r="F601" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="602">
@@ -9128,11 +9128,11 @@
       <c r="D602" s="7" t="n"/>
       <c r="E602" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên báo</t>
+          <t>quy cách đi bài pr trên báo</t>
         </is>
       </c>
       <c r="F602" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="603">
@@ -9142,7 +9142,7 @@
       <c r="D603" s="7" t="n"/>
       <c r="E603" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr</t>
+          <t>giá bài pr trên báo bưu điện</t>
         </is>
       </c>
       <c r="F603" s="9" t="n">
@@ -9156,7 +9156,7 @@
       <c r="D604" s="7" t="n"/>
       <c r="E604" s="8" t="inlineStr">
         <is>
-          <t>kênh đăng bài pr</t>
+          <t>giá đăng bài pr trên các báo</t>
         </is>
       </c>
       <c r="F604" s="9" t="n">
@@ -9170,7 +9170,7 @@
       <c r="D605" s="7" t="n"/>
       <c r="E605" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr thuê</t>
+          <t>neên đăng bài pr lên báo nào</t>
         </is>
       </c>
       <c r="F605" s="9" t="n">
@@ -9184,7 +9184,7 @@
       <c r="D606" s="7" t="n"/>
       <c r="E606" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr vo</t>
+          <t>đăng bài pr trên báo điện tử</t>
         </is>
       </c>
       <c r="F606" s="9" t="n">
@@ -9198,7 +9198,7 @@
       <c r="D607" s="7" t="n"/>
       <c r="E607" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr forbes</t>
+          <t>đăng bài pr trên các báo lớn</t>
         </is>
       </c>
       <c r="F607" s="9" t="n">
@@ -9212,7 +9212,7 @@
       <c r="D608" s="7" t="n"/>
       <c r="E608" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr ở đâu</t>
+          <t>cách book bài pr trên báo chí</t>
         </is>
       </c>
       <c r="F608" s="9" t="n">
@@ -9226,7 +9226,7 @@
       <c r="D609" s="7" t="n"/>
       <c r="E609" s="8" t="inlineStr">
         <is>
-          <t>agency book bài pr</t>
+          <t>cách đăng bài pr trên báo chí</t>
         </is>
       </c>
       <c r="F609" s="9" t="n">
@@ -9240,7 +9240,7 @@
       <c r="D610" s="7" t="n"/>
       <c r="E610" s="8" t="inlineStr">
         <is>
-          <t>agency đăng bài pr</t>
+          <t>đăng bài pr trên phụ nữ today</t>
         </is>
       </c>
       <c r="F610" s="9" t="n">
@@ -9254,7 +9254,7 @@
       <c r="D611" s="7" t="n"/>
       <c r="E611" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr voh</t>
+          <t>baáo giá lên bài pr phunuonline</t>
         </is>
       </c>
       <c r="F611" s="9" t="n">
@@ -9268,7 +9268,7 @@
       <c r="D612" s="7" t="n"/>
       <c r="E612" s="8" t="inlineStr">
         <is>
-          <t>book bài pr admicro</t>
+          <t>báo giá bài pr chính phủ online</t>
         </is>
       </c>
       <c r="F612" s="9" t="n">
@@ -9282,7 +9282,7 @@
       <c r="D613" s="7" t="n"/>
       <c r="E613" s="8" t="inlineStr">
         <is>
-          <t>booking viết bài pr</t>
+          <t>báo giá bài pr dan ong magazine</t>
         </is>
       </c>
       <c r="F613" s="9" t="n">
@@ -9296,7 +9296,7 @@
       <c r="D614" s="7" t="n"/>
       <c r="E614" s="8" t="inlineStr">
         <is>
-          <t>chi phí book bài pr</t>
+          <t>báo giá bài pr tư vấn tiêu dùng</t>
         </is>
       </c>
       <c r="F614" s="9" t="n">
@@ -9310,7 +9310,7 @@
       <c r="D615" s="7" t="n"/>
       <c r="E615" s="8" t="inlineStr">
         <is>
-          <t>chuỗi bài pr giá rẻ</t>
+          <t>báo giá bài pr đàn ông magazine</t>
         </is>
       </c>
       <c r="F615" s="9" t="n">
@@ -9324,7 +9324,7 @@
       <c r="D616" s="7" t="n"/>
       <c r="E616" s="8" t="inlineStr">
         <is>
-          <t>bao giá bài pr dmtin</t>
+          <t>chi phi đăng bài pr trên các báo</t>
         </is>
       </c>
       <c r="F616" s="9" t="n">
@@ -9338,7 +9338,7 @@
       <c r="D617" s="7" t="n"/>
       <c r="E617" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr facebook</t>
+          <t>giá bài pr trên thời báo kinh tế</t>
         </is>
       </c>
       <c r="F617" s="9" t="n">
@@ -9352,7 +9352,7 @@
       <c r="D618" s="7" t="n"/>
       <c r="E618" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr online</t>
+          <t>giá đăng bài pr trên báo điện tử</t>
         </is>
       </c>
       <c r="F618" s="9" t="n">
@@ -9366,7 +9366,7 @@
       <c r="D619" s="7" t="n"/>
       <c r="E619" s="8" t="inlineStr">
         <is>
-          <t>gói mua bài pr giá rẻ</t>
+          <t>xem báo giá bài pr các báo ở đâu</t>
         </is>
       </c>
       <c r="F619" s="9" t="n">
@@ -9380,7 +9380,7 @@
       <c r="D620" s="7" t="n"/>
       <c r="E620" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr dantri</t>
+          <t>giá bài pr báo công thương online</t>
         </is>
       </c>
       <c r="F620" s="9" t="n">
@@ -9394,7 +9394,7 @@
       <c r="D621" s="7" t="n"/>
       <c r="E621" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo mtv</t>
+          <t>hệ thống book bài pr trên các báo</t>
         </is>
       </c>
       <c r="F621" s="9" t="n">
@@ -9408,7 +9408,7 @@
       <c r="D622" s="7" t="n"/>
       <c r="E622" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr kenh 14</t>
+          <t>giá bài viêt pr trên diadiemanuong</t>
         </is>
       </c>
       <c r="F622" s="9" t="n">
@@ -9422,7 +9422,7 @@
       <c r="D623" s="7" t="n"/>
       <c r="E623" s="8" t="inlineStr">
         <is>
-          <t>công ty booking bài pr</t>
+          <t>viết bài pr sản phẩm trên facebook</t>
         </is>
       </c>
       <c r="F623" s="9" t="n">
@@ -9436,7 +9436,7 @@
       <c r="D624" s="7" t="n"/>
       <c r="E624" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo ione</t>
+          <t>baáo giá bài pr báo xã luận điện tử</t>
         </is>
       </c>
       <c r="F624" s="9" t="n">
@@ -9450,7 +9450,7 @@
       <c r="D625" s="7" t="n"/>
       <c r="E625" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr ict news</t>
+          <t>báo giá bài pr trên doanh nhan plus</t>
         </is>
       </c>
       <c r="F625" s="9" t="n">
@@ -9464,7 +9464,7 @@
       <c r="D626" s="7" t="n"/>
       <c r="E626" s="8" t="inlineStr">
         <is>
-          <t>giá dang bài pr báo mới</t>
+          <t>book bài pr trên báo nước ngoài time</t>
         </is>
       </c>
       <c r="F626" s="9" t="n">
@@ -9478,7 +9478,7 @@
       <c r="D627" s="7" t="n"/>
       <c r="E627" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr báo điện tử</t>
+          <t>báo giá bài pr trên báo giấy lao độn</t>
         </is>
       </c>
       <c r="F627" s="9" t="n">
@@ -9492,7 +9492,7 @@
       <c r="D628" s="7" t="n"/>
       <c r="E628" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr báo vsao</t>
+          <t>báo giá bài pr trên thế giới văn hóa</t>
         </is>
       </c>
       <c r="F628" s="9" t="n">
@@ -9506,7 +9506,7 @@
       <c r="D629" s="7" t="n"/>
       <c r="E629" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr ione 2017</t>
+          <t>báo giá đăng bài pr trên báo quốc tế</t>
         </is>
       </c>
       <c r="F629" s="9" t="n">
@@ -9520,7 +9520,7 @@
       <c r="D630" s="7" t="n"/>
       <c r="E630" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr marrybaby</t>
+          <t>giá bài pr trên báo đẹp plus điện tử</t>
         </is>
       </c>
       <c r="F630" s="9" t="n">
@@ -9534,7 +9534,7 @@
       <c r="D631" s="7" t="n"/>
       <c r="E631" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr thanhnien</t>
+          <t>báo giá bài pr báo công thương online</t>
         </is>
       </c>
       <c r="F631" s="9" t="n">
@@ -9548,7 +9548,7 @@
       <c r="D632" s="7" t="n"/>
       <c r="E632" s="8" t="inlineStr">
         <is>
-          <t>các bài pr mảng giáo dục</t>
+          <t>bảng giá bài pr có chèn tvc quảng cáo</t>
         </is>
       </c>
       <c r="F632" s="9" t="n">
@@ -9562,7 +9562,7 @@
       <c r="D633" s="7" t="n"/>
       <c r="E633" s="8" t="inlineStr">
         <is>
-          <t>booking bài pr báo online</t>
+          <t>bảng giá đăng bài pr trên báo điện tử</t>
         </is>
       </c>
       <c r="F633" s="9" t="n">
@@ -9576,7 +9576,7 @@
       <c r="D634" s="7" t="n"/>
       <c r="E634" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr the leader</t>
+          <t>biểu giá bài pr báo công thương online</t>
         </is>
       </c>
       <c r="F634" s="9" t="n">
@@ -9590,7 +9590,7 @@
       <c r="D635" s="7" t="n"/>
       <c r="E635" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên foody</t>
+          <t>báo giá bài pr báo hoa học trò điện tử</t>
         </is>
       </c>
       <c r="F635" s="9" t="n">
@@ -9604,7 +9604,7 @@
       <c r="D636" s="7" t="n"/>
       <c r="E636" s="8" t="inlineStr">
         <is>
-          <t>giá 1 bài pr thông thường</t>
+          <t>báo giá bài pr thế giới văn hóa online</t>
         </is>
       </c>
       <c r="F636" s="9" t="n">
@@ -9618,7 +9618,7 @@
       <c r="D637" s="7" t="n"/>
       <c r="E637" s="8" t="inlineStr">
         <is>
-          <t>giá 1 bài pr trên elle.vn</t>
+          <t>báo giá bài pr tư vấn tiêu dùng online</t>
         </is>
       </c>
       <c r="F637" s="9" t="n">
@@ -9632,7 +9632,7 @@
       <c r="D638" s="7" t="n"/>
       <c r="E638" s="8" t="inlineStr">
         <is>
-          <t>giá 1 bài pr trên kenh 14</t>
+          <t>báo giá bài pr v economic times online</t>
         </is>
       </c>
       <c r="F638" s="9" t="n">
@@ -9646,7 +9646,7 @@
       <c r="D639" s="7" t="n"/>
       <c r="E639" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr báo lecourrier</t>
+          <t>cách viêt bài pr facebook cho sản phẩm</t>
         </is>
       </c>
       <c r="F639" s="9" t="n">
@@ -9660,7 +9660,7 @@
       <c r="D640" s="7" t="n"/>
       <c r="E640" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo thitkho</t>
+          <t>giá của một bài pr trung bình hiện nay</t>
         </is>
       </c>
       <c r="F640" s="9" t="n">
@@ -9674,7 +9674,7 @@
       <c r="D641" s="7" t="n"/>
       <c r="E641" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr tuoitre</t>
+          <t>những bài pr dịch vụ educate consumers</t>
         </is>
       </c>
       <c r="F641" s="9" t="n">
@@ -9688,7 +9688,7 @@
       <c r="D642" s="7" t="n"/>
       <c r="E642" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo vsao.com</t>
+          <t>biểu giá bài pr báo công thương điện tử</t>
         </is>
       </c>
       <c r="F642" s="9" t="n">
@@ -9702,7 +9702,7 @@
       <c r="D643" s="7" t="n"/>
       <c r="E643" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr bạch mỹ liên</t>
+          <t>agency book bài pr trên các báo nước ngoài</t>
         </is>
       </c>
       <c r="F643" s="9" t="n">
@@ -9716,7 +9716,7 @@
       <c r="D644" s="7" t="n"/>
       <c r="E644" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên báo mới</t>
+          <t>báo giá bài pr báo thê thao văn hóa online</t>
         </is>
       </c>
       <c r="F644" s="9" t="n">
@@ -9730,7 +9730,7 @@
       <c r="D645" s="7" t="n"/>
       <c r="E645" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr dantri.com.vn</t>
+          <t>cah đăng bài pr trên các trang báo điện tử</t>
         </is>
       </c>
       <c r="F645" s="9" t="n">
@@ -9744,7 +9744,7 @@
       <c r="D646" s="7" t="n"/>
       <c r="E646" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên kienthuc</t>
+          <t>báo giá bài pr trên thế giới văn hóa online</t>
         </is>
       </c>
       <c r="F646" s="9" t="n">
@@ -9758,7 +9758,7 @@
       <c r="D647" s="7" t="n"/>
       <c r="E647" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên báo bưu điện</t>
+          <t>báo giá bài pr trên doanh nhan cuoi tuan online</t>
         </is>
       </c>
       <c r="F647" s="9" t="n">
@@ -9766,13 +9766,13 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="7" t="n"/>
-      <c r="B648" s="7" t="n"/>
-      <c r="C648" s="7" t="n"/>
-      <c r="D648" s="7" t="n"/>
+      <c r="A648" s="10" t="n"/>
+      <c r="B648" s="10" t="n"/>
+      <c r="C648" s="10" t="n"/>
+      <c r="D648" s="10" t="n"/>
       <c r="E648" s="8" t="inlineStr">
         <is>
-          <t>giá đăng bài pr trên các báo</t>
+          <t>agency book bài pr được các báo online nước ngoài</t>
         </is>
       </c>
       <c r="F648" s="9" t="n">
@@ -9780,17 +9780,31 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="7" t="n"/>
-      <c r="B649" s="7" t="n"/>
-      <c r="C649" s="7" t="n"/>
-      <c r="D649" s="7" t="n"/>
-      <c r="E649" s="8" t="inlineStr">
-        <is>
-          <t>neên đăng bài pr lên báo nào</t>
-        </is>
-      </c>
-      <c r="F649" s="9" t="n">
-        <v>0</v>
+      <c r="A649" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B649" s="3" t="inlineStr">
+        <is>
+          <t>PR theo sản phẩm</t>
+        </is>
+      </c>
+      <c r="C649" s="3" t="inlineStr">
+        <is>
+          <t>Mục con trong /cach-viet-bai-pr-chuan-bao-chi/ + /bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="D649" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="E649" s="5" t="inlineStr">
+        <is>
+          <t>bài pr sản phẩm mới</t>
+        </is>
+      </c>
+      <c r="F649" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="650">
@@ -9800,11 +9814,11 @@
       <c r="D650" s="7" t="n"/>
       <c r="E650" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên báo điện tử</t>
+          <t>bài viết pr sản phẩm</t>
         </is>
       </c>
       <c r="F650" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="651">
@@ -9814,11 +9828,11 @@
       <c r="D651" s="7" t="n"/>
       <c r="E651" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên các báo lớn</t>
+          <t>viết bài pr sản phẩm</t>
         </is>
       </c>
       <c r="F651" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="652">
@@ -9828,11 +9842,11 @@
       <c r="D652" s="7" t="n"/>
       <c r="E652" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr vneconomy</t>
+          <t>bài viết pr về sản phẩm</t>
         </is>
       </c>
       <c r="F652" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="653">
@@ -9842,11 +9856,11 @@
       <c r="D653" s="7" t="n"/>
       <c r="E653" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên marrybaby</t>
+          <t>viết bài pr cho sản phẩm</t>
         </is>
       </c>
       <c r="F653" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="654">
@@ -9856,7 +9870,7 @@
       <c r="D654" s="7" t="n"/>
       <c r="E654" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên trang voh</t>
+          <t>bài pr cho page</t>
         </is>
       </c>
       <c r="F654" s="9" t="n">
@@ -9870,7 +9884,7 @@
       <c r="D655" s="7" t="n"/>
       <c r="E655" s="8" t="inlineStr">
         <is>
-          <t>cách book bài pr trên báo chí</t>
+          <t>bài pr về ca sỹ</t>
         </is>
       </c>
       <c r="F655" s="9" t="n">
@@ -9884,7 +9898,7 @@
       <c r="D656" s="7" t="n"/>
       <c r="E656" s="8" t="inlineStr">
         <is>
-          <t>cách đăng bài pr trên báo chí</t>
+          <t>bài pr về nội y</t>
         </is>
       </c>
       <c r="F656" s="9" t="n">
@@ -9898,7 +9912,7 @@
       <c r="D657" s="7" t="n"/>
       <c r="E657" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên docbao online</t>
+          <t>bài pr cho texas</t>
         </is>
       </c>
       <c r="F657" s="9" t="n">
@@ -9912,7 +9926,7 @@
       <c r="D658" s="7" t="n"/>
       <c r="E658" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr trên phụ nữ today</t>
+          <t>bài pr của acnes</t>
         </is>
       </c>
       <c r="F658" s="9" t="n">
@@ -9926,7 +9940,7 @@
       <c r="D659" s="7" t="n"/>
       <c r="E659" s="8" t="inlineStr">
         <is>
-          <t>báo giá booking bài pr admicro</t>
+          <t>bài pr về dasani</t>
         </is>
       </c>
       <c r="F659" s="9" t="n">
@@ -9940,7 +9954,7 @@
       <c r="D660" s="7" t="n"/>
       <c r="E660" s="8" t="inlineStr">
         <is>
-          <t>bảng giá đăng bài pr vneconomy</t>
+          <t>bài pr về món nga</t>
         </is>
       </c>
       <c r="F660" s="9" t="n">
@@ -9954,7 +9968,7 @@
       <c r="D661" s="7" t="n"/>
       <c r="E661" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên depplus online</t>
+          <t>bài pr về trị mụn</t>
         </is>
       </c>
       <c r="F661" s="9" t="n">
@@ -9968,7 +9982,7 @@
       <c r="D662" s="7" t="n"/>
       <c r="E662" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr phunuonline</t>
+          <t>các bài pr về seo</t>
         </is>
       </c>
       <c r="F662" s="9" t="n">
@@ -9982,7 +9996,7 @@
       <c r="D663" s="7" t="n"/>
       <c r="E663" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo xone điện tử</t>
+          <t>bài pr về nhân vật</t>
         </is>
       </c>
       <c r="F663" s="9" t="n">
@@ -9996,7 +10010,7 @@
       <c r="D664" s="7" t="n"/>
       <c r="E664" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr chính phủ online</t>
+          <t>bài pr về nước tẩy</t>
         </is>
       </c>
       <c r="F664" s="9" t="n">
@@ -10010,7 +10024,7 @@
       <c r="D665" s="7" t="n"/>
       <c r="E665" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr dan ong magazine</t>
+          <t>bài pr về phân bón</t>
         </is>
       </c>
       <c r="F665" s="9" t="n">
@@ -10024,7 +10038,7 @@
       <c r="D666" s="7" t="n"/>
       <c r="E666" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr tư vấn tiêu dùng</t>
+          <t>gói bài pr cho seo</t>
         </is>
       </c>
       <c r="F666" s="9" t="n">
@@ -10038,7 +10052,7 @@
       <c r="D667" s="7" t="n"/>
       <c r="E667" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr vneconomy online</t>
+          <t>bài pr cho gà texas</t>
         </is>
       </c>
       <c r="F667" s="9" t="n">
@@ -10052,7 +10066,7 @@
       <c r="D668" s="7" t="n"/>
       <c r="E668" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr đàn ông magazine</t>
+          <t>bài pr cho sản phẩm</t>
         </is>
       </c>
       <c r="F668" s="9" t="n">
@@ -10066,7 +10080,7 @@
       <c r="D669" s="7" t="n"/>
       <c r="E669" s="8" t="inlineStr">
         <is>
-          <t>bảng giá book bài pr trên ivivu</t>
+          <t>bài pr về nutiboost</t>
         </is>
       </c>
       <c r="F669" s="9" t="n">
@@ -10080,7 +10094,7 @@
       <c r="D670" s="7" t="n"/>
       <c r="E670" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr báo vsao điện tử</t>
+          <t>bài pr về nước uống</t>
         </is>
       </c>
       <c r="F670" s="9" t="n">
@@ -10094,7 +10108,7 @@
       <c r="D671" s="7" t="n"/>
       <c r="E671" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo mtvwe điện tử</t>
+          <t>bài viết pr của now</t>
         </is>
       </c>
       <c r="F671" s="9" t="n">
@@ -10108,7 +10122,7 @@
       <c r="D672" s="7" t="n"/>
       <c r="E672" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên thanhnien.vn</t>
+          <t>bài viết pr cho shop</t>
         </is>
       </c>
       <c r="F672" s="9" t="n">
@@ -10122,7 +10136,7 @@
       <c r="D673" s="7" t="n"/>
       <c r="E673" s="8" t="inlineStr">
         <is>
-          <t>chi phi đăng bài pr trên các báo</t>
+          <t>bài viết pr về durex</t>
         </is>
       </c>
       <c r="F673" s="9" t="n">
@@ -10136,7 +10150,7 @@
       <c r="D674" s="7" t="n"/>
       <c r="E674" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr báo lecourrier online</t>
+          <t>nghiên cứu về bài pr</t>
         </is>
       </c>
       <c r="F674" s="9" t="n">
@@ -10150,7 +10164,7 @@
       <c r="D675" s="7" t="n"/>
       <c r="E675" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên thời báo kinh tế</t>
+          <t>bài pr về nước dasani</t>
         </is>
       </c>
       <c r="F675" s="9" t="n">
@@ -10164,7 +10178,7 @@
       <c r="D676" s="7" t="n"/>
       <c r="E676" s="8" t="inlineStr">
         <is>
-          <t>giá bài quảng cáo pr basomoi.com</t>
+          <t>bài viết pr của now.vn</t>
         </is>
       </c>
       <c r="F676" s="9" t="n">
@@ -10178,7 +10192,7 @@
       <c r="D677" s="7" t="n"/>
       <c r="E677" s="8" t="inlineStr">
         <is>
-          <t>giá đăng bài pr trên báo điện tử</t>
+          <t>từ khóa seo cho bài pr</t>
         </is>
       </c>
       <c r="F677" s="9" t="n">
@@ -10192,7 +10206,7 @@
       <c r="D678" s="7" t="n"/>
       <c r="E678" s="8" t="inlineStr">
         <is>
-          <t>xem báo giá bài pr các báo ở đâu</t>
+          <t>viết bài pr về món nga</t>
         </is>
       </c>
       <c r="F678" s="9" t="n">
@@ -10206,7 +10220,7 @@
       <c r="D679" s="7" t="n"/>
       <c r="E679" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr thethaovanhoa</t>
+          <t>bài pr về sữa nutiboost</t>
         </is>
       </c>
       <c r="F679" s="9" t="n">
@@ -10220,7 +10234,7 @@
       <c r="D680" s="7" t="n"/>
       <c r="E680" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo mtv we điện tử</t>
+          <t>bài viết pr về nha trang</t>
         </is>
       </c>
       <c r="F680" s="9" t="n">
@@ -10234,7 +10248,7 @@
       <c r="D681" s="7" t="n"/>
       <c r="E681" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr dantri.com.vn 2017</t>
+          <t>các bài viết pr sản phẩm</t>
         </is>
       </c>
       <c r="F681" s="9" t="n">
@@ -10248,7 +10262,7 @@
       <c r="D682" s="7" t="n"/>
       <c r="E682" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr báo công thương online</t>
+          <t>kế hoạch viết cho bài pr</t>
         </is>
       </c>
       <c r="F682" s="9" t="n">
@@ -10262,7 +10276,7 @@
       <c r="D683" s="7" t="n"/>
       <c r="E683" s="8" t="inlineStr">
         <is>
-          <t>hệ thống book bài pr trên các báo</t>
+          <t>viết bài pr sản phẩm mới</t>
         </is>
       </c>
       <c r="F683" s="9" t="n">
@@ -10276,7 +10290,7 @@
       <c r="D684" s="7" t="n"/>
       <c r="E684" s="8" t="inlineStr">
         <is>
-          <t>baáo giá lên bài pr vietnamexpress</t>
+          <t>viết bài pr cho cảng biển</t>
         </is>
       </c>
       <c r="F684" s="9" t="n">
@@ -10290,7 +10304,7 @@
       <c r="D685" s="7" t="n"/>
       <c r="E685" s="8" t="inlineStr">
         <is>
-          <t>giá bài quảng cáo pr trên tinxe.vn</t>
+          <t>bài báo pr về sàn văn phòng</t>
         </is>
       </c>
       <c r="F685" s="9" t="n">
@@ -10304,7 +10318,7 @@
       <c r="D686" s="7" t="n"/>
       <c r="E686" s="8" t="inlineStr">
         <is>
-          <t>giá bài viêt pr trên diadiemanuong</t>
+          <t>bài pr về digital marketing</t>
         </is>
       </c>
       <c r="F686" s="9" t="n">
@@ -10318,7 +10332,7 @@
       <c r="D687" s="7" t="n"/>
       <c r="E687" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr sản phẩm trên facebook</t>
+          <t>các bài viết pr về rong nho</t>
         </is>
       </c>
       <c r="F687" s="9" t="n">
@@ -10332,7 +10346,7 @@
       <c r="D688" s="7" t="n"/>
       <c r="E688" s="8" t="inlineStr">
         <is>
-          <t>baáo giá bài pr báo xã luận điện tử</t>
+          <t>viết bài pr cho studio cưới</t>
         </is>
       </c>
       <c r="F688" s="9" t="n">
@@ -10346,7 +10360,7 @@
       <c r="D689" s="7" t="n"/>
       <c r="E689" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên doanh nhan plus</t>
+          <t>vieết bài pr sao cho thu hút</t>
         </is>
       </c>
       <c r="F689" s="9" t="n">
@@ -10360,7 +10374,7 @@
       <c r="D690" s="7" t="n"/>
       <c r="E690" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên kienthucdoisong</t>
+          <t>cau trúc viêt bài pr sản phẩm</t>
         </is>
       </c>
       <c r="F690" s="9" t="n">
@@ -10374,7 +10388,7 @@
       <c r="D691" s="7" t="n"/>
       <c r="E691" s="8" t="inlineStr">
         <is>
-          <t>book bài pr trên báo nước ngoài time</t>
+          <t>bài pr cho sản phẩm mới ra mắt</t>
         </is>
       </c>
       <c r="F691" s="9" t="n">
@@ -10388,7 +10402,7 @@
       <c r="D692" s="7" t="n"/>
       <c r="E692" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên báo giấy lao độn</t>
+          <t>bài pr cho trang sức kim cương</t>
         </is>
       </c>
       <c r="F692" s="9" t="n">
@@ -10402,7 +10416,7 @@
       <c r="D693" s="7" t="n"/>
       <c r="E693" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên thế giới văn hóa</t>
+          <t>viết bài pr sản phẩm kiếm tiền</t>
         </is>
       </c>
       <c r="F693" s="9" t="n">
@@ -10416,7 +10430,7 @@
       <c r="D694" s="7" t="n"/>
       <c r="E694" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên báo quốc tế</t>
+          <t>bài pr cho sản phẩm dành cho pg</t>
         </is>
       </c>
       <c r="F694" s="9" t="n">
@@ -10430,7 +10444,7 @@
       <c r="D695" s="7" t="n"/>
       <c r="E695" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên báo đẹp plus điện tử</t>
+          <t>bài viết pr branding cho bán lẻ</t>
         </is>
       </c>
       <c r="F695" s="9" t="n">
@@ -10444,7 +10458,7 @@
       <c r="D696" s="7" t="n"/>
       <c r="E696" s="8" t="inlineStr">
         <is>
-          <t>giá bài pr trên trang infonet online</t>
+          <t>caác bài pr cho dầu gội trị gàu</t>
         </is>
       </c>
       <c r="F696" s="9" t="n">
@@ -10458,7 +10472,7 @@
       <c r="D697" s="7" t="n"/>
       <c r="E697" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo công thương online</t>
+          <t>sản phẩm mới của samsung bài pr</t>
         </is>
       </c>
       <c r="F697" s="9" t="n">
@@ -10472,7 +10486,7 @@
       <c r="D698" s="7" t="n"/>
       <c r="E698" s="8" t="inlineStr">
         <is>
-          <t>báo giá đăng bài pr trên baoquocte.vn</t>
+          <t>viết bài pr về địa điểm tổ chức</t>
         </is>
       </c>
       <c r="F698" s="9" t="n">
@@ -10486,7 +10500,7 @@
       <c r="D699" s="7" t="n"/>
       <c r="E699" s="8" t="inlineStr">
         <is>
-          <t>bảng giá bài pr có chèn tvc quảng cáo</t>
+          <t>bài pr của kols viết như thế nào</t>
         </is>
       </c>
       <c r="F699" s="9" t="n">
@@ -10500,7 +10514,7 @@
       <c r="D700" s="7" t="n"/>
       <c r="E700" s="8" t="inlineStr">
         <is>
-          <t>bảng giá đăng bài pr trên báo điện tử</t>
+          <t>caácc bài pr cho dầu gội trị gàu</t>
         </is>
       </c>
       <c r="F700" s="9" t="n">
@@ -10514,7 +10528,7 @@
       <c r="D701" s="7" t="n"/>
       <c r="E701" s="8" t="inlineStr">
         <is>
-          <t>biểu giá bài pr báo công thương online</t>
+          <t>cách làm 1 bài pr cho 1 sản phẩm</t>
         </is>
       </c>
       <c r="F701" s="9" t="n">
@@ -10528,7 +10542,7 @@
       <c r="D702" s="7" t="n"/>
       <c r="E702" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo hoa học trò điện tử</t>
+          <t>bài viết pr cho muối tôm tây ninh</t>
         </is>
       </c>
       <c r="F702" s="9" t="n">
@@ -10542,7 +10556,7 @@
       <c r="D703" s="7" t="n"/>
       <c r="E703" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr thế giới văn hóa online</t>
+          <t>bài viết pr sản phẩm của học vien</t>
         </is>
       </c>
       <c r="F703" s="9" t="n">
@@ -10556,7 +10570,7 @@
       <c r="D704" s="7" t="n"/>
       <c r="E704" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr tư vấn tiêu dùng online</t>
+          <t>các bài viết pr sản phẩm handmade</t>
         </is>
       </c>
       <c r="F704" s="9" t="n">
@@ -10570,7 +10584,7 @@
       <c r="D705" s="7" t="n"/>
       <c r="E705" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr v economic times online</t>
+          <t>bài viết pr về đồ nội thất cao cấp</t>
         </is>
       </c>
       <c r="F705" s="9" t="n">
@@ -10584,7 +10598,7 @@
       <c r="D706" s="7" t="n"/>
       <c r="E706" s="8" t="inlineStr">
         <is>
-          <t>cách viêt bài pr facebook cho sản phẩm</t>
+          <t>các bài viết pr về bác sĩ hàn quốc</t>
         </is>
       </c>
       <c r="F706" s="9" t="n">
@@ -10598,7 +10612,7 @@
       <c r="D707" s="7" t="n"/>
       <c r="E707" s="8" t="inlineStr">
         <is>
-          <t>giá bài quảng cáo pr trên autobikes.vn</t>
+          <t>cơ sở lý thuyết về bài pr của kols</t>
         </is>
       </c>
       <c r="F707" s="9" t="n">
@@ -10612,7 +10626,7 @@
       <c r="D708" s="7" t="n"/>
       <c r="E708" s="8" t="inlineStr">
         <is>
-          <t>giá của một bài pr trung bình hiện nay</t>
+          <t>tieu đề bài pr giới thiệu sản phẩm</t>
         </is>
       </c>
       <c r="F708" s="9" t="n">
@@ -10626,7 +10640,7 @@
       <c r="D709" s="7" t="n"/>
       <c r="E709" s="8" t="inlineStr">
         <is>
-          <t>những bài pr dịch vụ educate consumers</t>
+          <t>viết bài pr cho phụ gia ngành giấy</t>
         </is>
       </c>
       <c r="F709" s="9" t="n">
@@ -10640,7 +10654,7 @@
       <c r="D710" s="7" t="n"/>
       <c r="E710" s="8" t="inlineStr">
         <is>
-          <t>biểu giá bài pr báo công thương điện tử</t>
+          <t>những bài viết pr cho ngày hội sách</t>
         </is>
       </c>
       <c r="F710" s="9" t="n">
@@ -10654,7 +10668,7 @@
       <c r="D711" s="7" t="n"/>
       <c r="E711" s="8" t="inlineStr">
         <is>
-          <t>hỗ trợ đăng bài pr trên nhịp sống sendo</t>
+          <t>xác định công chúng của bài viết pr</t>
         </is>
       </c>
       <c r="F711" s="9" t="n">
@@ -10668,7 +10682,7 @@
       <c r="D712" s="7" t="n"/>
       <c r="E712" s="8" t="inlineStr">
         <is>
-          <t>agency book bài pr trên các báo nước ngoài</t>
+          <t>xây dựng thông điệp của bài viết pr</t>
         </is>
       </c>
       <c r="F712" s="9" t="n">
@@ -10682,7 +10696,7 @@
       <c r="D713" s="7" t="n"/>
       <c r="E713" s="8" t="inlineStr">
         <is>
-          <t>baáo giá gói đăng bài pr trên ngôi sao.net</t>
+          <t>bài pr về bộ phận chăm sóc khách hàng</t>
         </is>
       </c>
       <c r="F713" s="9" t="n">
@@ -10696,7 +10710,7 @@
       <c r="D714" s="7" t="n"/>
       <c r="E714" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr báo thê thao văn hóa online</t>
+          <t>bài viết pr quyên góp áo trắng cho em</t>
         </is>
       </c>
       <c r="F714" s="9" t="n">
@@ -10710,7 +10724,7 @@
       <c r="D715" s="7" t="n"/>
       <c r="E715" s="8" t="inlineStr">
         <is>
-          <t>cah đăng bài pr trên các trang báo điện tử</t>
+          <t>lượt view trung bình cho bài pr hieeu</t>
         </is>
       </c>
       <c r="F715" s="9" t="n">
@@ -10724,7 +10738,7 @@
       <c r="D716" s="7" t="n"/>
       <c r="E716" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên thế giới văn hóa online</t>
+          <t>neên đăn bài pr sản phẩm trên báo nào</t>
         </is>
       </c>
       <c r="F716" s="9" t="n">
@@ -10738,7 +10752,7 @@
       <c r="D717" s="7" t="n"/>
       <c r="E717" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên trang thegioivanhoa.net</t>
+          <t>bài biết pr cho sản phẩm nước giải khát</t>
         </is>
       </c>
       <c r="F717" s="9" t="n">
@@ -10752,7 +10766,7 @@
       <c r="D718" s="7" t="n"/>
       <c r="E718" s="8" t="inlineStr">
         <is>
-          <t>giá chạy bài pr trên vneconomy là bao nhiêu</t>
+          <t>bài viết pr cho sản phẩm nước giải khát</t>
         </is>
       </c>
       <c r="F718" s="9" t="n">
@@ -10766,7 +10780,7 @@
       <c r="D719" s="7" t="n"/>
       <c r="E719" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên trang thế giới văn hóa.net</t>
+          <t>viết bài pr sản phẩm thu hút khách hàng</t>
         </is>
       </c>
       <c r="F719" s="9" t="n">
@@ -10780,7 +10794,7 @@
       <c r="D720" s="7" t="n"/>
       <c r="E720" s="8" t="inlineStr">
         <is>
-          <t>báo giá bài pr trên doanh nhan cuoi tuan online</t>
+          <t>caác bài viết pr cho các dầu gội trị gàu</t>
         </is>
       </c>
       <c r="F720" s="9" t="n">
@@ -10788,13 +10802,13 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" s="10" t="n"/>
-      <c r="B721" s="10" t="n"/>
-      <c r="C721" s="10" t="n"/>
-      <c r="D721" s="10" t="n"/>
+      <c r="A721" s="7" t="n"/>
+      <c r="B721" s="7" t="n"/>
+      <c r="C721" s="7" t="n"/>
+      <c r="D721" s="7" t="n"/>
       <c r="E721" s="8" t="inlineStr">
         <is>
-          <t>agency book bài pr được các báo online nước ngoài</t>
+          <t>viết bài pr món ăn cho người mới bắt đầu</t>
         </is>
       </c>
       <c r="F721" s="9" t="n">
@@ -10802,45 +10816,45 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" s="12" t="inlineStr">
+      <c r="A722" s="10" t="n"/>
+      <c r="B722" s="10" t="n"/>
+      <c r="C722" s="10" t="n"/>
+      <c r="D722" s="10" t="n"/>
+      <c r="E722" s="8" t="inlineStr">
+        <is>
+          <t>những bài viết pr cho trung tâm tiếng anh</t>
+        </is>
+      </c>
+      <c r="F722" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="12" t="inlineStr">
         <is>
           <t>Đã có bài</t>
         </is>
       </c>
-      <c r="B722" s="3" t="inlineStr">
-        <is>
-          <t>PR theo sản phẩm</t>
-        </is>
-      </c>
-      <c r="C722" s="3" t="inlineStr">
-        <is>
-          <t>Mục con trong /cach-viet-bai-pr-chuan-bao-chi/ + /bai-pr-mau/</t>
-        </is>
-      </c>
-      <c r="D722" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="E722" s="5" t="inlineStr">
-        <is>
-          <t>bài pr sản phẩm mới</t>
-        </is>
-      </c>
-      <c r="F722" s="6" t="n">
+      <c r="B723" s="3" t="inlineStr">
+        <is>
+          <t>PR doanh nghiệp / thương hiệu</t>
+        </is>
+      </c>
+      <c r="C723" s="3" t="inlineStr">
+        <is>
+          <t>/bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="D723" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E723" s="5" t="inlineStr">
+        <is>
+          <t>bài pr thương hiệu</t>
+        </is>
+      </c>
+      <c r="F723" s="6" t="n">
         <v>30</v>
-      </c>
-    </row>
-    <row r="723">
-      <c r="A723" s="7" t="n"/>
-      <c r="B723" s="7" t="n"/>
-      <c r="C723" s="7" t="n"/>
-      <c r="D723" s="7" t="n"/>
-      <c r="E723" s="8" t="inlineStr">
-        <is>
-          <t>bài viết pr sản phẩm</t>
-        </is>
-      </c>
-      <c r="F723" s="9" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="724">
@@ -10850,11 +10864,11 @@
       <c r="D724" s="7" t="n"/>
       <c r="E724" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr sản phẩm</t>
+          <t>bài pr doanh nghiệp</t>
         </is>
       </c>
       <c r="F724" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="725">
@@ -10864,7 +10878,7 @@
       <c r="D725" s="7" t="n"/>
       <c r="E725" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr về sản phẩm</t>
+          <t>bài pr cho doanh nghiệp</t>
         </is>
       </c>
       <c r="F725" s="9" t="n">
@@ -10878,7 +10892,7 @@
       <c r="D726" s="7" t="n"/>
       <c r="E726" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho sản phẩm</t>
+          <t>viết bài pr cho doanh nghiệp</t>
         </is>
       </c>
       <c r="F726" s="9" t="n">
@@ -10892,7 +10906,7 @@
       <c r="D727" s="7" t="n"/>
       <c r="E727" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho sản phẩm</t>
+          <t>bài pr đại lý</t>
         </is>
       </c>
       <c r="F727" s="9" t="n">
@@ -10906,7 +10920,7 @@
       <c r="D728" s="7" t="n"/>
       <c r="E728" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr sản phẩm</t>
+          <t>bài pr về công ty</t>
         </is>
       </c>
       <c r="F728" s="9" t="n">
@@ -10920,7 +10934,7 @@
       <c r="D729" s="7" t="n"/>
       <c r="E729" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr sản phẩm mới</t>
+          <t>bài pr về tập đoàn</t>
         </is>
       </c>
       <c r="F729" s="9" t="n">
@@ -10934,7 +10948,7 @@
       <c r="D730" s="7" t="n"/>
       <c r="E730" s="8" t="inlineStr">
         <is>
-          <t>cau trúc viêt bài pr sản phẩm</t>
+          <t>bài pr đại lý ô tô</t>
         </is>
       </c>
       <c r="F730" s="9" t="n">
@@ -10948,7 +10962,7 @@
       <c r="D731" s="7" t="n"/>
       <c r="E731" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho sản phẩm mới ra mắt</t>
+          <t>viết bài pr công ty</t>
         </is>
       </c>
       <c r="F731" s="9" t="n">
@@ -10962,7 +10976,7 @@
       <c r="D732" s="7" t="n"/>
       <c r="E732" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr sản phẩm kiếm tiền</t>
+          <t>bài pr từ thương hiệu</t>
         </is>
       </c>
       <c r="F732" s="9" t="n">
@@ -10976,7 +10990,7 @@
       <c r="D733" s="7" t="n"/>
       <c r="E733" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho sản phẩm dành cho pg</t>
+          <t>bài pr về doanh nghiệp</t>
         </is>
       </c>
       <c r="F733" s="9" t="n">
@@ -10990,7 +11004,7 @@
       <c r="D734" s="7" t="n"/>
       <c r="E734" s="8" t="inlineStr">
         <is>
-          <t>sản phẩm mới của samsung bài pr</t>
+          <t>bài viết pr về công ty</t>
         </is>
       </c>
       <c r="F734" s="9" t="n">
@@ -11004,7 +11018,7 @@
       <c r="D735" s="7" t="n"/>
       <c r="E735" s="8" t="inlineStr">
         <is>
-          <t>cách làm 1 bài pr cho 1 sản phẩm</t>
+          <t>viết bài pr doanh nghiệp</t>
         </is>
       </c>
       <c r="F735" s="9" t="n">
@@ -11018,7 +11032,7 @@
       <c r="D736" s="7" t="n"/>
       <c r="E736" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr sản phẩm của học vien</t>
+          <t>viết bài pr công ty honda</t>
         </is>
       </c>
       <c r="F736" s="9" t="n">
@@ -11032,7 +11046,7 @@
       <c r="D737" s="7" t="n"/>
       <c r="E737" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr sản phẩm handmade</t>
+          <t>viết bài pr công ty với 200 từ</t>
         </is>
       </c>
       <c r="F737" s="9" t="n">
@@ -11046,7 +11060,7 @@
       <c r="D738" s="7" t="n"/>
       <c r="E738" s="8" t="inlineStr">
         <is>
-          <t>tieu đề bài pr giới thiệu sản phẩm</t>
+          <t>bài viết pr doanh nghiệp may mặc</t>
         </is>
       </c>
       <c r="F738" s="9" t="n">
@@ -11060,7 +11074,7 @@
       <c r="D739" s="7" t="n"/>
       <c r="E739" s="8" t="inlineStr">
         <is>
-          <t>neên đăn bài pr sản phẩm trên báo nào</t>
+          <t>bài pr cho công ty thiết kế nội thất</t>
         </is>
       </c>
       <c r="F739" s="9" t="n">
@@ -11074,7 +11088,7 @@
       <c r="D740" s="7" t="n"/>
       <c r="E740" s="8" t="inlineStr">
         <is>
-          <t>bài biết pr cho sản phẩm nước giải khát</t>
+          <t>có được bán bài pr doanh nghiệp không</t>
         </is>
       </c>
       <c r="F740" s="9" t="n">
@@ -11088,7 +11102,7 @@
       <c r="D741" s="7" t="n"/>
       <c r="E741" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr cho sản phẩm nước giải khát</t>
+          <t>viết bài pr cho thương hiệu giày nike</t>
         </is>
       </c>
       <c r="F741" s="9" t="n">
@@ -11096,13 +11110,13 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" s="10" t="n"/>
-      <c r="B742" s="10" t="n"/>
-      <c r="C742" s="10" t="n"/>
-      <c r="D742" s="10" t="n"/>
+      <c r="A742" s="7" t="n"/>
+      <c r="B742" s="7" t="n"/>
+      <c r="C742" s="7" t="n"/>
+      <c r="D742" s="7" t="n"/>
       <c r="E742" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr sản phẩm thu hút khách hàng</t>
+          <t>hướng dẫn viết bài pr cho doanh nghiệp</t>
         </is>
       </c>
       <c r="F742" s="9" t="n">
@@ -11110,31 +11124,17 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B743" s="3" t="inlineStr">
-        <is>
-          <t>PR doanh nghiệp / thương hiệu</t>
-        </is>
-      </c>
-      <c r="C743" s="3" t="inlineStr">
-        <is>
-          <t>/bai-pr-mau/</t>
-        </is>
-      </c>
-      <c r="D743" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E743" s="5" t="inlineStr">
-        <is>
-          <t>bài pr thương hiệu</t>
-        </is>
-      </c>
-      <c r="F743" s="6" t="n">
-        <v>30</v>
+      <c r="A743" s="7" t="n"/>
+      <c r="B743" s="7" t="n"/>
+      <c r="C743" s="7" t="n"/>
+      <c r="D743" s="7" t="n"/>
+      <c r="E743" s="8" t="inlineStr">
+        <is>
+          <t>nguyeên tắc iets một bài pr thương hiệu</t>
+        </is>
+      </c>
+      <c r="F743" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="744">
@@ -11144,11 +11144,11 @@
       <c r="D744" s="7" t="n"/>
       <c r="E744" s="8" t="inlineStr">
         <is>
-          <t>bài pr doanh nghiệp</t>
+          <t>viết bài pr cho thương hiệu công ty con</t>
         </is>
       </c>
       <c r="F744" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745">
@@ -11158,39 +11158,53 @@
       <c r="D745" s="7" t="n"/>
       <c r="E745" s="8" t="inlineStr">
         <is>
-          <t>bài pr cho doanh nghiệp</t>
+          <t>bài viết pr tăng độ nhận diện thương hiệu</t>
         </is>
       </c>
       <c r="F745" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
-      <c r="A746" s="7" t="n"/>
-      <c r="B746" s="7" t="n"/>
-      <c r="C746" s="7" t="n"/>
-      <c r="D746" s="7" t="n"/>
+      <c r="A746" s="10" t="n"/>
+      <c r="B746" s="10" t="n"/>
+      <c r="C746" s="10" t="n"/>
+      <c r="D746" s="10" t="n"/>
       <c r="E746" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho doanh nghiệp</t>
+          <t>viết bài pr cho thương hiệu cho doanh nghiệp</t>
         </is>
       </c>
       <c r="F746" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="747">
-      <c r="A747" s="7" t="n"/>
-      <c r="B747" s="7" t="n"/>
-      <c r="C747" s="7" t="n"/>
-      <c r="D747" s="7" t="n"/>
-      <c r="E747" s="8" t="inlineStr">
-        <is>
-          <t>bài pr từ thương hiệu</t>
-        </is>
-      </c>
-      <c r="F747" s="9" t="n">
-        <v>0</v>
+      <c r="A747" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B747" s="3" t="inlineStr">
+        <is>
+          <t>Bài PR là gì / định nghĩa</t>
+        </is>
+      </c>
+      <c r="C747" s="3" t="inlineStr">
+        <is>
+          <t>/bai-pr-la-gi/</t>
+        </is>
+      </c>
+      <c r="D747" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E747" s="5" t="inlineStr">
+        <is>
+          <t>viết bài pr là gì</t>
+        </is>
+      </c>
+      <c r="F747" s="6" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="748">
@@ -11200,11 +11214,11 @@
       <c r="D748" s="7" t="n"/>
       <c r="E748" s="8" t="inlineStr">
         <is>
-          <t>bài pr về doanh nghiệp</t>
+          <t>bài pr là gì</t>
         </is>
       </c>
       <c r="F748" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="749">
@@ -11214,7 +11228,7 @@
       <c r="D749" s="7" t="n"/>
       <c r="E749" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr doanh nghiệp</t>
+          <t>lead bài pr là gì</t>
         </is>
       </c>
       <c r="F749" s="9" t="n">
@@ -11228,7 +11242,7 @@
       <c r="D750" s="7" t="n"/>
       <c r="E750" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr doanh nghiệp may mặc</t>
+          <t>viết bài pr la gì</t>
         </is>
       </c>
       <c r="F750" s="9" t="n">
@@ -11242,7 +11256,7 @@
       <c r="D751" s="7" t="n"/>
       <c r="E751" s="8" t="inlineStr">
         <is>
-          <t>có được bán bài pr doanh nghiệp không</t>
+          <t>đăng bài pr là gì</t>
         </is>
       </c>
       <c r="F751" s="9" t="n">
@@ -11256,7 +11270,7 @@
       <c r="D752" s="7" t="n"/>
       <c r="E752" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho thương hiệu giày nike</t>
+          <t>dđịnh nghĩa bài pr</t>
         </is>
       </c>
       <c r="F752" s="9" t="n">
@@ -11270,7 +11284,7 @@
       <c r="D753" s="7" t="n"/>
       <c r="E753" s="8" t="inlineStr">
         <is>
-          <t>hướng dẫn viết bài pr cho doanh nghiệp</t>
+          <t>thế nào là bài báo pr</t>
         </is>
       </c>
       <c r="F753" s="9" t="n">
@@ -11284,7 +11298,7 @@
       <c r="D754" s="7" t="n"/>
       <c r="E754" s="8" t="inlineStr">
         <is>
-          <t>nguyeên tắc iets một bài pr thương hiệu</t>
+          <t>trình bày khái niệm pr</t>
         </is>
       </c>
       <c r="F754" s="9" t="n">
@@ -11298,7 +11312,7 @@
       <c r="D755" s="7" t="n"/>
       <c r="E755" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho thương hiệu công ty con</t>
+          <t>viết bài pr nghĩa là gì</t>
         </is>
       </c>
       <c r="F755" s="9" t="n">
@@ -11312,7 +11326,7 @@
       <c r="D756" s="7" t="n"/>
       <c r="E756" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr tăng độ nhận diện thương hiệu</t>
+          <t>bài viết pr tiếng anh là gì</t>
         </is>
       </c>
       <c r="F756" s="9" t="n">
@@ -11320,13 +11334,13 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" s="10" t="n"/>
-      <c r="B757" s="10" t="n"/>
-      <c r="C757" s="10" t="n"/>
-      <c r="D757" s="10" t="n"/>
+      <c r="A757" s="7" t="n"/>
+      <c r="B757" s="7" t="n"/>
+      <c r="C757" s="7" t="n"/>
+      <c r="D757" s="7" t="n"/>
       <c r="E757" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr cho thương hiệu cho doanh nghiệp</t>
+          <t>viết bài pr editorial là gì</t>
         </is>
       </c>
       <c r="F757" s="9" t="n">
@@ -11334,31 +11348,17 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B758" s="3" t="inlineStr">
-        <is>
-          <t>Bài PR là gì / định nghĩa</t>
-        </is>
-      </c>
-      <c r="C758" s="3" t="inlineStr">
-        <is>
-          <t>/bai-pr-la-gi/</t>
-        </is>
-      </c>
-      <c r="D758" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E758" s="5" t="inlineStr">
-        <is>
-          <t>viết bài pr là gì</t>
-        </is>
-      </c>
-      <c r="F758" s="6" t="n">
-        <v>30</v>
+      <c r="A758" s="7" t="n"/>
+      <c r="B758" s="7" t="n"/>
+      <c r="C758" s="7" t="n"/>
+      <c r="D758" s="7" t="n"/>
+      <c r="E758" s="8" t="inlineStr">
+        <is>
+          <t>sabo là gì trong viết bài pr</t>
+        </is>
+      </c>
+      <c r="F758" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="759">
@@ -11368,11 +11368,11 @@
       <c r="D759" s="7" t="n"/>
       <c r="E759" s="8" t="inlineStr">
         <is>
-          <t>bài pr là gì</t>
+          <t>bài pr có chân dung quảng cáo là gì</t>
         </is>
       </c>
       <c r="F759" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="760">
@@ -11382,7 +11382,7 @@
       <c r="D760" s="7" t="n"/>
       <c r="E760" s="8" t="inlineStr">
         <is>
-          <t>lead bài pr là gì</t>
+          <t>diễn văn bài phát biểu là gì trong pr</t>
         </is>
       </c>
       <c r="F760" s="9" t="n">
@@ -11390,13 +11390,13 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" s="7" t="n"/>
-      <c r="B761" s="7" t="n"/>
-      <c r="C761" s="7" t="n"/>
-      <c r="D761" s="7" t="n"/>
+      <c r="A761" s="10" t="n"/>
+      <c r="B761" s="10" t="n"/>
+      <c r="C761" s="10" t="n"/>
+      <c r="D761" s="10" t="n"/>
       <c r="E761" s="8" t="inlineStr">
         <is>
-          <t>đăng bài pr là gì</t>
+          <t>bài pr có chân dung quảng cáo là gì marketing</t>
         </is>
       </c>
       <c r="F761" s="9" t="n">
@@ -11404,17 +11404,31 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="7" t="n"/>
-      <c r="B762" s="7" t="n"/>
-      <c r="C762" s="7" t="n"/>
-      <c r="D762" s="7" t="n"/>
-      <c r="E762" s="8" t="inlineStr">
-        <is>
-          <t>viết bài pr nghĩa là gì</t>
-        </is>
-      </c>
-      <c r="F762" s="9" t="n">
-        <v>0</v>
+      <c r="A762" s="12" t="inlineStr">
+        <is>
+          <t>Đã có bài</t>
+        </is>
+      </c>
+      <c r="B762" s="3" t="inlineStr">
+        <is>
+          <t>PR theo sự kiện</t>
+        </is>
+      </c>
+      <c r="C762" s="3" t="inlineStr">
+        <is>
+          <t>Mục con trong /bai-pr-mau/</t>
+        </is>
+      </c>
+      <c r="D762" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E762" s="5" t="inlineStr">
+        <is>
+          <t>viết bài pr cho sự kiện</t>
+        </is>
+      </c>
+      <c r="F762" s="6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="763">
@@ -11424,7 +11438,7 @@
       <c r="D763" s="7" t="n"/>
       <c r="E763" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr tiếng anh là gì</t>
+          <t>bài pr sự kiện</t>
         </is>
       </c>
       <c r="F763" s="9" t="n">
@@ -11438,7 +11452,7 @@
       <c r="D764" s="7" t="n"/>
       <c r="E764" s="8" t="inlineStr">
         <is>
-          <t>viết bài pr editorial là gì</t>
+          <t>bài pr sau sự kiện</t>
         </is>
       </c>
       <c r="F764" s="9" t="n">
@@ -11452,7 +11466,7 @@
       <c r="D765" s="7" t="n"/>
       <c r="E765" s="8" t="inlineStr">
         <is>
-          <t>sabo là gì trong viết bài pr</t>
+          <t>bài viết pr sự kiện</t>
         </is>
       </c>
       <c r="F765" s="9" t="n">
@@ -11466,7 +11480,7 @@
       <c r="D766" s="7" t="n"/>
       <c r="E766" s="8" t="inlineStr">
         <is>
-          <t>bài pr có chân dung quảng cáo là gì</t>
+          <t>bài viết pr sự kiện ô tô</t>
         </is>
       </c>
       <c r="F766" s="9" t="n">
@@ -11480,7 +11494,7 @@
       <c r="D767" s="7" t="n"/>
       <c r="E767" s="8" t="inlineStr">
         <is>
-          <t>diễn văn bài phát biểu là gì trong pr</t>
+          <t>caác bài viết pr sự kiện</t>
         </is>
       </c>
       <c r="F767" s="9" t="n">
@@ -11488,13 +11502,13 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" s="10" t="n"/>
-      <c r="B768" s="10" t="n"/>
-      <c r="C768" s="10" t="n"/>
-      <c r="D768" s="10" t="n"/>
+      <c r="A768" s="7" t="n"/>
+      <c r="B768" s="7" t="n"/>
+      <c r="C768" s="7" t="n"/>
+      <c r="D768" s="7" t="n"/>
       <c r="E768" s="8" t="inlineStr">
         <is>
-          <t>bài pr có chân dung quảng cáo là gì marketing</t>
+          <t>các bài viết pr cho sự kiện</t>
         </is>
       </c>
       <c r="F768" s="9" t="n">
@@ -11502,41 +11516,27 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" s="12" t="inlineStr">
-        <is>
-          <t>Đã có bài</t>
-        </is>
-      </c>
-      <c r="B769" s="3" t="inlineStr">
-        <is>
-          <t>PR theo sự kiện</t>
-        </is>
-      </c>
-      <c r="C769" s="3" t="inlineStr">
-        <is>
-          <t>Mục con trong /bai-pr-mau/</t>
-        </is>
-      </c>
-      <c r="D769" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E769" s="5" t="inlineStr">
-        <is>
-          <t>viết bài pr cho sự kiện</t>
-        </is>
-      </c>
-      <c r="F769" s="6" t="n">
-        <v>10</v>
+      <c r="A769" s="7" t="n"/>
+      <c r="B769" s="7" t="n"/>
+      <c r="C769" s="7" t="n"/>
+      <c r="D769" s="7" t="n"/>
+      <c r="E769" s="8" t="inlineStr">
+        <is>
+          <t>bài pr sự kiện về quốc tế thiếu nhi</t>
+        </is>
+      </c>
+      <c r="F769" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="770">
-      <c r="A770" s="7" t="n"/>
-      <c r="B770" s="7" t="n"/>
-      <c r="C770" s="7" t="n"/>
-      <c r="D770" s="7" t="n"/>
+      <c r="A770" s="10" t="n"/>
+      <c r="B770" s="10" t="n"/>
+      <c r="C770" s="10" t="n"/>
+      <c r="D770" s="10" t="n"/>
       <c r="E770" s="8" t="inlineStr">
         <is>
-          <t>bài pr sự kiện</t>
+          <t>những bài viết pr cho sự kiện ngày hội sách</t>
         </is>
       </c>
       <c r="F770" s="9" t="n">
@@ -11544,17 +11544,31 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" s="7" t="n"/>
-      <c r="B771" s="7" t="n"/>
-      <c r="C771" s="7" t="n"/>
-      <c r="D771" s="7" t="n"/>
-      <c r="E771" s="8" t="inlineStr">
-        <is>
-          <t>bài pr sau sự kiện</t>
-        </is>
-      </c>
-      <c r="F771" s="9" t="n">
-        <v>0</v>
+      <c r="A771" s="13" t="inlineStr">
+        <is>
+          <t>Không viết (ngoài phạm vi)</t>
+        </is>
+      </c>
+      <c r="B771" s="3" t="inlineStr">
+        <is>
+          <t>PR bản thân - xin việc/du học Nhật</t>
+        </is>
+      </c>
+      <c r="C771" s="3" t="inlineStr">
+        <is>
+          <t>Ngoài phạm vi - tự giới thiệu khi xin việc/du học Nhật, không liên quan báo chí</t>
+        </is>
+      </c>
+      <c r="D771" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E771" s="5" t="inlineStr">
+        <is>
+          <t>bài mẫu pr bản thân bằng tiếng nhật</t>
+        </is>
+      </c>
+      <c r="F771" s="6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="772">
@@ -11564,7 +11578,7 @@
       <c r="D772" s="7" t="n"/>
       <c r="E772" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr sự kiện</t>
+          <t>bài pr bản thân bằng tiếng nhật</t>
         </is>
       </c>
       <c r="F772" s="9" t="n">
@@ -11572,13 +11586,13 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" s="7" t="n"/>
-      <c r="B773" s="7" t="n"/>
-      <c r="C773" s="7" t="n"/>
-      <c r="D773" s="7" t="n"/>
+      <c r="A773" s="10" t="n"/>
+      <c r="B773" s="10" t="n"/>
+      <c r="C773" s="10" t="n"/>
+      <c r="D773" s="10" t="n"/>
       <c r="E773" s="8" t="inlineStr">
         <is>
-          <t>bài viết pr sự kiện ô tô</t>
+          <t>các bài viết pr cho game học tiếng nhật</t>
         </is>
       </c>
       <c r="F773" s="9" t="n">
@@ -11586,17 +11600,31 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" s="7" t="n"/>
-      <c r="B774" s="7" t="n"/>
-      <c r="C774" s="7" t="n"/>
-      <c r="D774" s="7" t="n"/>
-      <c r="E774" s="8" t="inlineStr">
-        <is>
-          <t>caác bài viết pr sự kiện</t>
-        </is>
-      </c>
-      <c r="F774" s="9" t="n">
-        <v>0</v>
+      <c r="A774" s="13" t="inlineStr">
+        <is>
+          <t>Không viết (ngoài phạm vi)</t>
+        </is>
+      </c>
+      <c r="B774" s="3" t="inlineStr">
+        <is>
+          <t>CTV / tuyển người viết (cung ứng, không phải khách)</t>
+        </is>
+      </c>
+      <c r="C774" s="3" t="inlineStr">
+        <is>
+          <t>Intent người ĐI LÀM/ứng tuyển viết bài, không phải khách mua dịch vụ</t>
+        </is>
+      </c>
+      <c r="D774" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E774" s="5" t="inlineStr">
+        <is>
+          <t>ctv viết bài pr</t>
+        </is>
+      </c>
+      <c r="F774" s="6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="775">
@@ -11606,11 +11634,11 @@
       <c r="D775" s="7" t="n"/>
       <c r="E775" s="8" t="inlineStr">
         <is>
-          <t>caách viết bài pr sự kiện</t>
+          <t>cộng tác viên viết bài pr</t>
         </is>
       </c>
       <c r="F775" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="776">
@@ -11620,7 +11648,7 @@
       <c r="D776" s="7" t="n"/>
       <c r="E776" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr cho sự kiện</t>
+          <t>nghề viết bài pr</t>
         </is>
       </c>
       <c r="F776" s="9" t="n">
@@ -11634,7 +11662,7 @@
       <c r="D777" s="7" t="n"/>
       <c r="E777" s="8" t="inlineStr">
         <is>
-          <t>bài pr sự kiện về quốc tế thiếu nhi</t>
+          <t>nhận viết bài pr</t>
         </is>
       </c>
       <c r="F777" s="9" t="n">
@@ -11642,13 +11670,13 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" s="10" t="n"/>
-      <c r="B778" s="10" t="n"/>
-      <c r="C778" s="10" t="n"/>
-      <c r="D778" s="10" t="n"/>
+      <c r="A778" s="7" t="n"/>
+      <c r="B778" s="7" t="n"/>
+      <c r="C778" s="7" t="n"/>
+      <c r="D778" s="7" t="n"/>
       <c r="E778" s="8" t="inlineStr">
         <is>
-          <t>những bài viết pr cho sự kiện ngày hội sách</t>
+          <t>nhân viên viết bài pr</t>
         </is>
       </c>
       <c r="F778" s="9" t="n">
@@ -11656,31 +11684,17 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" s="13" t="inlineStr">
-        <is>
-          <t>Không viết (ngoài phạm vi)</t>
-        </is>
-      </c>
-      <c r="B779" s="3" t="inlineStr">
-        <is>
-          <t>PR bản thân - xin việc/du học Nhật</t>
-        </is>
-      </c>
-      <c r="C779" s="3" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi - tự giới thiệu khi xin việc/du học Nhật, không liên quan báo chí</t>
-        </is>
-      </c>
-      <c r="D779" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E779" s="5" t="inlineStr">
-        <is>
-          <t>bài mẫu pr bản thân bằng tiếng nhật</t>
-        </is>
-      </c>
-      <c r="F779" s="6" t="n">
-        <v>20</v>
+      <c r="A779" s="7" t="n"/>
+      <c r="B779" s="7" t="n"/>
+      <c r="C779" s="7" t="n"/>
+      <c r="D779" s="7" t="n"/>
+      <c r="E779" s="8" t="inlineStr">
+        <is>
+          <t>tuyển ctv viết bài pr</t>
+        </is>
+      </c>
+      <c r="F779" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="780">
@@ -11690,7 +11704,7 @@
       <c r="D780" s="7" t="n"/>
       <c r="E780" s="8" t="inlineStr">
         <is>
-          <t>bài pr bản thân bằng tiếng nhật</t>
+          <t>freelancer viết bài pr</t>
         </is>
       </c>
       <c r="F780" s="9" t="n">
@@ -11698,13 +11712,13 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" s="10" t="n"/>
-      <c r="B781" s="10" t="n"/>
-      <c r="C781" s="10" t="n"/>
-      <c r="D781" s="10" t="n"/>
+      <c r="A781" s="7" t="n"/>
+      <c r="B781" s="7" t="n"/>
+      <c r="C781" s="7" t="n"/>
+      <c r="D781" s="7" t="n"/>
       <c r="E781" s="8" t="inlineStr">
         <is>
-          <t>các bài viết pr cho game học tiếng nhật</t>
+          <t>tuyển người viết bài pr</t>
         </is>
       </c>
       <c r="F781" s="9" t="n">
@@ -11712,31 +11726,17 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" s="13" t="inlineStr">
-        <is>
-          <t>Không viết (ngoài phạm vi)</t>
-        </is>
-      </c>
-      <c r="B782" s="3" t="inlineStr">
-        <is>
-          <t>CTV / tuyển người viết</t>
-        </is>
-      </c>
-      <c r="C782" s="3" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi - intent ứng tuyển, không phải khách mua dịch vụ</t>
-        </is>
-      </c>
-      <c r="D782" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E782" s="5" t="inlineStr">
-        <is>
-          <t>ctv viết bài pr</t>
-        </is>
-      </c>
-      <c r="F782" s="6" t="n">
-        <v>10</v>
+      <c r="A782" s="7" t="n"/>
+      <c r="B782" s="7" t="n"/>
+      <c r="C782" s="7" t="n"/>
+      <c r="D782" s="7" t="n"/>
+      <c r="E782" s="8" t="inlineStr">
+        <is>
+          <t>agency tuyển viết bài pr</t>
+        </is>
+      </c>
+      <c r="F782" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="783">
@@ -11746,11 +11746,11 @@
       <c r="D783" s="7" t="n"/>
       <c r="E783" s="8" t="inlineStr">
         <is>
-          <t>cộng tác viên viết bài pr</t>
+          <t>tuyển viết bài pr agency</t>
         </is>
       </c>
       <c r="F783" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="784">
@@ -11760,7 +11760,7 @@
       <c r="D784" s="7" t="n"/>
       <c r="E784" s="8" t="inlineStr">
         <is>
-          <t>tuyển ctv viết bài pr</t>
+          <t>tìm việc làm viết bài pr</t>
         </is>
       </c>
       <c r="F784" s="9" t="n">
@@ -11774,7 +11774,7 @@
       <c r="D785" s="7" t="n"/>
       <c r="E785" s="8" t="inlineStr">
         <is>
-          <t>tuyển người viết bài pr</t>
+          <t>tuyển viết bài pr đăng báo</t>
         </is>
       </c>
       <c r="F785" s="9" t="n">
@@ -11788,7 +11788,7 @@
       <c r="D786" s="7" t="n"/>
       <c r="E786" s="8" t="inlineStr">
         <is>
-          <t>agency tuyển viết bài pr</t>
+          <t>agency tuyển ctv viết bài pr</t>
         </is>
       </c>
       <c r="F786" s="9" t="n">
@@ -11802,7 +11802,7 @@
       <c r="D787" s="7" t="n"/>
       <c r="E787" s="8" t="inlineStr">
         <is>
-          <t>tuyển viết bài pr agency</t>
+          <t>agency tuyển team viết bài pr</t>
         </is>
       </c>
       <c r="F787" s="9" t="n">
@@ -11816,7 +11816,7 @@
       <c r="D788" s="7" t="n"/>
       <c r="E788" s="8" t="inlineStr">
         <is>
-          <t>tuyển viết bài pr đăng báo</t>
+          <t>tuyển ctv viết bài pr báo chí</t>
         </is>
       </c>
       <c r="F788" s="9" t="n">
@@ -11830,7 +11830,7 @@
       <c r="D789" s="7" t="n"/>
       <c r="E789" s="8" t="inlineStr">
         <is>
-          <t>agency tuyển ctv viết bài pr</t>
+          <t>tuyển cộng tác viên viết bài pr</t>
         </is>
       </c>
       <c r="F789" s="9" t="n">
@@ -11844,7 +11844,7 @@
       <c r="D790" s="7" t="n"/>
       <c r="E790" s="8" t="inlineStr">
         <is>
-          <t>agency tuyển team viết bài pr</t>
+          <t>mục đích đăng bài tuyển dụng để pr</t>
         </is>
       </c>
       <c r="F790" s="9" t="n">
@@ -11852,123 +11852,81 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" s="7" t="n"/>
-      <c r="B791" s="7" t="n"/>
-      <c r="C791" s="7" t="n"/>
-      <c r="D791" s="7" t="n"/>
+      <c r="A791" s="10" t="n"/>
+      <c r="B791" s="10" t="n"/>
+      <c r="C791" s="10" t="n"/>
+      <c r="D791" s="10" t="n"/>
       <c r="E791" s="8" t="inlineStr">
         <is>
-          <t>tuyển ctv viết bài pr báo chí</t>
+          <t>tuyển nhân viên pr viết bài website</t>
         </is>
       </c>
       <c r="F791" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="792">
-      <c r="A792" s="7" t="n"/>
-      <c r="B792" s="7" t="n"/>
-      <c r="C792" s="7" t="n"/>
-      <c r="D792" s="7" t="n"/>
-      <c r="E792" s="8" t="inlineStr">
-        <is>
-          <t>tuyển cộng tác viên viết bài pr</t>
-        </is>
-      </c>
-      <c r="F792" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="793">
-      <c r="A793" s="7" t="n"/>
-      <c r="B793" s="7" t="n"/>
-      <c r="C793" s="7" t="n"/>
-      <c r="D793" s="7" t="n"/>
-      <c r="E793" s="8" t="inlineStr">
-        <is>
-          <t>mục đích đăng bài tuyển dụng để pr</t>
-        </is>
-      </c>
-      <c r="F793" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="794">
-      <c r="A794" s="10" t="n"/>
-      <c r="B794" s="10" t="n"/>
-      <c r="C794" s="10" t="n"/>
-      <c r="D794" s="10" t="n"/>
-      <c r="E794" s="8" t="inlineStr">
-        <is>
-          <t>tuyển nhân viên pr viết bài website</t>
-        </is>
-      </c>
-      <c r="F794" s="9" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B782:B794"/>
-    <mergeCell ref="A444:A595"/>
-    <mergeCell ref="A596:A721"/>
-    <mergeCell ref="B117:B376"/>
-    <mergeCell ref="C444:C595"/>
-    <mergeCell ref="C596:C721"/>
-    <mergeCell ref="B47:B116"/>
-    <mergeCell ref="C117:C376"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="D596:D721"/>
-    <mergeCell ref="B722:B742"/>
-    <mergeCell ref="A758:A768"/>
-    <mergeCell ref="D722:D742"/>
-    <mergeCell ref="B16:B34"/>
-    <mergeCell ref="B743:B757"/>
-    <mergeCell ref="D743:D757"/>
-    <mergeCell ref="D769:D778"/>
-    <mergeCell ref="C782:C794"/>
-    <mergeCell ref="A769:A778"/>
-    <mergeCell ref="C769:C778"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="A722:A742"/>
-    <mergeCell ref="C779:C781"/>
-    <mergeCell ref="C16:C34"/>
-    <mergeCell ref="D16:D34"/>
-    <mergeCell ref="A35:A41"/>
-    <mergeCell ref="C47:C116"/>
-    <mergeCell ref="C377:C443"/>
-    <mergeCell ref="B35:B41"/>
-    <mergeCell ref="D117:D376"/>
-    <mergeCell ref="D35:D41"/>
-    <mergeCell ref="A779:A781"/>
-    <mergeCell ref="A16:A34"/>
-    <mergeCell ref="B758:B768"/>
-    <mergeCell ref="B444:B595"/>
-    <mergeCell ref="D47:D116"/>
-    <mergeCell ref="C743:C757"/>
-    <mergeCell ref="C758:C768"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="A47:A116"/>
-    <mergeCell ref="A117:A376"/>
-    <mergeCell ref="B596:B721"/>
-    <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B779:B781"/>
-    <mergeCell ref="A743:A757"/>
-    <mergeCell ref="D2:D15"/>
-    <mergeCell ref="B769:B778"/>
-    <mergeCell ref="D779:D781"/>
-    <mergeCell ref="D782:D794"/>
-    <mergeCell ref="D758:D768"/>
-    <mergeCell ref="A377:A443"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="C722:C742"/>
-    <mergeCell ref="D444:D595"/>
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="B377:B443"/>
-    <mergeCell ref="C2:C15"/>
-    <mergeCell ref="D377:D443"/>
-    <mergeCell ref="A782:A794"/>
-    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="D23:D41"/>
+    <mergeCell ref="A747:A761"/>
+    <mergeCell ref="D771:D773"/>
+    <mergeCell ref="D723:D746"/>
+    <mergeCell ref="A54:A167"/>
+    <mergeCell ref="C567:C648"/>
+    <mergeCell ref="B762:B770"/>
+    <mergeCell ref="C54:C167"/>
+    <mergeCell ref="A299:A367"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="C299:C367"/>
+    <mergeCell ref="D747:D761"/>
+    <mergeCell ref="C649:C722"/>
+    <mergeCell ref="B368:B566"/>
+    <mergeCell ref="D649:D722"/>
+    <mergeCell ref="D368:D566"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="D299:D367"/>
+    <mergeCell ref="B747:B761"/>
+    <mergeCell ref="A771:A773"/>
+    <mergeCell ref="A723:A746"/>
+    <mergeCell ref="B771:B773"/>
+    <mergeCell ref="C762:C770"/>
+    <mergeCell ref="A774:A791"/>
+    <mergeCell ref="D42:D48"/>
+    <mergeCell ref="C774:C791"/>
+    <mergeCell ref="B2:B22"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="D2:D22"/>
+    <mergeCell ref="C49:C53"/>
+    <mergeCell ref="A168:A298"/>
+    <mergeCell ref="C168:C298"/>
+    <mergeCell ref="A649:A722"/>
+    <mergeCell ref="A368:A566"/>
+    <mergeCell ref="C368:C566"/>
+    <mergeCell ref="B723:B746"/>
+    <mergeCell ref="B23:B41"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C747:C761"/>
+    <mergeCell ref="A567:A648"/>
+    <mergeCell ref="D774:D791"/>
+    <mergeCell ref="C23:C41"/>
+    <mergeCell ref="A2:A22"/>
+    <mergeCell ref="D49:D53"/>
+    <mergeCell ref="B54:B167"/>
+    <mergeCell ref="D762:D770"/>
+    <mergeCell ref="B649:B722"/>
+    <mergeCell ref="C771:C773"/>
+    <mergeCell ref="C723:C746"/>
+    <mergeCell ref="B774:B791"/>
+    <mergeCell ref="C2:C22"/>
+    <mergeCell ref="A23:A41"/>
+    <mergeCell ref="B567:B648"/>
+    <mergeCell ref="B168:B298"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="D567:D648"/>
+    <mergeCell ref="D168:D298"/>
+    <mergeCell ref="D54:D167"/>
+    <mergeCell ref="A762:A770"/>
+    <mergeCell ref="B299:B367"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
+++ b/content/ke-hoach-noi-dung-cum-pr-2026-08-10.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,10 @@
     <font>
       <b val="1"/>
       <color rgb="006B7280"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -200,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -261,6 +265,20 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F791"/>
+  <dimension ref="A1:F845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10898,7 +10916,7 @@
       </c>
       <c r="B722" s="16" t="inlineStr">
         <is>
-          <t>PR doanh nghiệp / thương hiệu</t>
+          <t>PR thương hiệu lớn (mẫu bài)</t>
         </is>
       </c>
       <c r="C722" s="16" t="inlineStr">
@@ -10907,7 +10925,7 @@
         </is>
       </c>
       <c r="D722" s="17" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E722" s="18" t="inlineStr">
         <is>
@@ -10919,10 +10937,24 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" s="20" t="n"/>
-      <c r="B723" s="20" t="n"/>
-      <c r="C723" s="20" t="n"/>
-      <c r="D723" s="20" t="n"/>
+      <c r="A723" s="23" t="inlineStr">
+        <is>
+          <t>CHƯA CÓ - cần viết mới</t>
+        </is>
+      </c>
+      <c r="B723" s="16" t="inlineStr">
+        <is>
+          <t>PR doanh nghiệp / công ty</t>
+        </is>
+      </c>
+      <c r="C723" s="16" t="inlineStr">
+        <is>
+          <t>CHƯA CÓ - viết bài mới "Cách viết bài PR cho doanh nghiệp/công ty" (howto): định nghĩa ngắn (link về /bai-pr-la-gi/, không lặp lại), các bước viết, ví dụ theo ngành (đại lý ô tô, may mặc, thiết kế nội thất, công ty con/tập đoàn), 1-2 ví dụ minh hoạ theo thương hiệu lớn (Honda, Nike - dán nhãn "ví dụ minh hoạ", không phải case thật), FAQ (giới hạn 200 từ, có được bán bài PR doanh nghiệp không). CTA về /booking-bao-pr/</t>
+        </is>
+      </c>
+      <c r="D723" s="17" t="n">
+        <v>70</v>
+      </c>
       <c r="E723" s="18" t="inlineStr">
         <is>
           <t>bài pr doanh nghiệp</t>
@@ -11271,7 +11303,7 @@
     <row r="747">
       <c r="A747" s="20" t="n"/>
       <c r="B747" s="20" t="n"/>
-      <c r="C747" s="20" t="n"/>
+      <c r="C747" s="21" t="n"/>
       <c r="D747" s="20" t="n"/>
       <c r="E747" s="18" t="inlineStr">
         <is>
@@ -11285,7 +11317,11 @@
     <row r="748">
       <c r="A748" s="20" t="n"/>
       <c r="B748" s="20" t="n"/>
-      <c r="C748" s="20" t="n"/>
+      <c r="C748" s="16" t="inlineStr">
+        <is>
+          <t>Đã có bài (bài con riêng) - /lead-bai-pr-la-gi/ (mở rộng chi tiết từ /bai-pr-la-gi/, viết 2026-08-11)</t>
+        </is>
+      </c>
       <c r="D748" s="20" t="n"/>
       <c r="E748" s="18" t="inlineStr">
         <is>
@@ -11299,7 +11335,7 @@
     <row r="749">
       <c r="A749" s="20" t="n"/>
       <c r="B749" s="20" t="n"/>
-      <c r="C749" s="20" t="n"/>
+      <c r="C749" s="16" t="n"/>
       <c r="D749" s="20" t="n"/>
       <c r="E749" s="18" t="inlineStr">
         <is>
@@ -11397,7 +11433,7 @@
     <row r="756">
       <c r="A756" s="20" t="n"/>
       <c r="B756" s="20" t="n"/>
-      <c r="C756" s="20" t="n"/>
+      <c r="C756" s="21" t="n"/>
       <c r="D756" s="20" t="n"/>
       <c r="E756" s="18" t="inlineStr">
         <is>
@@ -11411,7 +11447,11 @@
     <row r="757">
       <c r="A757" s="20" t="n"/>
       <c r="B757" s="20" t="n"/>
-      <c r="C757" s="20" t="n"/>
+      <c r="C757" s="16" t="inlineStr">
+        <is>
+          <t>Đã có bài (bài con riêng) - /sapo-la-gi-trong-bai-pr/ (vị trí/vai trò/format sapo, viết 2026-08-11)</t>
+        </is>
+      </c>
       <c r="D757" s="20" t="n"/>
       <c r="E757" s="18" t="inlineStr">
         <is>
@@ -11425,7 +11465,7 @@
     <row r="758">
       <c r="A758" s="20" t="n"/>
       <c r="B758" s="20" t="n"/>
-      <c r="C758" s="20" t="n"/>
+      <c r="C758" s="16" t="n"/>
       <c r="D758" s="20" t="n"/>
       <c r="E758" s="18" t="inlineStr">
         <is>
@@ -11940,52 +11980,651 @@
         <v>0</v>
       </c>
     </row>
+    <row r="792">
+      <c r="A792" s="25" t="inlineStr">
+        <is>
+          <t>Có bài, cần bổ sung thêm</t>
+        </is>
+      </c>
+      <c r="B792" s="26" t="inlineStr">
+        <is>
+          <t>Công thức viết bài PR: PAS / 3S / Strings</t>
+        </is>
+      </c>
+      <c r="C792" s="26" t="inlineStr">
+        <is>
+          <t>Bổ sung 3 mục lớn (PAS, 3S, Strings) vào /cach-viet-bai-pr-chuan-bao-chi/ - moi cong thuc 1 so do giai thich + vi du bai PR mau ap dung. 'công thức pas' rieng le da 260 vol (cao hon volume ca cum hien tai 280) - CAN research SERP truoc khi quyet dinh giu lam muc con hay tach trang rieng /cong-thuc-pas-la-gi/ (theo audit-intent-truoc.md, khong tu quyet)</t>
+        </is>
+      </c>
+      <c r="D792" s="27" t="n">
+        <v>430</v>
+      </c>
+      <c r="E792" s="28" t="inlineStr">
+        <is>
+          <t>công thức pas</t>
+        </is>
+      </c>
+      <c r="F792" s="28" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="E793" s="28" t="inlineStr">
+        <is>
+          <t>công thức content pas</t>
+        </is>
+      </c>
+      <c r="F793" s="28" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="E794" s="28" t="inlineStr">
+        <is>
+          <t>công thức pas là gì</t>
+        </is>
+      </c>
+      <c r="F794" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="E795" s="28" t="inlineStr">
+        <is>
+          <t>công thức viết bài pas</t>
+        </is>
+      </c>
+      <c r="F795" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="E796" s="28" t="inlineStr">
+        <is>
+          <t>công thức viết content pas</t>
+        </is>
+      </c>
+      <c r="F796" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="E797" s="28" t="inlineStr">
+        <is>
+          <t>cách viết công thức pas</t>
+        </is>
+      </c>
+      <c r="F797" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="E798" s="28" t="inlineStr">
+        <is>
+          <t>công thức bán hàng pas</t>
+        </is>
+      </c>
+      <c r="F798" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="E799" s="28" t="inlineStr">
+        <is>
+          <t>công thức 3s</t>
+        </is>
+      </c>
+      <c r="F799" s="28" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="E800" s="28" t="inlineStr">
+        <is>
+          <t>công thức strings</t>
+        </is>
+      </c>
+      <c r="F800" s="28" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="E801" s="28" t="inlineStr">
+        <is>
+          <t>ví dụ công thức strings</t>
+        </is>
+      </c>
+      <c r="F801" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="E802" s="28" t="inlineStr">
+        <is>
+          <t>ví dụ công thức strings pr</t>
+        </is>
+      </c>
+      <c r="F802" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="E803" s="28" t="inlineStr">
+        <is>
+          <t>công thức strings các bài viết theo công thức này</t>
+        </is>
+      </c>
+      <c r="F803" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="29" t="inlineStr">
+        <is>
+          <t>CHƯA CÓ - cần viết mới</t>
+        </is>
+      </c>
+      <c r="B804" s="26" t="inlineStr">
+        <is>
+          <t>Các dạng bài PR: Advertorial / Editorial / Testimonial</t>
+        </is>
+      </c>
+      <c r="C804" s="26" t="inlineStr">
+        <is>
+          <t>CHUA CO - viet bai moi 'Cac Dang Bai PR Pho Bien' giai thich + vi du mau tung dang (Advertorial/Editorial/Testimonial). Link 2 chieu voi /cach-viet-bai-pr-chuan-bao-chi/ (muc 'cac dang bai pr' dang chung chung, doi sang tro bai nay) va /bai-pr-mau/. CTA ve /booking-bao-pr/</t>
+        </is>
+      </c>
+      <c r="D804" s="27" t="n">
+        <v>160</v>
+      </c>
+      <c r="E804" s="28" t="inlineStr">
+        <is>
+          <t>bài advertorial</t>
+        </is>
+      </c>
+      <c r="F804" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="E805" s="28" t="inlineStr">
+        <is>
+          <t>bài advertorial mẫu</t>
+        </is>
+      </c>
+      <c r="F805" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="E806" s="28" t="inlineStr">
+        <is>
+          <t>bài advertorial mẫu về khách sạn</t>
+        </is>
+      </c>
+      <c r="F806" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="E807" s="28" t="inlineStr">
+        <is>
+          <t>cách viết bài advertorial</t>
+        </is>
+      </c>
+      <c r="F807" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="E808" s="28" t="inlineStr">
+        <is>
+          <t>viết bài advertorial</t>
+        </is>
+      </c>
+      <c r="F808" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="E809" s="28" t="inlineStr">
+        <is>
+          <t>viết bài advertorial cho bitis hunter x</t>
+        </is>
+      </c>
+      <c r="F809" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="E810" s="28" t="inlineStr">
+        <is>
+          <t>đăng bài advertorial</t>
+        </is>
+      </c>
+      <c r="F810" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="E811" s="28" t="inlineStr">
+        <is>
+          <t>bài editorial mẫu</t>
+        </is>
+      </c>
+      <c r="F811" s="28" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="E812" s="28" t="inlineStr">
+        <is>
+          <t>bài viết editorial</t>
+        </is>
+      </c>
+      <c r="F812" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="E813" s="28" t="inlineStr">
+        <is>
+          <t>dạng bài editorial</t>
+        </is>
+      </c>
+      <c r="F813" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="E814" s="28" t="inlineStr">
+        <is>
+          <t>bài editorial</t>
+        </is>
+      </c>
+      <c r="F814" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="E815" s="28" t="inlineStr">
+        <is>
+          <t>bài báo editorial</t>
+        </is>
+      </c>
+      <c r="F815" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="E816" s="28" t="inlineStr">
+        <is>
+          <t>bài báo viết theo dạng editorial</t>
+        </is>
+      </c>
+      <c r="F816" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="E817" s="28" t="inlineStr">
+        <is>
+          <t>bài editorial kinh tế</t>
+        </is>
+      </c>
+      <c r="F817" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="E818" s="28" t="inlineStr">
+        <is>
+          <t>bài editorials</t>
+        </is>
+      </c>
+      <c r="F818" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="E819" s="28" t="inlineStr">
+        <is>
+          <t>các bài báo editorial</t>
+        </is>
+      </c>
+      <c r="F819" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="E820" s="28" t="inlineStr">
+        <is>
+          <t>các bài editorial về dịch vụ du lịch</t>
+        </is>
+      </c>
+      <c r="F820" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="E821" s="28" t="inlineStr">
+        <is>
+          <t>các bài viết editorial</t>
+        </is>
+      </c>
+      <c r="F821" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="E822" s="28" t="inlineStr">
+        <is>
+          <t>các dạng bài editorial</t>
+        </is>
+      </c>
+      <c r="F822" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="E823" s="28" t="inlineStr">
+        <is>
+          <t>những bài editorial hay nhất</t>
+        </is>
+      </c>
+      <c r="F823" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="E824" s="28" t="inlineStr">
+        <is>
+          <t>viết bài editorial</t>
+        </is>
+      </c>
+      <c r="F824" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="E825" s="28" t="inlineStr">
+        <is>
+          <t>viết bài editorial và advertorial</t>
+        </is>
+      </c>
+      <c r="F825" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="E826" s="28" t="inlineStr">
+        <is>
+          <t>ví dụ bài editorial</t>
+        </is>
+      </c>
+      <c r="F826" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="E827" s="28" t="inlineStr">
+        <is>
+          <t>dạng bài testimonial</t>
+        </is>
+      </c>
+      <c r="F827" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="E828" s="28" t="inlineStr">
+        <is>
+          <t>bài viết testimonial hay</t>
+        </is>
+      </c>
+      <c r="F828" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="E829" s="28" t="inlineStr">
+        <is>
+          <t>dạng bài testimonial là gì</t>
+        </is>
+      </c>
+      <c r="F829" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="25" t="inlineStr">
+        <is>
+          <t>Có bài, cần bổ sung thêm</t>
+        </is>
+      </c>
+      <c r="B830" s="26" t="inlineStr">
+        <is>
+          <t>Mô hình kim tự tháp ngược trong viết bài PR</t>
+        </is>
+      </c>
+      <c r="C830" s="26" t="inlineStr">
+        <is>
+          <t>Them 1 muc ngan + so do minh hoa 'Mo hinh kim tu thap nguoc' vao /cach-viet-bai-pr-chuan-bao-chi/ (muc cau truc bai, da co dong 0-vol 'mo hinh kim tu thap nguoc trong viet bai pr'). CANH BAO: 'mo hinh kim tu thap nguoc' (50) va 'kim tu thap nguoc' (10) la tu khoa DA NGHIA - phan lon volume thuoc ve bao tang/landmark Ha Noi va mo hinh tai chinh John Exter (xem cum ben duoi), KHONG phai khai niem viet bai. KHONG viet bai/pillar rieng cho cum nay, chi la 1 muc bo sung, khong ky vong volume thuc te cao nhu con so hien</t>
+        </is>
+      </c>
+      <c r="D830" s="27" t="n">
+        <v>60</v>
+      </c>
+      <c r="E830" s="28" t="inlineStr">
+        <is>
+          <t>mô hình kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F830" s="28" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="E831" s="28" t="inlineStr">
+        <is>
+          <t>kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F831" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="E832" s="28" t="inlineStr">
+        <is>
+          <t>kim tự tháp ngược trong viết content</t>
+        </is>
+      </c>
+      <c r="F832" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="E833" s="28" t="inlineStr">
+        <is>
+          <t>format chuẩn kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F833" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="E834" s="28" t="inlineStr">
+        <is>
+          <t>đây là mô hình kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F834" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="30" t="inlineStr">
+        <is>
+          <t>Không viết (ngoài phạm vi)</t>
+        </is>
+      </c>
+      <c r="B835" s="26" t="inlineStr">
+        <is>
+          <t>Kim tự tháp ngược - bảo tàng / mô hình tài chính</t>
+        </is>
+      </c>
+      <c r="C835" s="26" t="inlineStr">
+        <is>
+          <t>Ngoai pham vi - thuoc chu de bao tang/landmark kien truc (Ha Noi) hoac mo hinh tai chinh John Exter (lai suat, thanh khoan ngan hang), khong lien quan viet bai PR/content</t>
+        </is>
+      </c>
+      <c r="D835" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E835" s="28" t="inlineStr">
+        <is>
+          <t>bảo tàng kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F835" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="E836" s="28" t="inlineStr">
+        <is>
+          <t>bảo tàng hình kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F836" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="E837" s="28" t="inlineStr">
+        <is>
+          <t>bảo tàng kim tự tháp lộn ngược</t>
+        </is>
+      </c>
+      <c r="F837" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="E838" s="28" t="inlineStr">
+        <is>
+          <t>kim tự tháp chổng ngược ở hà nội</t>
+        </is>
+      </c>
+      <c r="F838" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="E839" s="28" t="inlineStr">
+        <is>
+          <t>kim tự tháp ngược ở hà nội</t>
+        </is>
+      </c>
+      <c r="F839" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="E840" s="28" t="inlineStr">
+        <is>
+          <t>lãi suất mô hình kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F840" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="E841" s="28" t="inlineStr">
+        <is>
+          <t>lãi suất ngân hàng mô hình kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F841" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="E842" s="28" t="inlineStr">
+        <is>
+          <t>mô hình kim tự tháp ngược của john exter</t>
+        </is>
+      </c>
+      <c r="F842" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="E843" s="28" t="inlineStr">
+        <is>
+          <t>mô hình kim tự tháp ngược john exter</t>
+        </is>
+      </c>
+      <c r="F843" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="E844" s="28" t="inlineStr">
+        <is>
+          <t>mô hình kim tự tháp ngược lãi suất</t>
+        </is>
+      </c>
+      <c r="F844" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="E845" s="28" t="inlineStr">
+        <is>
+          <t>mô hình quản trị kim tự tháp ngược</t>
+        </is>
+      </c>
+      <c r="F845" s="28" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="60">
+  <mergeCells count="62">
     <mergeCell ref="D566:D647"/>
+    <mergeCell ref="D23:D41"/>
+    <mergeCell ref="B298:B366"/>
     <mergeCell ref="D167:D297"/>
+    <mergeCell ref="C749:C756"/>
+    <mergeCell ref="D298:D366"/>
     <mergeCell ref="D771:D773"/>
+    <mergeCell ref="B42:B48"/>
     <mergeCell ref="D761:D770"/>
+    <mergeCell ref="D648:D721"/>
+    <mergeCell ref="C746:C747"/>
+    <mergeCell ref="B723:B745"/>
+    <mergeCell ref="A761:A770"/>
     <mergeCell ref="A648:A721"/>
+    <mergeCell ref="C761:C770"/>
     <mergeCell ref="C367:C565"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="A746:A760"/>
+    <mergeCell ref="A167:A297"/>
+    <mergeCell ref="C298:C366"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="A771:A773"/>
+    <mergeCell ref="C723:C745"/>
+    <mergeCell ref="C758:C760"/>
+    <mergeCell ref="C648:C721"/>
     <mergeCell ref="B771:B773"/>
     <mergeCell ref="A774:A791"/>
     <mergeCell ref="B54:B166"/>
     <mergeCell ref="D42:D48"/>
+    <mergeCell ref="C774:C791"/>
     <mergeCell ref="D54:D166"/>
-    <mergeCell ref="C774:C791"/>
-    <mergeCell ref="A54:A166"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C54:C166"/>
-    <mergeCell ref="B746:B760"/>
-    <mergeCell ref="D746:D760"/>
-    <mergeCell ref="D774:D791"/>
-    <mergeCell ref="A298:A366"/>
-    <mergeCell ref="A566:A647"/>
-    <mergeCell ref="C566:C647"/>
-    <mergeCell ref="B722:B745"/>
-    <mergeCell ref="B774:B791"/>
-    <mergeCell ref="D722:D745"/>
-    <mergeCell ref="C2:C22"/>
-    <mergeCell ref="B648:B721"/>
-    <mergeCell ref="B761:B770"/>
-    <mergeCell ref="A722:A745"/>
-    <mergeCell ref="D23:D41"/>
-    <mergeCell ref="B298:B366"/>
-    <mergeCell ref="D298:D366"/>
-    <mergeCell ref="B42:B48"/>
-    <mergeCell ref="D648:D721"/>
-    <mergeCell ref="A761:A770"/>
-    <mergeCell ref="C761:C770"/>
-    <mergeCell ref="B49:B53"/>
-    <mergeCell ref="A746:A760"/>
-    <mergeCell ref="A167:A297"/>
-    <mergeCell ref="C746:C760"/>
-    <mergeCell ref="C298:C366"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="A771:A773"/>
-    <mergeCell ref="C648:C721"/>
-    <mergeCell ref="C722:C745"/>
     <mergeCell ref="B2:B22"/>
     <mergeCell ref="A49:A53"/>
     <mergeCell ref="D2:D22"/>
@@ -11993,11 +12632,26 @@
     <mergeCell ref="B566:B647"/>
     <mergeCell ref="B167:B297"/>
     <mergeCell ref="A367:A565"/>
+    <mergeCell ref="A54:A166"/>
     <mergeCell ref="B23:B41"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C54:C166"/>
+    <mergeCell ref="B746:B760"/>
+    <mergeCell ref="D746:D760"/>
+    <mergeCell ref="D774:D791"/>
+    <mergeCell ref="A723:A745"/>
     <mergeCell ref="A2:A22"/>
     <mergeCell ref="D49:D53"/>
+    <mergeCell ref="D723:D745"/>
     <mergeCell ref="C167:C297"/>
     <mergeCell ref="C771:C773"/>
+    <mergeCell ref="A298:A366"/>
+    <mergeCell ref="A566:A647"/>
+    <mergeCell ref="C566:C647"/>
+    <mergeCell ref="B774:B791"/>
+    <mergeCell ref="C2:C22"/>
+    <mergeCell ref="B648:B721"/>
+    <mergeCell ref="B761:B770"/>
     <mergeCell ref="B367:B565"/>
     <mergeCell ref="A23:A41"/>
     <mergeCell ref="D367:D565"/>
